--- a/research/traditional_assets/database/data/israel/israel_recreation.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_recreation.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="tase_hlms" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -587,23 +589,29 @@
           <t>Recreation</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.0409</v>
+      </c>
+      <c r="E2">
+        <v>0.173</v>
+      </c>
       <c r="G2">
-        <v>0.1342465753424658</v>
+        <v>0.04621643612693246</v>
       </c>
       <c r="H2">
-        <v>0.1342465753424658</v>
+        <v>0.04621643612693246</v>
       </c>
       <c r="I2">
-        <v>-0.2952815829528158</v>
+        <v>0.1358828315703824</v>
       </c>
       <c r="J2">
-        <v>-0.2952815829528158</v>
+        <v>0.1358828315703824</v>
       </c>
       <c r="K2">
-        <v>-20.5</v>
+        <v>8.08</v>
       </c>
       <c r="L2">
-        <v>-0.3120243531202435</v>
+        <v>0.06574450772986168</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -621,79 +629,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>6.08</v>
+        <v>8.59</v>
       </c>
       <c r="V2">
-        <v>0.05380530973451327</v>
+        <v>0.08315585672797676</v>
       </c>
       <c r="W2">
-        <v>-0.657051282051282</v>
+        <v>0.3380753138075314</v>
       </c>
       <c r="X2">
-        <v>0.1479934176624617</v>
+        <v>0.249760813224301</v>
       </c>
       <c r="Y2">
-        <v>-0.8050446997137438</v>
+        <v>0.08831450058323043</v>
       </c>
       <c r="Z2">
-        <v>0.2680538555691555</v>
+        <v>0.4959244613025584</v>
       </c>
       <c r="AA2">
-        <v>-0.07915136678906567</v>
+        <v>0.06738762004680816</v>
       </c>
       <c r="AB2">
-        <v>0.06318624038251862</v>
+        <v>0.1007409874965098</v>
       </c>
       <c r="AC2">
-        <v>-0.1423376071715843</v>
+        <v>-0.03335336744970159</v>
       </c>
       <c r="AD2">
-        <v>258.7</v>
+        <v>266.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>258.7</v>
+        <v>266.9</v>
       </c>
       <c r="AG2">
-        <v>252.62</v>
+        <v>258.31</v>
       </c>
       <c r="AH2">
-        <v>0.6959913909066451</v>
+        <v>0.7209616423554834</v>
       </c>
       <c r="AI2">
-        <v>0.9170506912442397</v>
+        <v>0.9059742023082146</v>
       </c>
       <c r="AJ2">
-        <v>0.6909359444231715</v>
+        <v>0.7143331213185475</v>
       </c>
       <c r="AK2">
-        <v>0.9152235345264835</v>
+        <v>0.9031502395021154</v>
       </c>
       <c r="AL2">
-        <v>9.609999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="AM2">
-        <v>9.609999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="AN2">
-        <v>24.17757009345794</v>
+        <v>10.76209677419355</v>
       </c>
       <c r="AO2">
-        <v>-2.018730489073882</v>
+        <v>1.711065573770492</v>
       </c>
       <c r="AP2">
-        <v>23.60934579439252</v>
+        <v>10.41572580645161</v>
       </c>
       <c r="AQ2">
-        <v>-2.018730489073882</v>
+        <v>1.711065573770492</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +712,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Holmes Place International Ltd. (TASE:HLMS)</t>
+          <t>Holmes Place International Ltd (TASE:HLMS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -712,23 +720,29 @@
           <t>Recreation</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.0409</v>
+      </c>
+      <c r="E3">
+        <v>0.173</v>
+      </c>
       <c r="G3">
-        <v>0.1342465753424658</v>
+        <v>0.04621643612693246</v>
       </c>
       <c r="H3">
-        <v>0.1342465753424658</v>
+        <v>0.04621643612693246</v>
       </c>
       <c r="I3">
-        <v>-0.2952815829528158</v>
+        <v>0.1358828315703824</v>
       </c>
       <c r="J3">
-        <v>-0.2952815829528158</v>
+        <v>0.1358828315703824</v>
       </c>
       <c r="K3">
-        <v>-20.5</v>
+        <v>8.08</v>
       </c>
       <c r="L3">
-        <v>-0.3120243531202435</v>
+        <v>0.06574450772986168</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -737,7 +751,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -746,79 +760,8791 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>6.08</v>
+        <v>8.59</v>
       </c>
       <c r="V3">
-        <v>0.05380530973451327</v>
+        <v>0.08315585672797676</v>
       </c>
       <c r="W3">
-        <v>-0.657051282051282</v>
+        <v>0.3380753138075314</v>
       </c>
       <c r="X3">
-        <v>0.1479934176624617</v>
+        <v>0.249760813224301</v>
       </c>
       <c r="Y3">
-        <v>-0.8050446997137438</v>
+        <v>0.08831450058323043</v>
       </c>
       <c r="Z3">
-        <v>0.2680538555691555</v>
+        <v>0.4959244613025584</v>
       </c>
       <c r="AA3">
-        <v>-0.07915136678906567</v>
+        <v>0.06738762004680816</v>
       </c>
       <c r="AB3">
-        <v>0.06318624038251862</v>
+        <v>0.1007409874965098</v>
       </c>
       <c r="AC3">
-        <v>-0.1423376071715843</v>
+        <v>-0.03335336744970159</v>
       </c>
       <c r="AD3">
-        <v>258.7</v>
+        <v>266.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>258.7</v>
+        <v>266.9</v>
       </c>
       <c r="AG3">
-        <v>252.62</v>
+        <v>258.31</v>
       </c>
       <c r="AH3">
-        <v>0.6959913909066451</v>
+        <v>0.7209616423554834</v>
       </c>
       <c r="AI3">
-        <v>0.9170506912442397</v>
+        <v>0.9059742023082146</v>
       </c>
       <c r="AJ3">
-        <v>0.6909359444231715</v>
+        <v>0.7143331213185475</v>
       </c>
       <c r="AK3">
-        <v>0.9152235345264835</v>
+        <v>0.9031502395021154</v>
       </c>
       <c r="AL3">
-        <v>9.609999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="AM3">
-        <v>9.609999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="AN3">
-        <v>24.17757009345794</v>
+        <v>10.76209677419355</v>
       </c>
       <c r="AO3">
-        <v>-2.018730489073882</v>
+        <v>1.711065573770492</v>
       </c>
       <c r="AP3">
-        <v>23.60934579439252</v>
+        <v>10.41572580645161</v>
       </c>
       <c r="AQ3">
-        <v>-2.018730489073882</v>
+        <v>1.711065573770492</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Holmes Place International Ltd (TASE:HLMS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TASE:HLMS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.720961642355483</v>
+      </c>
+      <c r="F2">
+        <v>0.18</v>
+      </c>
+      <c r="G2">
+        <v>103.3</v>
+      </c>
+      <c r="H2">
+        <v>269.967273874088</v>
+      </c>
+      <c r="I2">
+        <v>361.61</v>
+      </c>
+      <c r="J2">
+        <v>328.013273874088</v>
+      </c>
+      <c r="K2">
+        <v>266.9</v>
+      </c>
+      <c r="L2">
+        <v>66.636</v>
+      </c>
+      <c r="M2">
+        <v>0.10074098749651</v>
+      </c>
+      <c r="N2">
+        <v>0.107085286824127</v>
+      </c>
+      <c r="O2">
+        <v>0.0430648990825688</v>
+      </c>
+      <c r="P2">
+        <v>0.04235</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.249760813224301</v>
+      </c>
+      <c r="T2">
+        <v>0.12129547173674</v>
+      </c>
+      <c r="U2">
+        <v>2.95820075631007</v>
+      </c>
+      <c r="V2">
+        <v>1.15679382892931</v>
+      </c>
+      <c r="W2">
+        <v>4.556641509639888</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>103.3</v>
+      </c>
+      <c r="AB2">
+        <v>0.07131389334354851</v>
+      </c>
+      <c r="AC2">
+        <v>0.05592844036697248</v>
+      </c>
+      <c r="AD2">
+        <v>0.23</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>24.8</v>
+      </c>
+      <c r="AH2">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="AI2">
+        <v>15.971</v>
+      </c>
+      <c r="AJ2">
+        <v>266.9</v>
+      </c>
+      <c r="AK2">
+        <v>266.9</v>
+      </c>
+      <c r="AL2">
+        <v>9.76</v>
+      </c>
+      <c r="AM2">
+        <v>266.9</v>
+      </c>
+      <c r="AN2">
+        <v>8.59</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.109367793473948</v>
+      </c>
+      <c r="C2">
+        <v>325.9937246450381</v>
+      </c>
+      <c r="D2">
+        <v>317.4037246450381</v>
+      </c>
+      <c r="E2">
+        <v>-266.9</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>8.59</v>
+      </c>
+      <c r="H2">
+        <v>103.3</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>24.8</v>
+      </c>
+      <c r="K2">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L2">
+        <v>16.7</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>16.7</v>
+      </c>
+      <c r="O2">
+        <v>3.841</v>
+      </c>
+      <c r="P2">
+        <v>12.859</v>
+      </c>
+      <c r="Q2">
+        <v>20.959</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.109367793473948</v>
+      </c>
+      <c r="T2">
+        <v>0.9895378048425111</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.23</v>
+      </c>
+      <c r="W2">
+        <v>0.035189</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1091693775489579</v>
+      </c>
+      <c r="C3">
+        <v>323.1866871388717</v>
+      </c>
+      <c r="D3">
+        <v>318.2986871388717</v>
+      </c>
+      <c r="E3">
+        <v>-263.198</v>
+      </c>
+      <c r="F3">
+        <v>3.702</v>
+      </c>
+      <c r="G3">
+        <v>8.59</v>
+      </c>
+      <c r="H3">
+        <v>103.3</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>24.8</v>
+      </c>
+      <c r="K3">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L3">
+        <v>16.7</v>
+      </c>
+      <c r="M3">
+        <v>0.1691814</v>
+      </c>
+      <c r="N3">
+        <v>16.5308186</v>
+      </c>
+      <c r="O3">
+        <v>3.802088278</v>
+      </c>
+      <c r="P3">
+        <v>12.728730322</v>
+      </c>
+      <c r="Q3">
+        <v>20.828730322</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1099166540898565</v>
+      </c>
+      <c r="T3">
+        <v>0.9972342099912863</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.23</v>
+      </c>
+      <c r="W3">
+        <v>0.035189</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>98.71061476025142</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1089709616239678</v>
+      </c>
+      <c r="C4">
+        <v>320.3847108377092</v>
+      </c>
+      <c r="D4">
+        <v>319.1987108377092</v>
+      </c>
+      <c r="E4">
+        <v>-259.496</v>
+      </c>
+      <c r="F4">
+        <v>7.404</v>
+      </c>
+      <c r="G4">
+        <v>8.59</v>
+      </c>
+      <c r="H4">
+        <v>103.3</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>24.8</v>
+      </c>
+      <c r="K4">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L4">
+        <v>16.7</v>
+      </c>
+      <c r="M4">
+        <v>0.3383628</v>
+      </c>
+      <c r="N4">
+        <v>16.3616372</v>
+      </c>
+      <c r="O4">
+        <v>3.763176556</v>
+      </c>
+      <c r="P4">
+        <v>12.598460644</v>
+      </c>
+      <c r="Q4">
+        <v>20.698460644</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1104767159428243</v>
+      </c>
+      <c r="T4">
+        <v>1.005087684632894</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.23</v>
+      </c>
+      <c r="W4">
+        <v>0.035189</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>49.35530738012571</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1087725456989777</v>
+      </c>
+      <c r="C5">
+        <v>317.5878387965943</v>
+      </c>
+      <c r="D5">
+        <v>320.1038387965943</v>
+      </c>
+      <c r="E5">
+        <v>-255.794</v>
+      </c>
+      <c r="F5">
+        <v>11.106</v>
+      </c>
+      <c r="G5">
+        <v>8.59</v>
+      </c>
+      <c r="H5">
+        <v>103.3</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>24.8</v>
+      </c>
+      <c r="K5">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L5">
+        <v>16.7</v>
+      </c>
+      <c r="M5">
+        <v>0.5075442</v>
+      </c>
+      <c r="N5">
+        <v>16.1924558</v>
+      </c>
+      <c r="O5">
+        <v>3.724264833999999</v>
+      </c>
+      <c r="P5">
+        <v>12.468190966</v>
+      </c>
+      <c r="Q5">
+        <v>20.568190966</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1110483254628636</v>
+      </c>
+      <c r="T5">
+        <v>1.013103086586699</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.23</v>
+      </c>
+      <c r="W5">
+        <v>0.035189</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>32.90353825341714</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1085741297739876</v>
+      </c>
+      <c r="C6">
+        <v>314.7961145603113</v>
+      </c>
+      <c r="D6">
+        <v>321.0141145603113</v>
+      </c>
+      <c r="E6">
+        <v>-252.092</v>
+      </c>
+      <c r="F6">
+        <v>14.808</v>
+      </c>
+      <c r="G6">
+        <v>8.59</v>
+      </c>
+      <c r="H6">
+        <v>103.3</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>24.8</v>
+      </c>
+      <c r="K6">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L6">
+        <v>16.7</v>
+      </c>
+      <c r="M6">
+        <v>0.6767256</v>
+      </c>
+      <c r="N6">
+        <v>16.0232744</v>
+      </c>
+      <c r="O6">
+        <v>3.685353111999999</v>
+      </c>
+      <c r="P6">
+        <v>12.337921288</v>
+      </c>
+      <c r="Q6">
+        <v>20.437921288</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1116318435145705</v>
+      </c>
+      <c r="T6">
+        <v>1.021285476081208</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.23</v>
+      </c>
+      <c r="W6">
+        <v>0.035189</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>24.67765369006285</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1083757138489976</v>
+      </c>
+      <c r="C7">
+        <v>312.0095821703683</v>
+      </c>
+      <c r="D7">
+        <v>321.9295821703683</v>
+      </c>
+      <c r="E7">
+        <v>-248.39</v>
+      </c>
+      <c r="F7">
+        <v>18.51</v>
+      </c>
+      <c r="G7">
+        <v>8.59</v>
+      </c>
+      <c r="H7">
+        <v>103.3</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>24.8</v>
+      </c>
+      <c r="K7">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L7">
+        <v>16.7</v>
+      </c>
+      <c r="M7">
+        <v>0.8459070000000002</v>
+      </c>
+      <c r="N7">
+        <v>15.854093</v>
+      </c>
+      <c r="O7">
+        <v>3.64644139</v>
+      </c>
+      <c r="P7">
+        <v>12.20765161</v>
+      </c>
+      <c r="Q7">
+        <v>20.30765161</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1122276461568395</v>
+      </c>
+      <c r="T7">
+        <v>1.029640126407181</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.23</v>
+      </c>
+      <c r="W7">
+        <v>0.035189</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>19.74212295205028</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1081772979240075</v>
+      </c>
+      <c r="C8">
+        <v>309.2282861721006</v>
+      </c>
+      <c r="D8">
+        <v>322.8502861721006</v>
+      </c>
+      <c r="E8">
+        <v>-244.688</v>
+      </c>
+      <c r="F8">
+        <v>22.212</v>
+      </c>
+      <c r="G8">
+        <v>8.59</v>
+      </c>
+      <c r="H8">
+        <v>103.3</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>24.8</v>
+      </c>
+      <c r="K8">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L8">
+        <v>16.7</v>
+      </c>
+      <c r="M8">
+        <v>1.0150884</v>
+      </c>
+      <c r="N8">
+        <v>15.6849116</v>
+      </c>
+      <c r="O8">
+        <v>3.607529668</v>
+      </c>
+      <c r="P8">
+        <v>12.077381932</v>
+      </c>
+      <c r="Q8">
+        <v>20.177381932</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1128361254510718</v>
+      </c>
+      <c r="T8">
+        <v>1.038172535250728</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.23</v>
+      </c>
+      <c r="W8">
+        <v>0.035189</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>16.45176912670857</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1079788819990174</v>
+      </c>
+      <c r="C9">
+        <v>306.4522716218952</v>
+      </c>
+      <c r="D9">
+        <v>323.7762716218952</v>
+      </c>
+      <c r="E9">
+        <v>-240.986</v>
+      </c>
+      <c r="F9">
+        <v>25.914</v>
+      </c>
+      <c r="G9">
+        <v>8.59</v>
+      </c>
+      <c r="H9">
+        <v>103.3</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>24.8</v>
+      </c>
+      <c r="K9">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L9">
+        <v>16.7</v>
+      </c>
+      <c r="M9">
+        <v>1.1842698</v>
+      </c>
+      <c r="N9">
+        <v>15.5157302</v>
+      </c>
+      <c r="O9">
+        <v>3.568617945999999</v>
+      </c>
+      <c r="P9">
+        <v>11.947112254</v>
+      </c>
+      <c r="Q9">
+        <v>20.047112254</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1134576903215241</v>
+      </c>
+      <c r="T9">
+        <v>1.046888436757577</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.23</v>
+      </c>
+      <c r="W9">
+        <v>0.035189</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>14.10151639432163</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1078790260740273</v>
+      </c>
+      <c r="C10">
+        <v>303.2183005002698</v>
+      </c>
+      <c r="D10">
+        <v>324.2443005002698</v>
+      </c>
+      <c r="E10">
+        <v>-237.284</v>
+      </c>
+      <c r="F10">
+        <v>29.616</v>
+      </c>
+      <c r="G10">
+        <v>8.59</v>
+      </c>
+      <c r="H10">
+        <v>103.3</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>24.8</v>
+      </c>
+      <c r="K10">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L10">
+        <v>16.7</v>
+      </c>
+      <c r="M10">
+        <v>1.4008368</v>
+      </c>
+      <c r="N10">
+        <v>15.2991632</v>
+      </c>
+      <c r="O10">
+        <v>3.518807535999999</v>
+      </c>
+      <c r="P10">
+        <v>11.780355664</v>
+      </c>
+      <c r="Q10">
+        <v>19.880355664</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1140927674717688</v>
+      </c>
+      <c r="T10">
+        <v>1.05579381438414</v>
+      </c>
+      <c r="U10">
+        <v>0.0473</v>
+      </c>
+      <c r="V10">
+        <v>0.23</v>
+      </c>
+      <c r="W10">
+        <v>0.036421</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>11.92144581010436</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1076929301490372</v>
+      </c>
+      <c r="C11">
+        <v>300.3921602277313</v>
+      </c>
+      <c r="D11">
+        <v>325.1201602277313</v>
+      </c>
+      <c r="E11">
+        <v>-233.582</v>
+      </c>
+      <c r="F11">
+        <v>33.318</v>
+      </c>
+      <c r="G11">
+        <v>8.59</v>
+      </c>
+      <c r="H11">
+        <v>103.3</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>24.8</v>
+      </c>
+      <c r="K11">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L11">
+        <v>16.7</v>
+      </c>
+      <c r="M11">
+        <v>1.5759414</v>
+      </c>
+      <c r="N11">
+        <v>15.1240586</v>
+      </c>
+      <c r="O11">
+        <v>3.478533478</v>
+      </c>
+      <c r="P11">
+        <v>11.645525122</v>
+      </c>
+      <c r="Q11">
+        <v>19.745525122</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1147418023615794</v>
+      </c>
+      <c r="T11">
+        <v>1.064894914595902</v>
+      </c>
+      <c r="U11">
+        <v>0.0473</v>
+      </c>
+      <c r="V11">
+        <v>0.23</v>
+      </c>
+      <c r="W11">
+        <v>0.036421</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>10.59684072009276</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1077994342240472</v>
+      </c>
+      <c r="C12">
+        <v>296.188321012359</v>
+      </c>
+      <c r="D12">
+        <v>324.618321012359</v>
+      </c>
+      <c r="E12">
+        <v>-229.88</v>
+      </c>
+      <c r="F12">
+        <v>37.02</v>
+      </c>
+      <c r="G12">
+        <v>8.59</v>
+      </c>
+      <c r="H12">
+        <v>103.3</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>24.8</v>
+      </c>
+      <c r="K12">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L12">
+        <v>16.7</v>
+      </c>
+      <c r="M12">
+        <v>1.891722</v>
+      </c>
+      <c r="N12">
+        <v>14.808278</v>
+      </c>
+      <c r="O12">
+        <v>3.40590394</v>
+      </c>
+      <c r="P12">
+        <v>11.40237406</v>
+      </c>
+      <c r="Q12">
+        <v>19.50237406</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1154052602489413</v>
+      </c>
+      <c r="T12">
+        <v>1.074198261479037</v>
+      </c>
+      <c r="U12">
+        <v>0.0511</v>
+      </c>
+      <c r="V12">
+        <v>0.23</v>
+      </c>
+      <c r="W12">
+        <v>0.039347</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>8.827935605760253</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1076425982990571</v>
+      </c>
+      <c r="C13">
+        <v>293.2258604240403</v>
+      </c>
+      <c r="D13">
+        <v>325.3578604240403</v>
+      </c>
+      <c r="E13">
+        <v>-226.178</v>
+      </c>
+      <c r="F13">
+        <v>40.722</v>
+      </c>
+      <c r="G13">
+        <v>8.59</v>
+      </c>
+      <c r="H13">
+        <v>103.3</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>24.8</v>
+      </c>
+      <c r="K13">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L13">
+        <v>16.7</v>
+      </c>
+      <c r="M13">
+        <v>2.0808942</v>
+      </c>
+      <c r="N13">
+        <v>14.6191058</v>
+      </c>
+      <c r="O13">
+        <v>3.362394334</v>
+      </c>
+      <c r="P13">
+        <v>11.256711466</v>
+      </c>
+      <c r="Q13">
+        <v>19.356711466</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1160836273023113</v>
+      </c>
+      <c r="T13">
+        <v>1.083710672337074</v>
+      </c>
+      <c r="U13">
+        <v>0.0511</v>
+      </c>
+      <c r="V13">
+        <v>0.23</v>
+      </c>
+      <c r="W13">
+        <v>0.039347</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>8.025396005236594</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.107661322374067</v>
+      </c>
+      <c r="C14">
+        <v>289.4353924020272</v>
+      </c>
+      <c r="D14">
+        <v>325.2693924020272</v>
+      </c>
+      <c r="E14">
+        <v>-222.476</v>
+      </c>
+      <c r="F14">
+        <v>44.424</v>
+      </c>
+      <c r="G14">
+        <v>8.59</v>
+      </c>
+      <c r="H14">
+        <v>103.3</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>24.8</v>
+      </c>
+      <c r="K14">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L14">
+        <v>16.7</v>
+      </c>
+      <c r="M14">
+        <v>2.354472</v>
+      </c>
+      <c r="N14">
+        <v>14.345528</v>
+      </c>
+      <c r="O14">
+        <v>3.299471439999999</v>
+      </c>
+      <c r="P14">
+        <v>11.04605656</v>
+      </c>
+      <c r="Q14">
+        <v>19.14605656</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1167774117887125</v>
+      </c>
+      <c r="T14">
+        <v>1.093439274350975</v>
+      </c>
+      <c r="U14">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V14">
+        <v>0.23</v>
+      </c>
+      <c r="W14">
+        <v>0.04081000000000001</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>7.09288536877907</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1075191164490769</v>
+      </c>
+      <c r="C15">
+        <v>286.4064981869622</v>
+      </c>
+      <c r="D15">
+        <v>325.9424981869622</v>
+      </c>
+      <c r="E15">
+        <v>-218.774</v>
+      </c>
+      <c r="F15">
+        <v>48.126</v>
+      </c>
+      <c r="G15">
+        <v>8.59</v>
+      </c>
+      <c r="H15">
+        <v>103.3</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>24.8</v>
+      </c>
+      <c r="K15">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L15">
+        <v>16.7</v>
+      </c>
+      <c r="M15">
+        <v>2.550678</v>
+      </c>
+      <c r="N15">
+        <v>14.149322</v>
+      </c>
+      <c r="O15">
+        <v>3.25434406</v>
+      </c>
+      <c r="P15">
+        <v>10.89497794</v>
+      </c>
+      <c r="Q15">
+        <v>18.99497794</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1174871453437666</v>
+      </c>
+      <c r="T15">
+        <v>1.103391522388184</v>
+      </c>
+      <c r="U15">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V15">
+        <v>0.23</v>
+      </c>
+      <c r="W15">
+        <v>0.04081000000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>6.547278801949913</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1075925105240868</v>
+      </c>
+      <c r="C16">
+        <v>282.356753236551</v>
+      </c>
+      <c r="D16">
+        <v>325.594753236551</v>
+      </c>
+      <c r="E16">
+        <v>-215.072</v>
+      </c>
+      <c r="F16">
+        <v>51.828</v>
+      </c>
+      <c r="G16">
+        <v>8.59</v>
+      </c>
+      <c r="H16">
+        <v>103.3</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>24.8</v>
+      </c>
+      <c r="K16">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L16">
+        <v>16.7</v>
+      </c>
+      <c r="M16">
+        <v>2.85054</v>
+      </c>
+      <c r="N16">
+        <v>13.84946</v>
+      </c>
+      <c r="O16">
+        <v>3.1853758</v>
+      </c>
+      <c r="P16">
+        <v>10.6640842</v>
+      </c>
+      <c r="Q16">
+        <v>18.7640842</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1182133843303335</v>
+      </c>
+      <c r="T16">
+        <v>1.113575218054165</v>
+      </c>
+      <c r="U16">
+        <v>0.055</v>
+      </c>
+      <c r="V16">
+        <v>0.23</v>
+      </c>
+      <c r="W16">
+        <v>0.04235</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>5.858539083822714</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1074657045990968</v>
+      </c>
+      <c r="C17">
+        <v>279.2560336588103</v>
+      </c>
+      <c r="D17">
+        <v>326.1960336588103</v>
+      </c>
+      <c r="E17">
+        <v>-211.37</v>
+      </c>
+      <c r="F17">
+        <v>55.52999999999999</v>
+      </c>
+      <c r="G17">
+        <v>8.59</v>
+      </c>
+      <c r="H17">
+        <v>103.3</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>24.8</v>
+      </c>
+      <c r="K17">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L17">
+        <v>16.7</v>
+      </c>
+      <c r="M17">
+        <v>3.054149999999999</v>
+      </c>
+      <c r="N17">
+        <v>13.64585</v>
+      </c>
+      <c r="O17">
+        <v>3.1385455</v>
+      </c>
+      <c r="P17">
+        <v>10.5073045</v>
+      </c>
+      <c r="Q17">
+        <v>18.6073045</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.118956711293055</v>
+      </c>
+      <c r="T17">
+        <v>1.123998530088758</v>
+      </c>
+      <c r="U17">
+        <v>0.055</v>
+      </c>
+      <c r="V17">
+        <v>0.23</v>
+      </c>
+      <c r="W17">
+        <v>0.04235</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>5.467969811567867</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1073388986741067</v>
+      </c>
+      <c r="C18">
+        <v>276.157538975884</v>
+      </c>
+      <c r="D18">
+        <v>326.799538975884</v>
+      </c>
+      <c r="E18">
+        <v>-207.668</v>
+      </c>
+      <c r="F18">
+        <v>59.232</v>
+      </c>
+      <c r="G18">
+        <v>8.59</v>
+      </c>
+      <c r="H18">
+        <v>103.3</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>24.8</v>
+      </c>
+      <c r="K18">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L18">
+        <v>16.7</v>
+      </c>
+      <c r="M18">
+        <v>3.25776</v>
+      </c>
+      <c r="N18">
+        <v>13.44224</v>
+      </c>
+      <c r="O18">
+        <v>3.0917152</v>
+      </c>
+      <c r="P18">
+        <v>10.3505248</v>
+      </c>
+      <c r="Q18">
+        <v>18.4505248</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1197177365167937</v>
+      </c>
+      <c r="T18">
+        <v>1.134670016219413</v>
+      </c>
+      <c r="U18">
+        <v>0.055</v>
+      </c>
+      <c r="V18">
+        <v>0.23</v>
+      </c>
+      <c r="W18">
+        <v>0.04235</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>5.126221698344875</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1072120927491166</v>
+      </c>
+      <c r="C19">
+        <v>273.0612815597008</v>
+      </c>
+      <c r="D19">
+        <v>327.4052815597009</v>
+      </c>
+      <c r="E19">
+        <v>-203.966</v>
+      </c>
+      <c r="F19">
+        <v>62.934</v>
+      </c>
+      <c r="G19">
+        <v>8.59</v>
+      </c>
+      <c r="H19">
+        <v>103.3</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>24.8</v>
+      </c>
+      <c r="K19">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L19">
+        <v>16.7</v>
+      </c>
+      <c r="M19">
+        <v>3.46137</v>
+      </c>
+      <c r="N19">
+        <v>13.23863</v>
+      </c>
+      <c r="O19">
+        <v>3.0448849</v>
+      </c>
+      <c r="P19">
+        <v>10.1937451</v>
+      </c>
+      <c r="Q19">
+        <v>18.2937451</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1204970996977308</v>
+      </c>
+      <c r="T19">
+        <v>1.145598646594179</v>
+      </c>
+      <c r="U19">
+        <v>0.055</v>
+      </c>
+      <c r="V19">
+        <v>0.23</v>
+      </c>
+      <c r="W19">
+        <v>0.04235</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>4.824679245501058</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1070852868241265</v>
+      </c>
+      <c r="C20">
+        <v>269.9672738740883</v>
+      </c>
+      <c r="D20">
+        <v>328.0132738740883</v>
+      </c>
+      <c r="E20">
+        <v>-200.264</v>
+      </c>
+      <c r="F20">
+        <v>66.636</v>
+      </c>
+      <c r="G20">
+        <v>8.59</v>
+      </c>
+      <c r="H20">
+        <v>103.3</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>24.8</v>
+      </c>
+      <c r="K20">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L20">
+        <v>16.7</v>
+      </c>
+      <c r="M20">
+        <v>3.66498</v>
+      </c>
+      <c r="N20">
+        <v>13.03502</v>
+      </c>
+      <c r="O20">
+        <v>2.9980546</v>
+      </c>
+      <c r="P20">
+        <v>10.0369654</v>
+      </c>
+      <c r="Q20">
+        <v>18.1369654</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1212954717367397</v>
+      </c>
+      <c r="T20">
+        <v>1.156793828929306</v>
+      </c>
+      <c r="U20">
+        <v>0.055</v>
+      </c>
+      <c r="V20">
+        <v>0.23</v>
+      </c>
+      <c r="W20">
+        <v>0.04235</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>4.556641509639888</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1075144208991364</v>
+      </c>
+      <c r="C21">
+        <v>264.2167712303485</v>
+      </c>
+      <c r="D21">
+        <v>325.9647712303486</v>
+      </c>
+      <c r="E21">
+        <v>-196.562</v>
+      </c>
+      <c r="F21">
+        <v>70.33799999999999</v>
+      </c>
+      <c r="G21">
+        <v>8.59</v>
+      </c>
+      <c r="H21">
+        <v>103.3</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>24.8</v>
+      </c>
+      <c r="K21">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L21">
+        <v>16.7</v>
+      </c>
+      <c r="M21">
+        <v>4.1358744</v>
+      </c>
+      <c r="N21">
+        <v>12.5641256</v>
+      </c>
+      <c r="O21">
+        <v>2.889748888</v>
+      </c>
+      <c r="P21">
+        <v>9.674376712000001</v>
+      </c>
+      <c r="Q21">
+        <v>17.774376712</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1221135566656005</v>
+      </c>
+      <c r="T21">
+        <v>1.168265435519621</v>
+      </c>
+      <c r="U21">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V21">
+        <v>0.23</v>
+      </c>
+      <c r="W21">
+        <v>0.045276</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>4.037840220679816</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1080636749741463</v>
+      </c>
+      <c r="C22">
+        <v>257.9299029140952</v>
+      </c>
+      <c r="D22">
+        <v>323.3799029140952</v>
+      </c>
+      <c r="E22">
+        <v>-192.86</v>
+      </c>
+      <c r="F22">
+        <v>74.04000000000001</v>
+      </c>
+      <c r="G22">
+        <v>8.59</v>
+      </c>
+      <c r="H22">
+        <v>103.3</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>24.8</v>
+      </c>
+      <c r="K22">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L22">
+        <v>16.7</v>
+      </c>
+      <c r="M22">
+        <v>4.66452</v>
+      </c>
+      <c r="N22">
+        <v>12.03548</v>
+      </c>
+      <c r="O22">
+        <v>2.7681604</v>
+      </c>
+      <c r="P22">
+        <v>9.2673196</v>
+      </c>
+      <c r="Q22">
+        <v>17.3673196</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1229520937176829</v>
+      </c>
+      <c r="T22">
+        <v>1.180023832274694</v>
+      </c>
+      <c r="U22">
+        <v>0.063</v>
+      </c>
+      <c r="V22">
+        <v>0.23</v>
+      </c>
+      <c r="W22">
+        <v>0.04851</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>3.580218329002769</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1091465390491563</v>
+      </c>
+      <c r="C23">
+        <v>249.2500250514589</v>
+      </c>
+      <c r="D23">
+        <v>318.402025051459</v>
+      </c>
+      <c r="E23">
+        <v>-189.158</v>
+      </c>
+      <c r="F23">
+        <v>77.74199999999999</v>
+      </c>
+      <c r="G23">
+        <v>8.59</v>
+      </c>
+      <c r="H23">
+        <v>103.3</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>24.8</v>
+      </c>
+      <c r="K23">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L23">
+        <v>16.7</v>
+      </c>
+      <c r="M23">
+        <v>5.449714199999999</v>
+      </c>
+      <c r="N23">
+        <v>11.2502858</v>
+      </c>
+      <c r="O23">
+        <v>2.587565734</v>
+      </c>
+      <c r="P23">
+        <v>8.662720066</v>
+      </c>
+      <c r="Q23">
+        <v>16.762720066</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.123811859555894</v>
+      </c>
+      <c r="T23">
+        <v>1.192079909960276</v>
+      </c>
+      <c r="U23">
+        <v>0.0701</v>
+      </c>
+      <c r="V23">
+        <v>0.23</v>
+      </c>
+      <c r="W23">
+        <v>0.053977</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>3.064380880744169</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1127442231241662</v>
+      </c>
+      <c r="C24">
+        <v>230.0564849881463</v>
+      </c>
+      <c r="D24">
+        <v>302.9104849881464</v>
+      </c>
+      <c r="E24">
+        <v>-185.456</v>
+      </c>
+      <c r="F24">
+        <v>81.444</v>
+      </c>
+      <c r="G24">
+        <v>8.59</v>
+      </c>
+      <c r="H24">
+        <v>103.3</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>24.8</v>
+      </c>
+      <c r="K24">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L24">
+        <v>16.7</v>
+      </c>
+      <c r="M24">
+        <v>7.443981600000001</v>
+      </c>
+      <c r="N24">
+        <v>9.256018399999999</v>
+      </c>
+      <c r="O24">
+        <v>2.128884231999999</v>
+      </c>
+      <c r="P24">
+        <v>7.127134168</v>
+      </c>
+      <c r="Q24">
+        <v>15.227134168</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1246936706720079</v>
+      </c>
+      <c r="T24">
+        <v>1.204445117842923</v>
+      </c>
+      <c r="U24">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V24">
+        <v>0.23</v>
+      </c>
+      <c r="W24">
+        <v>0.07037800000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>2.243423062732987</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1128976971991761</v>
+      </c>
+      <c r="C25">
+        <v>225.7270848360283</v>
+      </c>
+      <c r="D25">
+        <v>302.2830848360284</v>
+      </c>
+      <c r="E25">
+        <v>-181.754</v>
+      </c>
+      <c r="F25">
+        <v>85.146</v>
+      </c>
+      <c r="G25">
+        <v>8.59</v>
+      </c>
+      <c r="H25">
+        <v>103.3</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>24.8</v>
+      </c>
+      <c r="K25">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L25">
+        <v>16.7</v>
+      </c>
+      <c r="M25">
+        <v>7.782344400000001</v>
+      </c>
+      <c r="N25">
+        <v>8.917655599999998</v>
+      </c>
+      <c r="O25">
+        <v>2.051060788</v>
+      </c>
+      <c r="P25">
+        <v>6.866594811999999</v>
+      </c>
+      <c r="Q25">
+        <v>14.966594812</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.125598385972956</v>
+      </c>
+      <c r="T25">
+        <v>1.217131499956289</v>
+      </c>
+      <c r="U25">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V25">
+        <v>0.23</v>
+      </c>
+      <c r="W25">
+        <v>0.07037800000000001</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>2.145882929570683</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.113051171274186</v>
+      </c>
+      <c r="C26">
+        <v>221.4002783038183</v>
+      </c>
+      <c r="D26">
+        <v>301.6582783038183</v>
+      </c>
+      <c r="E26">
+        <v>-178.052</v>
+      </c>
+      <c r="F26">
+        <v>88.848</v>
+      </c>
+      <c r="G26">
+        <v>8.59</v>
+      </c>
+      <c r="H26">
+        <v>103.3</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>24.8</v>
+      </c>
+      <c r="K26">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L26">
+        <v>16.7</v>
+      </c>
+      <c r="M26">
+        <v>8.1207072</v>
+      </c>
+      <c r="N26">
+        <v>8.579292799999999</v>
+      </c>
+      <c r="O26">
+        <v>1.973237344</v>
+      </c>
+      <c r="P26">
+        <v>6.606055456</v>
+      </c>
+      <c r="Q26">
+        <v>14.706055456</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1265269095712974</v>
+      </c>
+      <c r="T26">
+        <v>1.230151734230532</v>
+      </c>
+      <c r="U26">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V26">
+        <v>0.23</v>
+      </c>
+      <c r="W26">
+        <v>0.07037800000000001</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>2.056471140838571</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.117266395349196</v>
+      </c>
+      <c r="C27">
+        <v>201.4931597753892</v>
+      </c>
+      <c r="D27">
+        <v>285.4531597753892</v>
+      </c>
+      <c r="E27">
+        <v>-174.35</v>
+      </c>
+      <c r="F27">
+        <v>92.55</v>
+      </c>
+      <c r="G27">
+        <v>8.59</v>
+      </c>
+      <c r="H27">
+        <v>103.3</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>24.8</v>
+      </c>
+      <c r="K27">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L27">
+        <v>16.7</v>
+      </c>
+      <c r="M27">
+        <v>10.411875</v>
+      </c>
+      <c r="N27">
+        <v>6.288124999999999</v>
+      </c>
+      <c r="O27">
+        <v>1.44626875</v>
+      </c>
+      <c r="P27">
+        <v>4.841856249999999</v>
+      </c>
+      <c r="Q27">
+        <v>12.94185625</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1274801937989279</v>
+      </c>
+      <c r="T27">
+        <v>1.243519174752089</v>
+      </c>
+      <c r="U27">
+        <v>0.1125</v>
+      </c>
+      <c r="V27">
+        <v>0.23</v>
+      </c>
+      <c r="W27">
+        <v>0.08662500000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>1.603937811393241</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1175823394242059</v>
+      </c>
+      <c r="C28">
+        <v>196.646395159575</v>
+      </c>
+      <c r="D28">
+        <v>284.3083951595751</v>
+      </c>
+      <c r="E28">
+        <v>-170.648</v>
+      </c>
+      <c r="F28">
+        <v>96.252</v>
+      </c>
+      <c r="G28">
+        <v>8.59</v>
+      </c>
+      <c r="H28">
+        <v>103.3</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>24.8</v>
+      </c>
+      <c r="K28">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L28">
+        <v>16.7</v>
+      </c>
+      <c r="M28">
+        <v>10.82835</v>
+      </c>
+      <c r="N28">
+        <v>5.871649999999999</v>
+      </c>
+      <c r="O28">
+        <v>1.3504795</v>
+      </c>
+      <c r="P28">
+        <v>4.521170499999999</v>
+      </c>
+      <c r="Q28">
+        <v>12.6211705</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1284592424651431</v>
+      </c>
+      <c r="T28">
+        <v>1.257247897449904</v>
+      </c>
+      <c r="U28">
+        <v>0.1125</v>
+      </c>
+      <c r="V28">
+        <v>0.23</v>
+      </c>
+      <c r="W28">
+        <v>0.08662500000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>1.542247895570424</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1378741385798977</v>
+      </c>
+      <c r="C29">
+        <v>134.7139736232556</v>
+      </c>
+      <c r="D29">
+        <v>226.0779736232556</v>
+      </c>
+      <c r="E29">
+        <v>-166.946</v>
+      </c>
+      <c r="F29">
+        <v>99.95400000000001</v>
+      </c>
+      <c r="G29">
+        <v>8.59</v>
+      </c>
+      <c r="H29">
+        <v>103.3</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>24.8</v>
+      </c>
+      <c r="K29">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L29">
+        <v>16.7</v>
+      </c>
+      <c r="M29">
+        <v>19.6509564</v>
+      </c>
+      <c r="N29">
+        <v>-2.950956400000003</v>
+      </c>
+      <c r="O29">
+        <v>-0.6787199720000006</v>
+      </c>
+      <c r="P29">
+        <v>-2.272236428000002</v>
+      </c>
+      <c r="Q29">
+        <v>5.827763571999999</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1303665908182846</v>
+      </c>
+      <c r="T29">
+        <v>1.283993714621224</v>
+      </c>
+      <c r="U29">
+        <v>0.1966</v>
+      </c>
+      <c r="V29">
+        <v>0.1954612244725147</v>
+      </c>
+      <c r="W29">
+        <v>0.1581723232687036</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.849831410750064</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1394521385798977</v>
+      </c>
+      <c r="C30">
+        <v>127.4675775735452</v>
+      </c>
+      <c r="D30">
+        <v>222.5335775735452</v>
+      </c>
+      <c r="E30">
+        <v>-163.244</v>
+      </c>
+      <c r="F30">
+        <v>103.656</v>
+      </c>
+      <c r="G30">
+        <v>8.59</v>
+      </c>
+      <c r="H30">
+        <v>103.3</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>24.8</v>
+      </c>
+      <c r="K30">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L30">
+        <v>16.7</v>
+      </c>
+      <c r="M30">
+        <v>20.3787696</v>
+      </c>
+      <c r="N30">
+        <v>-3.678769600000003</v>
+      </c>
+      <c r="O30">
+        <v>-0.8461170080000006</v>
+      </c>
+      <c r="P30">
+        <v>-2.832652592000002</v>
+      </c>
+      <c r="Q30">
+        <v>5.267347407999999</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1316383490240942</v>
+      </c>
+      <c r="T30">
+        <v>1.30182696065763</v>
+      </c>
+      <c r="U30">
+        <v>0.1966</v>
+      </c>
+      <c r="V30">
+        <v>0.1884804664556392</v>
+      </c>
+      <c r="W30">
+        <v>0.1595447402948213</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.8194802889375616</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1463177453780153</v>
+      </c>
+      <c r="C31">
+        <v>109.5555693779051</v>
+      </c>
+      <c r="D31">
+        <v>208.3235693779051</v>
+      </c>
+      <c r="E31">
+        <v>-159.542</v>
+      </c>
+      <c r="F31">
+        <v>107.358</v>
+      </c>
+      <c r="G31">
+        <v>8.59</v>
+      </c>
+      <c r="H31">
+        <v>103.3</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>24.8</v>
+      </c>
+      <c r="K31">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L31">
+        <v>16.7</v>
+      </c>
+      <c r="M31">
+        <v>22.9531404</v>
+      </c>
+      <c r="N31">
+        <v>-6.253140399999996</v>
+      </c>
+      <c r="O31">
+        <v>-1.438222291999999</v>
+      </c>
+      <c r="P31">
+        <v>-4.814918107999997</v>
+      </c>
+      <c r="Q31">
+        <v>3.285081892000004</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1333679128105145</v>
+      </c>
+      <c r="T31">
+        <v>1.326079791422153</v>
+      </c>
+      <c r="U31">
+        <v>0.2138</v>
+      </c>
+      <c r="V31">
+        <v>0.1673409360577083</v>
+      </c>
+      <c r="W31">
+        <v>0.178022507870862</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.7275692872074273</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1480677453780153</v>
+      </c>
+      <c r="C32">
+        <v>102.5171205004243</v>
+      </c>
+      <c r="D32">
+        <v>204.9871205004243</v>
+      </c>
+      <c r="E32">
+        <v>-155.84</v>
+      </c>
+      <c r="F32">
+        <v>111.06</v>
+      </c>
+      <c r="G32">
+        <v>8.59</v>
+      </c>
+      <c r="H32">
+        <v>103.3</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>24.8</v>
+      </c>
+      <c r="K32">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L32">
+        <v>16.7</v>
+      </c>
+      <c r="M32">
+        <v>23.744628</v>
+      </c>
+      <c r="N32">
+        <v>-7.044627999999996</v>
+      </c>
+      <c r="O32">
+        <v>-1.620264439999999</v>
+      </c>
+      <c r="P32">
+        <v>-5.424363559999997</v>
+      </c>
+      <c r="Q32">
+        <v>2.675636440000004</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1347188829935218</v>
+      </c>
+      <c r="T32">
+        <v>1.34502378844247</v>
+      </c>
+      <c r="U32">
+        <v>0.2138</v>
+      </c>
+      <c r="V32">
+        <v>0.1617629048557847</v>
+      </c>
+      <c r="W32">
+        <v>0.1792150909418332</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.7033169776338464</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1498177453780153</v>
+      </c>
+      <c r="C33">
+        <v>95.58385814993898</v>
+      </c>
+      <c r="D33">
+        <v>201.755858149939</v>
+      </c>
+      <c r="E33">
+        <v>-152.138</v>
+      </c>
+      <c r="F33">
+        <v>114.762</v>
+      </c>
+      <c r="G33">
+        <v>8.59</v>
+      </c>
+      <c r="H33">
+        <v>103.3</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>24.8</v>
+      </c>
+      <c r="K33">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L33">
+        <v>16.7</v>
+      </c>
+      <c r="M33">
+        <v>24.5361156</v>
+      </c>
+      <c r="N33">
+        <v>-7.836115599999999</v>
+      </c>
+      <c r="O33">
+        <v>-1.802306588</v>
+      </c>
+      <c r="P33">
+        <v>-6.033809012</v>
+      </c>
+      <c r="Q33">
+        <v>2.066190988000002</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1361090117325584</v>
+      </c>
+      <c r="T33">
+        <v>1.364516886825694</v>
+      </c>
+      <c r="U33">
+        <v>0.2138</v>
+      </c>
+      <c r="V33">
+        <v>0.1565447466346303</v>
+      </c>
+      <c r="W33">
+        <v>0.180330733169516</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.6806293331940447</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1515677453780153</v>
+      </c>
+      <c r="C34">
+        <v>88.75088527663345</v>
+      </c>
+      <c r="D34">
+        <v>198.6248852766334</v>
+      </c>
+      <c r="E34">
+        <v>-148.436</v>
+      </c>
+      <c r="F34">
+        <v>118.464</v>
+      </c>
+      <c r="G34">
+        <v>8.59</v>
+      </c>
+      <c r="H34">
+        <v>103.3</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>24.8</v>
+      </c>
+      <c r="K34">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L34">
+        <v>16.7</v>
+      </c>
+      <c r="M34">
+        <v>25.3276032</v>
+      </c>
+      <c r="N34">
+        <v>-8.627603199999999</v>
+      </c>
+      <c r="O34">
+        <v>-1.984348736</v>
+      </c>
+      <c r="P34">
+        <v>-6.643254464</v>
+      </c>
+      <c r="Q34">
+        <v>1.456745536000001</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1375400266109784</v>
+      </c>
+      <c r="T34">
+        <v>1.384583311631954</v>
+      </c>
+      <c r="U34">
+        <v>0.2138</v>
+      </c>
+      <c r="V34">
+        <v>0.1516527233022981</v>
+      </c>
+      <c r="W34">
+        <v>0.1813766477579687</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.6593596665317309</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1533177453780153</v>
+      </c>
+      <c r="C35">
+        <v>82.01360416725842</v>
+      </c>
+      <c r="D35">
+        <v>195.5896041672584</v>
+      </c>
+      <c r="E35">
+        <v>-144.734</v>
+      </c>
+      <c r="F35">
+        <v>122.166</v>
+      </c>
+      <c r="G35">
+        <v>8.59</v>
+      </c>
+      <c r="H35">
+        <v>103.3</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>24.8</v>
+      </c>
+      <c r="K35">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L35">
+        <v>16.7</v>
+      </c>
+      <c r="M35">
+        <v>26.1190908</v>
+      </c>
+      <c r="N35">
+        <v>-9.419090799999999</v>
+      </c>
+      <c r="O35">
+        <v>-2.166390884</v>
+      </c>
+      <c r="P35">
+        <v>-7.252699915999999</v>
+      </c>
+      <c r="Q35">
+        <v>0.8473000840000022</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1390137583514408</v>
+      </c>
+      <c r="T35">
+        <v>1.405248734193625</v>
+      </c>
+      <c r="U35">
+        <v>0.2138</v>
+      </c>
+      <c r="V35">
+        <v>0.1470571862325315</v>
+      </c>
+      <c r="W35">
+        <v>0.1823591735834847</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.6393790705762239</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1550677453780153</v>
+      </c>
+      <c r="C36">
+        <v>75.36769391786071</v>
+      </c>
+      <c r="D36">
+        <v>192.6456939178607</v>
+      </c>
+      <c r="E36">
+        <v>-141.032</v>
+      </c>
+      <c r="F36">
+        <v>125.868</v>
+      </c>
+      <c r="G36">
+        <v>8.59</v>
+      </c>
+      <c r="H36">
+        <v>103.3</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>24.8</v>
+      </c>
+      <c r="K36">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L36">
+        <v>16.7</v>
+      </c>
+      <c r="M36">
+        <v>26.9105784</v>
+      </c>
+      <c r="N36">
+        <v>-10.2105784</v>
+      </c>
+      <c r="O36">
+        <v>-2.348433032</v>
+      </c>
+      <c r="P36">
+        <v>-7.862145368000002</v>
+      </c>
+      <c r="Q36">
+        <v>0.2378546319999995</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1405321486294929</v>
+      </c>
+      <c r="T36">
+        <v>1.426540381681407</v>
+      </c>
+      <c r="U36">
+        <v>0.2138</v>
+      </c>
+      <c r="V36">
+        <v>0.1427319748727511</v>
+      </c>
+      <c r="W36">
+        <v>0.1832839037722058</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.6205738037945702</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1568177453780152</v>
+      </c>
+      <c r="C37">
+        <v>68.8090899107564</v>
+      </c>
+      <c r="D37">
+        <v>189.7890899107564</v>
+      </c>
+      <c r="E37">
+        <v>-137.33</v>
+      </c>
+      <c r="F37">
+        <v>129.57</v>
+      </c>
+      <c r="G37">
+        <v>8.59</v>
+      </c>
+      <c r="H37">
+        <v>103.3</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>24.8</v>
+      </c>
+      <c r="K37">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L37">
+        <v>16.7</v>
+      </c>
+      <c r="M37">
+        <v>27.702066</v>
+      </c>
+      <c r="N37">
+        <v>-11.002066</v>
+      </c>
+      <c r="O37">
+        <v>-2.53047518</v>
+      </c>
+      <c r="P37">
+        <v>-8.471590820000003</v>
+      </c>
+      <c r="Q37">
+        <v>-0.3715908200000015</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1420972586084081</v>
+      </c>
+      <c r="T37">
+        <v>1.448487156784198</v>
+      </c>
+      <c r="U37">
+        <v>0.2138</v>
+      </c>
+      <c r="V37">
+        <v>0.1386539184478154</v>
+      </c>
+      <c r="W37">
+        <v>0.1841557922358571</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.6028431236861539</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1585677453780153</v>
+      </c>
+      <c r="C38">
+        <v>62.33396509075129</v>
+      </c>
+      <c r="D38">
+        <v>187.0159650907513</v>
+      </c>
+      <c r="E38">
+        <v>-133.628</v>
+      </c>
+      <c r="F38">
+        <v>133.272</v>
+      </c>
+      <c r="G38">
+        <v>8.59</v>
+      </c>
+      <c r="H38">
+        <v>103.3</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>24.8</v>
+      </c>
+      <c r="K38">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L38">
+        <v>16.7</v>
+      </c>
+      <c r="M38">
+        <v>28.4935536</v>
+      </c>
+      <c r="N38">
+        <v>-11.7935536</v>
+      </c>
+      <c r="O38">
+        <v>-2.712517328</v>
+      </c>
+      <c r="P38">
+        <v>-9.081036271999999</v>
+      </c>
+      <c r="Q38">
+        <v>-0.9810362719999972</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1437112782741645</v>
+      </c>
+      <c r="T38">
+        <v>1.471119768608951</v>
+      </c>
+      <c r="U38">
+        <v>0.2138</v>
+      </c>
+      <c r="V38">
+        <v>0.1348024207131539</v>
+      </c>
+      <c r="W38">
+        <v>0.1849792424515277</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.5860974813615385</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1603177453780152</v>
+      </c>
+      <c r="C39">
+        <v>55.93871285922972</v>
+      </c>
+      <c r="D39">
+        <v>184.3227128592297</v>
+      </c>
+      <c r="E39">
+        <v>-129.926</v>
+      </c>
+      <c r="F39">
+        <v>136.974</v>
+      </c>
+      <c r="G39">
+        <v>8.59</v>
+      </c>
+      <c r="H39">
+        <v>103.3</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>24.8</v>
+      </c>
+      <c r="K39">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L39">
+        <v>16.7</v>
+      </c>
+      <c r="M39">
+        <v>29.28504119999999</v>
+      </c>
+      <c r="N39">
+        <v>-12.5850412</v>
+      </c>
+      <c r="O39">
+        <v>-2.894559475999999</v>
+      </c>
+      <c r="P39">
+        <v>-9.690481723999998</v>
+      </c>
+      <c r="Q39">
+        <v>-1.590481723999996</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1453765366594687</v>
+      </c>
+      <c r="T39">
+        <v>1.494470876047189</v>
+      </c>
+      <c r="U39">
+        <v>0.2138</v>
+      </c>
+      <c r="V39">
+        <v>0.1311591120452308</v>
+      </c>
+      <c r="W39">
+        <v>0.1857581818447296</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.5702570088923078</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1620677453780153</v>
+      </c>
+      <c r="C40">
+        <v>49.61993142533171</v>
+      </c>
+      <c r="D40">
+        <v>181.7059314253317</v>
+      </c>
+      <c r="E40">
+        <v>-126.224</v>
+      </c>
+      <c r="F40">
+        <v>140.676</v>
+      </c>
+      <c r="G40">
+        <v>8.59</v>
+      </c>
+      <c r="H40">
+        <v>103.3</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>24.8</v>
+      </c>
+      <c r="K40">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L40">
+        <v>16.7</v>
+      </c>
+      <c r="M40">
+        <v>30.07652879999999</v>
+      </c>
+      <c r="N40">
+        <v>-13.3765288</v>
+      </c>
+      <c r="O40">
+        <v>-3.076601623999999</v>
+      </c>
+      <c r="P40">
+        <v>-10.299927176</v>
+      </c>
+      <c r="Q40">
+        <v>-2.199927175999996</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1470955130572021</v>
+      </c>
+      <c r="T40">
+        <v>1.518575245015692</v>
+      </c>
+      <c r="U40">
+        <v>0.2138</v>
+      </c>
+      <c r="V40">
+        <v>0.1277075564650932</v>
+      </c>
+      <c r="W40">
+        <v>0.1864961244277631</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.555250245500405</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1638177453780152</v>
+      </c>
+      <c r="C41">
+        <v>43.3744094714456</v>
+      </c>
+      <c r="D41">
+        <v>179.1624094714456</v>
+      </c>
+      <c r="E41">
+        <v>-122.522</v>
+      </c>
+      <c r="F41">
+        <v>144.378</v>
+      </c>
+      <c r="G41">
+        <v>8.59</v>
+      </c>
+      <c r="H41">
+        <v>103.3</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>24.8</v>
+      </c>
+      <c r="K41">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L41">
+        <v>16.7</v>
+      </c>
+      <c r="M41">
+        <v>30.8680164</v>
+      </c>
+      <c r="N41">
+        <v>-14.1680164</v>
+      </c>
+      <c r="O41">
+        <v>-3.258643772000001</v>
+      </c>
+      <c r="P41">
+        <v>-10.909372628</v>
+      </c>
+      <c r="Q41">
+        <v>-2.809372628</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1488708493368283</v>
+      </c>
+      <c r="T41">
+        <v>1.54346992116349</v>
+      </c>
+      <c r="U41">
+        <v>0.2138</v>
+      </c>
+      <c r="V41">
+        <v>0.1244330037352189</v>
+      </c>
+      <c r="W41">
+        <v>0.1871962238014102</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.5410130597183432</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1655677453780152</v>
+      </c>
+      <c r="C42">
+        <v>37.19911300600725</v>
+      </c>
+      <c r="D42">
+        <v>176.6891130060073</v>
+      </c>
+      <c r="E42">
+        <v>-118.82</v>
+      </c>
+      <c r="F42">
+        <v>148.08</v>
+      </c>
+      <c r="G42">
+        <v>8.59</v>
+      </c>
+      <c r="H42">
+        <v>103.3</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>24.8</v>
+      </c>
+      <c r="K42">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L42">
+        <v>16.7</v>
+      </c>
+      <c r="M42">
+        <v>31.659504</v>
+      </c>
+      <c r="N42">
+        <v>-14.959504</v>
+      </c>
+      <c r="O42">
+        <v>-3.44068592</v>
+      </c>
+      <c r="P42">
+        <v>-11.51881808</v>
+      </c>
+      <c r="Q42">
+        <v>-3.418818080000001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1507053634924421</v>
+      </c>
+      <c r="T42">
+        <v>1.569194419849548</v>
+      </c>
+      <c r="U42">
+        <v>0.2138</v>
+      </c>
+      <c r="V42">
+        <v>0.1213221786418385</v>
+      </c>
+      <c r="W42">
+        <v>0.1878613182063749</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.5274877332253847</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1673177453780152</v>
+      </c>
+      <c r="C43">
+        <v>31.09117329043698</v>
+      </c>
+      <c r="D43">
+        <v>174.283173290437</v>
+      </c>
+      <c r="E43">
+        <v>-115.118</v>
+      </c>
+      <c r="F43">
+        <v>151.782</v>
+      </c>
+      <c r="G43">
+        <v>8.59</v>
+      </c>
+      <c r="H43">
+        <v>103.3</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>24.8</v>
+      </c>
+      <c r="K43">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L43">
+        <v>16.7</v>
+      </c>
+      <c r="M43">
+        <v>32.4509916</v>
+      </c>
+      <c r="N43">
+        <v>-15.7509916</v>
+      </c>
+      <c r="O43">
+        <v>-3.622728068</v>
+      </c>
+      <c r="P43">
+        <v>-12.128263532</v>
+      </c>
+      <c r="Q43">
+        <v>-4.028263532</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1526020645685852</v>
+      </c>
+      <c r="T43">
+        <v>1.595790935440218</v>
+      </c>
+      <c r="U43">
+        <v>0.2138</v>
+      </c>
+      <c r="V43">
+        <v>0.1183631011139887</v>
+      </c>
+      <c r="W43">
+        <v>0.1884939689818292</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.5146221787564729</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1690677453780153</v>
+      </c>
+      <c r="C44">
+        <v>25.04787573920345</v>
+      </c>
+      <c r="D44">
+        <v>171.9418757392034</v>
+      </c>
+      <c r="E44">
+        <v>-111.416</v>
+      </c>
+      <c r="F44">
+        <v>155.484</v>
+      </c>
+      <c r="G44">
+        <v>8.59</v>
+      </c>
+      <c r="H44">
+        <v>103.3</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>24.8</v>
+      </c>
+      <c r="K44">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L44">
+        <v>16.7</v>
+      </c>
+      <c r="M44">
+        <v>33.24247919999999</v>
+      </c>
+      <c r="N44">
+        <v>-16.54247919999999</v>
+      </c>
+      <c r="O44">
+        <v>-3.804770215999998</v>
+      </c>
+      <c r="P44">
+        <v>-12.73770898399999</v>
+      </c>
+      <c r="Q44">
+        <v>-4.637708983999993</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1545641691301126</v>
+      </c>
+      <c r="T44">
+        <v>1.623304572258153</v>
+      </c>
+      <c r="U44">
+        <v>0.2138</v>
+      </c>
+      <c r="V44">
+        <v>0.1155449320398462</v>
+      </c>
+      <c r="W44">
+        <v>0.1890964935298809</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.5023692697384617</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1819262645759301</v>
+      </c>
+      <c r="C45">
+        <v>5.898550842764763</v>
+      </c>
+      <c r="D45">
+        <v>156.4945508427647</v>
+      </c>
+      <c r="E45">
+        <v>-107.714</v>
+      </c>
+      <c r="F45">
+        <v>159.186</v>
+      </c>
+      <c r="G45">
+        <v>8.59</v>
+      </c>
+      <c r="H45">
+        <v>103.3</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>24.8</v>
+      </c>
+      <c r="K45">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L45">
+        <v>16.7</v>
+      </c>
+      <c r="M45">
+        <v>38.01361679999999</v>
+      </c>
+      <c r="N45">
+        <v>-21.31361679999999</v>
+      </c>
+      <c r="O45">
+        <v>-4.902131863999998</v>
+      </c>
+      <c r="P45">
+        <v>-16.411484936</v>
+      </c>
+      <c r="Q45">
+        <v>-8.311484935999996</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.157224100514702</v>
+      </c>
+      <c r="T45">
+        <v>1.660603494808566</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.1010427400320403</v>
+      </c>
+      <c r="W45">
+        <v>0.2146709936803488</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.439316261008871</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1839262645759301</v>
+      </c>
+      <c r="C46">
+        <v>0.03988331879787665</v>
+      </c>
+      <c r="D46">
+        <v>154.3378833187979</v>
+      </c>
+      <c r="E46">
+        <v>-104.012</v>
+      </c>
+      <c r="F46">
+        <v>162.888</v>
+      </c>
+      <c r="G46">
+        <v>8.59</v>
+      </c>
+      <c r="H46">
+        <v>103.3</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>24.8</v>
+      </c>
+      <c r="K46">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L46">
+        <v>16.7</v>
+      </c>
+      <c r="M46">
+        <v>38.8976544</v>
+      </c>
+      <c r="N46">
+        <v>-22.1976544</v>
+      </c>
+      <c r="O46">
+        <v>-5.105460512</v>
+      </c>
+      <c r="P46">
+        <v>-17.092193888</v>
+      </c>
+      <c r="Q46">
+        <v>-8.992193887999999</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1593388165953217</v>
+      </c>
+      <c r="T46">
+        <v>1.690257128644433</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.09874631412222119</v>
+      </c>
+      <c r="W46">
+        <v>0.2152193801876136</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.4293318005313965</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1859262645759301</v>
+      </c>
+      <c r="C47">
+        <v>-5.760149738231831</v>
+      </c>
+      <c r="D47">
+        <v>152.2398502617682</v>
+      </c>
+      <c r="E47">
+        <v>-100.31</v>
+      </c>
+      <c r="F47">
+        <v>166.59</v>
+      </c>
+      <c r="G47">
+        <v>8.59</v>
+      </c>
+      <c r="H47">
+        <v>103.3</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>24.8</v>
+      </c>
+      <c r="K47">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L47">
+        <v>16.7</v>
+      </c>
+      <c r="M47">
+        <v>39.781692</v>
+      </c>
+      <c r="N47">
+        <v>-23.081692</v>
+      </c>
+      <c r="O47">
+        <v>-5.30878916</v>
+      </c>
+      <c r="P47">
+        <v>-17.77290284</v>
+      </c>
+      <c r="Q47">
+        <v>-9.672902839999999</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1615304314425093</v>
+      </c>
+      <c r="T47">
+        <v>1.720989076437969</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.09655195158617184</v>
+      </c>
+      <c r="W47">
+        <v>0.2157433939612222</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.4197910938529211</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1879262645759301</v>
+      </c>
+      <c r="C48">
+        <v>-11.50390744864848</v>
+      </c>
+      <c r="D48">
+        <v>150.1980925513515</v>
+      </c>
+      <c r="E48">
+        <v>-96.60799999999998</v>
+      </c>
+      <c r="F48">
+        <v>170.292</v>
+      </c>
+      <c r="G48">
+        <v>8.59</v>
+      </c>
+      <c r="H48">
+        <v>103.3</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>24.8</v>
+      </c>
+      <c r="K48">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L48">
+        <v>16.7</v>
+      </c>
+      <c r="M48">
+        <v>40.66572960000001</v>
+      </c>
+      <c r="N48">
+        <v>-23.96572960000001</v>
+      </c>
+      <c r="O48">
+        <v>-5.512117808000001</v>
+      </c>
+      <c r="P48">
+        <v>-18.453611792</v>
+      </c>
+      <c r="Q48">
+        <v>-10.353611792</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1638032172099632</v>
+      </c>
+      <c r="T48">
+        <v>1.752859244520153</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.09445299611690722</v>
+      </c>
+      <c r="W48">
+        <v>0.2162446245272826</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.4106652005082922</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1899262645759301</v>
+      </c>
+      <c r="C49">
+        <v>-17.19362405069396</v>
+      </c>
+      <c r="D49">
+        <v>148.210375949306</v>
+      </c>
+      <c r="E49">
+        <v>-92.90599999999998</v>
+      </c>
+      <c r="F49">
+        <v>173.994</v>
+      </c>
+      <c r="G49">
+        <v>8.59</v>
+      </c>
+      <c r="H49">
+        <v>103.3</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>24.8</v>
+      </c>
+      <c r="K49">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L49">
+        <v>16.7</v>
+      </c>
+      <c r="M49">
+        <v>41.54976720000001</v>
+      </c>
+      <c r="N49">
+        <v>-24.84976720000001</v>
+      </c>
+      <c r="O49">
+        <v>-5.715446456000001</v>
+      </c>
+      <c r="P49">
+        <v>-19.134320744</v>
+      </c>
+      <c r="Q49">
+        <v>-11.034320744</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1661617684780757</v>
+      </c>
+      <c r="T49">
+        <v>1.785932060454496</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.09244335790165388</v>
+      </c>
+      <c r="W49">
+        <v>0.216724526133085</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.4019276430506691</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1919262645759301</v>
+      </c>
+      <c r="C50">
+        <v>-22.83141705602534</v>
+      </c>
+      <c r="D50">
+        <v>146.2745829439747</v>
+      </c>
+      <c r="E50">
+        <v>-89.20399999999998</v>
+      </c>
+      <c r="F50">
+        <v>177.696</v>
+      </c>
+      <c r="G50">
+        <v>8.59</v>
+      </c>
+      <c r="H50">
+        <v>103.3</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>24.8</v>
+      </c>
+      <c r="K50">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L50">
+        <v>16.7</v>
+      </c>
+      <c r="M50">
+        <v>42.4338048</v>
+      </c>
+      <c r="N50">
+        <v>-25.73380480000001</v>
+      </c>
+      <c r="O50">
+        <v>-5.918775104000001</v>
+      </c>
+      <c r="P50">
+        <v>-19.815029696</v>
+      </c>
+      <c r="Q50">
+        <v>-11.715029696</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1686110332565003</v>
+      </c>
+      <c r="T50">
+        <v>1.820276907770928</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.09051745461203609</v>
+      </c>
+      <c r="W50">
+        <v>0.2171844318386458</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.3935541504871135</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1939262645759301</v>
+      </c>
+      <c r="C51">
+        <v>-28.41929477433237</v>
+      </c>
+      <c r="D51">
+        <v>144.3887052256676</v>
+      </c>
+      <c r="E51">
+        <v>-85.50199999999998</v>
+      </c>
+      <c r="F51">
+        <v>181.398</v>
+      </c>
+      <c r="G51">
+        <v>8.59</v>
+      </c>
+      <c r="H51">
+        <v>103.3</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>24.8</v>
+      </c>
+      <c r="K51">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L51">
+        <v>16.7</v>
+      </c>
+      <c r="M51">
+        <v>43.3178424</v>
+      </c>
+      <c r="N51">
+        <v>-26.6178424</v>
+      </c>
+      <c r="O51">
+        <v>-6.122103752</v>
+      </c>
+      <c r="P51">
+        <v>-20.495738648</v>
+      </c>
+      <c r="Q51">
+        <v>-12.395738648</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1711563476340787</v>
+      </c>
+      <c r="T51">
+        <v>1.855968611844868</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.08867015961995373</v>
+      </c>
+      <c r="W51">
+        <v>0.2176255658827551</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.3855224331302336</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1959262645759301</v>
+      </c>
+      <c r="C52">
+        <v>-33.95916326328759</v>
+      </c>
+      <c r="D52">
+        <v>142.5508367367124</v>
+      </c>
+      <c r="E52">
+        <v>-81.79999999999998</v>
+      </c>
+      <c r="F52">
+        <v>185.1</v>
+      </c>
+      <c r="G52">
+        <v>8.59</v>
+      </c>
+      <c r="H52">
+        <v>103.3</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>24.8</v>
+      </c>
+      <c r="K52">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L52">
+        <v>16.7</v>
+      </c>
+      <c r="M52">
+        <v>44.20188</v>
+      </c>
+      <c r="N52">
+        <v>-27.50188</v>
+      </c>
+      <c r="O52">
+        <v>-6.3254324</v>
+      </c>
+      <c r="P52">
+        <v>-21.1764476</v>
+      </c>
+      <c r="Q52">
+        <v>-13.0764476</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1738034745867603</v>
+      </c>
+      <c r="T52">
+        <v>1.893087984081765</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.08689675642755465</v>
+      </c>
+      <c r="W52">
+        <v>0.2180490545651</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.377811984467629</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1979262645759301</v>
+      </c>
+      <c r="C53">
+        <v>-39.45283275438771</v>
+      </c>
+      <c r="D53">
+        <v>140.7591672456123</v>
+      </c>
+      <c r="E53">
+        <v>-78.09799999999998</v>
+      </c>
+      <c r="F53">
+        <v>188.802</v>
+      </c>
+      <c r="G53">
+        <v>8.59</v>
+      </c>
+      <c r="H53">
+        <v>103.3</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>24.8</v>
+      </c>
+      <c r="K53">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L53">
+        <v>16.7</v>
+      </c>
+      <c r="M53">
+        <v>45.0859176</v>
+      </c>
+      <c r="N53">
+        <v>-28.3859176</v>
+      </c>
+      <c r="O53">
+        <v>-6.528761048</v>
+      </c>
+      <c r="P53">
+        <v>-21.857156552</v>
+      </c>
+      <c r="Q53">
+        <v>-13.757156552</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1765586475375105</v>
+      </c>
+      <c r="T53">
+        <v>1.931722432736495</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.08519289845838691</v>
+      </c>
+      <c r="W53">
+        <v>0.2184559358481372</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.3704039063408127</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1999262645759301</v>
+      </c>
+      <c r="C54">
+        <v>-44.90202360022624</v>
+      </c>
+      <c r="D54">
+        <v>139.0119763997737</v>
+      </c>
+      <c r="E54">
+        <v>-74.39599999999999</v>
+      </c>
+      <c r="F54">
+        <v>192.504</v>
+      </c>
+      <c r="G54">
+        <v>8.59</v>
+      </c>
+      <c r="H54">
+        <v>103.3</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>24.8</v>
+      </c>
+      <c r="K54">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L54">
+        <v>16.7</v>
+      </c>
+      <c r="M54">
+        <v>45.9699552</v>
+      </c>
+      <c r="N54">
+        <v>-29.2699552</v>
+      </c>
+      <c r="O54">
+        <v>-6.732089696</v>
+      </c>
+      <c r="P54">
+        <v>-22.537865504</v>
+      </c>
+      <c r="Q54">
+        <v>-14.437865504</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1794286193612086</v>
+      </c>
+      <c r="T54">
+        <v>1.971966650085172</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.08355457348803333</v>
+      </c>
+      <c r="W54">
+        <v>0.2188471678510577</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.3632807542957971</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2019262645759301</v>
+      </c>
+      <c r="C55">
+        <v>-50.30837178426836</v>
+      </c>
+      <c r="D55">
+        <v>137.3076282157317</v>
+      </c>
+      <c r="E55">
+        <v>-70.69399999999996</v>
+      </c>
+      <c r="F55">
+        <v>196.206</v>
+      </c>
+      <c r="G55">
+        <v>8.59</v>
+      </c>
+      <c r="H55">
+        <v>103.3</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>24.8</v>
+      </c>
+      <c r="K55">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L55">
+        <v>16.7</v>
+      </c>
+      <c r="M55">
+        <v>46.85399280000001</v>
+      </c>
+      <c r="N55">
+        <v>-30.15399280000001</v>
+      </c>
+      <c r="O55">
+        <v>-6.935418344000001</v>
+      </c>
+      <c r="P55">
+        <v>-23.21857445600001</v>
+      </c>
+      <c r="Q55">
+        <v>-15.118574456</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1824207176454897</v>
+      </c>
+      <c r="T55">
+        <v>2.013923387321027</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.08197807210146665</v>
+      </c>
+      <c r="W55">
+        <v>0.2192236363821698</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.3564264004411594</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2039262645759302</v>
+      </c>
+      <c r="C56">
+        <v>-55.6734340302213</v>
+      </c>
+      <c r="D56">
+        <v>135.6445659697787</v>
+      </c>
+      <c r="E56">
+        <v>-66.99199999999996</v>
+      </c>
+      <c r="F56">
+        <v>199.908</v>
+      </c>
+      <c r="G56">
+        <v>8.59</v>
+      </c>
+      <c r="H56">
+        <v>103.3</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>24.8</v>
+      </c>
+      <c r="K56">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L56">
+        <v>16.7</v>
+      </c>
+      <c r="M56">
+        <v>47.73803040000001</v>
+      </c>
+      <c r="N56">
+        <v>-31.03803040000001</v>
+      </c>
+      <c r="O56">
+        <v>-7.138746992000002</v>
+      </c>
+      <c r="P56">
+        <v>-23.89928340800001</v>
+      </c>
+      <c r="Q56">
+        <v>-15.799283408</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1855429071595221</v>
+      </c>
+      <c r="T56">
+        <v>2.057704330523658</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.08045995965514319</v>
+      </c>
+      <c r="W56">
+        <v>0.2195861616343518</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.3498259115441008</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2059262645759302</v>
+      </c>
+      <c r="C57">
+        <v>-60.99869254454239</v>
+      </c>
+      <c r="D57">
+        <v>134.0213074554576</v>
+      </c>
+      <c r="E57">
+        <v>-63.28999999999996</v>
+      </c>
+      <c r="F57">
+        <v>203.61</v>
+      </c>
+      <c r="G57">
+        <v>8.59</v>
+      </c>
+      <c r="H57">
+        <v>103.3</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>24.8</v>
+      </c>
+      <c r="K57">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L57">
+        <v>16.7</v>
+      </c>
+      <c r="M57">
+        <v>48.62206800000001</v>
+      </c>
+      <c r="N57">
+        <v>-31.92206800000001</v>
+      </c>
+      <c r="O57">
+        <v>-7.342075640000001</v>
+      </c>
+      <c r="P57">
+        <v>-24.57999236000001</v>
+      </c>
+      <c r="Q57">
+        <v>-16.47999236</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1888038606519559</v>
+      </c>
+      <c r="T57">
+        <v>2.103431093424184</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.07899705129777694</v>
+      </c>
+      <c r="W57">
+        <v>0.2199355041500909</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.3434654404251172</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2079262645759301</v>
+      </c>
+      <c r="C58">
+        <v>-66.28555942245166</v>
+      </c>
+      <c r="D58">
+        <v>132.4364405775484</v>
+      </c>
+      <c r="E58">
+        <v>-59.58799999999997</v>
+      </c>
+      <c r="F58">
+        <v>207.312</v>
+      </c>
+      <c r="G58">
+        <v>8.59</v>
+      </c>
+      <c r="H58">
+        <v>103.3</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>24.8</v>
+      </c>
+      <c r="K58">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L58">
+        <v>16.7</v>
+      </c>
+      <c r="M58">
+        <v>49.50610560000001</v>
+      </c>
+      <c r="N58">
+        <v>-32.80610560000001</v>
+      </c>
+      <c r="O58">
+        <v>-7.545404288000001</v>
+      </c>
+      <c r="P58">
+        <v>-25.26070131200001</v>
+      </c>
+      <c r="Q58">
+        <v>-17.16070131200001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1922130393031367</v>
+      </c>
+      <c r="T58">
+        <v>2.151236345547461</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.0775863896674595</v>
+      </c>
+      <c r="W58">
+        <v>0.2202723701474107</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.3373321289889544</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2099262645759301</v>
+      </c>
+      <c r="C59">
+        <v>-71.53538074497911</v>
+      </c>
+      <c r="D59">
+        <v>130.8886192550209</v>
+      </c>
+      <c r="E59">
+        <v>-55.88599999999997</v>
+      </c>
+      <c r="F59">
+        <v>211.014</v>
+      </c>
+      <c r="G59">
+        <v>8.59</v>
+      </c>
+      <c r="H59">
+        <v>103.3</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>24.8</v>
+      </c>
+      <c r="K59">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L59">
+        <v>16.7</v>
+      </c>
+      <c r="M59">
+        <v>50.3901432</v>
+      </c>
+      <c r="N59">
+        <v>-33.69014320000001</v>
+      </c>
+      <c r="O59">
+        <v>-7.748732936000001</v>
+      </c>
+      <c r="P59">
+        <v>-25.94141026400001</v>
+      </c>
+      <c r="Q59">
+        <v>-17.841410264</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1957807844032096</v>
+      </c>
+      <c r="T59">
+        <v>2.201265097769495</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.07622522493645144</v>
+      </c>
+      <c r="W59">
+        <v>0.2205974162851754</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.3314140214628323</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2119262645759301</v>
+      </c>
+      <c r="C60">
+        <v>-76.74944039203064</v>
+      </c>
+      <c r="D60">
+        <v>129.3765596079693</v>
+      </c>
+      <c r="E60">
+        <v>-52.184</v>
+      </c>
+      <c r="F60">
+        <v>214.716</v>
+      </c>
+      <c r="G60">
+        <v>8.59</v>
+      </c>
+      <c r="H60">
+        <v>103.3</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>24.8</v>
+      </c>
+      <c r="K60">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L60">
+        <v>16.7</v>
+      </c>
+      <c r="M60">
+        <v>51.2741808</v>
+      </c>
+      <c r="N60">
+        <v>-34.57418079999999</v>
+      </c>
+      <c r="O60">
+        <v>-7.952061583999998</v>
+      </c>
+      <c r="P60">
+        <v>-26.62211921599999</v>
+      </c>
+      <c r="Q60">
+        <v>-18.52211921599999</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1995184221270956</v>
+      </c>
+      <c r="T60">
+        <v>2.253676171525911</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.07491099692030574</v>
+      </c>
+      <c r="W60">
+        <v>0.220911253935431</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.3256999866100251</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2139262645759301</v>
+      </c>
+      <c r="C61">
+        <v>-81.92896359417574</v>
+      </c>
+      <c r="D61">
+        <v>127.8990364058242</v>
+      </c>
+      <c r="E61">
+        <v>-48.482</v>
+      </c>
+      <c r="F61">
+        <v>218.418</v>
+      </c>
+      <c r="G61">
+        <v>8.59</v>
+      </c>
+      <c r="H61">
+        <v>103.3</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>24.8</v>
+      </c>
+      <c r="K61">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L61">
+        <v>16.7</v>
+      </c>
+      <c r="M61">
+        <v>52.1582184</v>
+      </c>
+      <c r="N61">
+        <v>-35.45821839999999</v>
+      </c>
+      <c r="O61">
+        <v>-8.155390231999998</v>
+      </c>
+      <c r="P61">
+        <v>-27.30282816799999</v>
+      </c>
+      <c r="Q61">
+        <v>-19.20282816799999</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2034383836423906</v>
+      </c>
+      <c r="T61">
+        <v>2.308643883026543</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.07364131900640226</v>
+      </c>
+      <c r="W61">
+        <v>0.2212144530212712</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.3201796478539229</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2159262645759301</v>
+      </c>
+      <c r="C62">
+        <v>-87.07512024380685</v>
+      </c>
+      <c r="D62">
+        <v>126.4548797561931</v>
+      </c>
+      <c r="E62">
+        <v>-44.78</v>
+      </c>
+      <c r="F62">
+        <v>222.12</v>
+      </c>
+      <c r="G62">
+        <v>8.59</v>
+      </c>
+      <c r="H62">
+        <v>103.3</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>24.8</v>
+      </c>
+      <c r="K62">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L62">
+        <v>16.7</v>
+      </c>
+      <c r="M62">
+        <v>53.04225599999999</v>
+      </c>
+      <c r="N62">
+        <v>-36.34225599999999</v>
+      </c>
+      <c r="O62">
+        <v>-8.358718879999998</v>
+      </c>
+      <c r="P62">
+        <v>-27.98353711999999</v>
+      </c>
+      <c r="Q62">
+        <v>-19.88353711999999</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2075543432334503</v>
+      </c>
+      <c r="T62">
+        <v>2.366359980102207</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.07241396368962888</v>
+      </c>
+      <c r="W62">
+        <v>0.2215075454709166</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.3148433203896909</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2179262645759301</v>
+      </c>
+      <c r="C63">
+        <v>-92.18902798447871</v>
+      </c>
+      <c r="D63">
+        <v>125.0429720155213</v>
+      </c>
+      <c r="E63">
+        <v>-41.078</v>
+      </c>
+      <c r="F63">
+        <v>225.822</v>
+      </c>
+      <c r="G63">
+        <v>8.59</v>
+      </c>
+      <c r="H63">
+        <v>103.3</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>24.8</v>
+      </c>
+      <c r="K63">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L63">
+        <v>16.7</v>
+      </c>
+      <c r="M63">
+        <v>53.92629359999999</v>
+      </c>
+      <c r="N63">
+        <v>-37.22629359999999</v>
+      </c>
+      <c r="O63">
+        <v>-8.562047527999997</v>
+      </c>
+      <c r="P63">
+        <v>-28.66424607199999</v>
+      </c>
+      <c r="Q63">
+        <v>-20.56424607199999</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2118813776753337</v>
+      </c>
+      <c r="T63">
+        <v>2.427035877027905</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.07122684953078251</v>
+      </c>
+      <c r="W63">
+        <v>0.2217910283320491</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.3096819544816631</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2199262645759301</v>
+      </c>
+      <c r="C64">
+        <v>-97.27175509557199</v>
+      </c>
+      <c r="D64">
+        <v>123.662244904428</v>
+      </c>
+      <c r="E64">
+        <v>-37.37599999999998</v>
+      </c>
+      <c r="F64">
+        <v>229.524</v>
+      </c>
+      <c r="G64">
+        <v>8.59</v>
+      </c>
+      <c r="H64">
+        <v>103.3</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>24.8</v>
+      </c>
+      <c r="K64">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L64">
+        <v>16.7</v>
+      </c>
+      <c r="M64">
+        <v>54.8103312</v>
+      </c>
+      <c r="N64">
+        <v>-38.1103312</v>
+      </c>
+      <c r="O64">
+        <v>-8.765376176</v>
+      </c>
+      <c r="P64">
+        <v>-29.344955024</v>
+      </c>
+      <c r="Q64">
+        <v>-21.244955024</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.216436150772053</v>
+      </c>
+      <c r="T64">
+        <v>2.490905242212849</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.0700780293770602</v>
+      </c>
+      <c r="W64">
+        <v>0.222065366584758</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.3046870842480878</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2219262645759301</v>
+      </c>
+      <c r="C65">
+        <v>-102.3243231879294</v>
+      </c>
+      <c r="D65">
+        <v>122.3116768120706</v>
+      </c>
+      <c r="E65">
+        <v>-33.67399999999998</v>
+      </c>
+      <c r="F65">
+        <v>233.226</v>
+      </c>
+      <c r="G65">
+        <v>8.59</v>
+      </c>
+      <c r="H65">
+        <v>103.3</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>24.8</v>
+      </c>
+      <c r="K65">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L65">
+        <v>16.7</v>
+      </c>
+      <c r="M65">
+        <v>55.6943688</v>
+      </c>
+      <c r="N65">
+        <v>-38.9943688</v>
+      </c>
+      <c r="O65">
+        <v>-8.968704824</v>
+      </c>
+      <c r="P65">
+        <v>-30.025663976</v>
+      </c>
+      <c r="Q65">
+        <v>-21.925663976</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2212371278199463</v>
+      </c>
+      <c r="T65">
+        <v>2.558227005515899</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.06896567970440846</v>
+      </c>
+      <c r="W65">
+        <v>0.2223309956865873</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.2998507813235149</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2239262645759301</v>
+      </c>
+      <c r="C66">
+        <v>-107.3477097247588</v>
+      </c>
+      <c r="D66">
+        <v>120.9902902752412</v>
+      </c>
+      <c r="E66">
+        <v>-29.97199999999998</v>
+      </c>
+      <c r="F66">
+        <v>236.928</v>
+      </c>
+      <c r="G66">
+        <v>8.59</v>
+      </c>
+      <c r="H66">
+        <v>103.3</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>24.8</v>
+      </c>
+      <c r="K66">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L66">
+        <v>16.7</v>
+      </c>
+      <c r="M66">
+        <v>56.57840640000001</v>
+      </c>
+      <c r="N66">
+        <v>-39.8784064</v>
+      </c>
+      <c r="O66">
+        <v>-9.172033472000001</v>
+      </c>
+      <c r="P66">
+        <v>-30.706372928</v>
+      </c>
+      <c r="Q66">
+        <v>-22.606372928</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2263048258149449</v>
+      </c>
+      <c r="T66">
+        <v>2.62928886678023</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.06788809095902706</v>
+      </c>
+      <c r="W66">
+        <v>0.2225883238789844</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.2951656128653352</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2259262645759301</v>
+      </c>
+      <c r="C67">
+        <v>-112.342850380876</v>
+      </c>
+      <c r="D67">
+        <v>119.697149619124</v>
+      </c>
+      <c r="E67">
+        <v>-26.26999999999998</v>
+      </c>
+      <c r="F67">
+        <v>240.63</v>
+      </c>
+      <c r="G67">
+        <v>8.59</v>
+      </c>
+      <c r="H67">
+        <v>103.3</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>24.8</v>
+      </c>
+      <c r="K67">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L67">
+        <v>16.7</v>
+      </c>
+      <c r="M67">
+        <v>57.462444</v>
+      </c>
+      <c r="N67">
+        <v>-40.762444</v>
+      </c>
+      <c r="O67">
+        <v>-9.37536212</v>
+      </c>
+      <c r="P67">
+        <v>-31.38708188</v>
+      </c>
+      <c r="Q67">
+        <v>-23.28708188</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2316621065525147</v>
+      </c>
+      <c r="T67">
+        <v>2.704411405831094</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.06684365879042665</v>
+      </c>
+      <c r="W67">
+        <v>0.2228377342808461</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.2906246034366377</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2279262645759302</v>
+      </c>
+      <c r="C68">
+        <v>-117.3106412522552</v>
+      </c>
+      <c r="D68">
+        <v>118.4313587477448</v>
+      </c>
+      <c r="E68">
+        <v>-22.56799999999998</v>
+      </c>
+      <c r="F68">
+        <v>244.332</v>
+      </c>
+      <c r="G68">
+        <v>8.59</v>
+      </c>
+      <c r="H68">
+        <v>103.3</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>24.8</v>
+      </c>
+      <c r="K68">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L68">
+        <v>16.7</v>
+      </c>
+      <c r="M68">
+        <v>58.3464816</v>
+      </c>
+      <c r="N68">
+        <v>-41.6464816</v>
+      </c>
+      <c r="O68">
+        <v>-9.578690768</v>
+      </c>
+      <c r="P68">
+        <v>-32.067790832</v>
+      </c>
+      <c r="Q68">
+        <v>-23.967790832</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2373345214511181</v>
+      </c>
+      <c r="T68">
+        <v>2.783952917767303</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.06583087608148079</v>
+      </c>
+      <c r="W68">
+        <v>0.2230795867917424</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.2862212003542645</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2299262645759301</v>
+      </c>
+      <c r="C69">
+        <v>-122.2519409268501</v>
+      </c>
+      <c r="D69">
+        <v>117.1920590731499</v>
+      </c>
+      <c r="E69">
+        <v>-18.86599999999996</v>
+      </c>
+      <c r="F69">
+        <v>248.034</v>
+      </c>
+      <c r="G69">
+        <v>8.59</v>
+      </c>
+      <c r="H69">
+        <v>103.3</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>24.8</v>
+      </c>
+      <c r="K69">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L69">
+        <v>16.7</v>
+      </c>
+      <c r="M69">
+        <v>59.23051920000001</v>
+      </c>
+      <c r="N69">
+        <v>-42.53051920000001</v>
+      </c>
+      <c r="O69">
+        <v>-9.782019416000002</v>
+      </c>
+      <c r="P69">
+        <v>-32.74849978400001</v>
+      </c>
+      <c r="Q69">
+        <v>-24.64849978400001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2433507190708489</v>
+      </c>
+      <c r="T69">
+        <v>2.868315127396614</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.06484832569220494</v>
+      </c>
+      <c r="W69">
+        <v>0.2233142198247015</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.2819492421400215</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2319262645759301</v>
+      </c>
+      <c r="C70">
+        <v>-127.1675724267445</v>
+      </c>
+      <c r="D70">
+        <v>115.9784275732555</v>
+      </c>
+      <c r="E70">
+        <v>-15.16399999999996</v>
+      </c>
+      <c r="F70">
+        <v>251.736</v>
+      </c>
+      <c r="G70">
+        <v>8.59</v>
+      </c>
+      <c r="H70">
+        <v>103.3</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>24.8</v>
+      </c>
+      <c r="K70">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L70">
+        <v>16.7</v>
+      </c>
+      <c r="M70">
+        <v>60.11455680000001</v>
+      </c>
+      <c r="N70">
+        <v>-43.41455680000001</v>
+      </c>
+      <c r="O70">
+        <v>-9.985348064000002</v>
+      </c>
+      <c r="P70">
+        <v>-33.42920873600001</v>
+      </c>
+      <c r="Q70">
+        <v>-25.32920873600001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.249742929041813</v>
+      </c>
+      <c r="T70">
+        <v>2.957949975127759</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.06389467384379018</v>
+      </c>
+      <c r="W70">
+        <v>0.2235419518861029</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.2778029297556094</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2339262645759302</v>
+      </c>
+      <c r="C71">
+        <v>-132.0583250308628</v>
+      </c>
+      <c r="D71">
+        <v>114.7896749691372</v>
+      </c>
+      <c r="E71">
+        <v>-11.46199999999996</v>
+      </c>
+      <c r="F71">
+        <v>255.438</v>
+      </c>
+      <c r="G71">
+        <v>8.59</v>
+      </c>
+      <c r="H71">
+        <v>103.3</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>24.8</v>
+      </c>
+      <c r="K71">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L71">
+        <v>16.7</v>
+      </c>
+      <c r="M71">
+        <v>60.99859440000001</v>
+      </c>
+      <c r="N71">
+        <v>-44.29859440000001</v>
+      </c>
+      <c r="O71">
+        <v>-10.188676712</v>
+      </c>
+      <c r="P71">
+        <v>-34.10991768800001</v>
+      </c>
+      <c r="Q71">
+        <v>-26.00991768800001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.256547539656065</v>
+      </c>
+      <c r="T71">
+        <v>3.053367716260913</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.06296866407793815</v>
+      </c>
+      <c r="W71">
+        <v>0.2237630830181884</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.2737768003388614</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2359262645759301</v>
+      </c>
+      <c r="C72">
+        <v>-136.9249559867233</v>
+      </c>
+      <c r="D72">
+        <v>113.6250440132767</v>
+      </c>
+      <c r="E72">
+        <v>-7.759999999999934</v>
+      </c>
+      <c r="F72">
+        <v>259.14</v>
+      </c>
+      <c r="G72">
+        <v>8.59</v>
+      </c>
+      <c r="H72">
+        <v>103.3</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>24.8</v>
+      </c>
+      <c r="K72">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L72">
+        <v>16.7</v>
+      </c>
+      <c r="M72">
+        <v>61.88263200000002</v>
+      </c>
+      <c r="N72">
+        <v>-45.18263200000001</v>
+      </c>
+      <c r="O72">
+        <v>-10.39200536</v>
+      </c>
+      <c r="P72">
+        <v>-34.79062664000001</v>
+      </c>
+      <c r="Q72">
+        <v>-26.69062664000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2638057909779338</v>
+      </c>
+      <c r="T72">
+        <v>3.155146640136276</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.0620691117339676</v>
+      </c>
+      <c r="W72">
+        <v>0.2239778961179286</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.2698657031911635</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2379262645759301</v>
+      </c>
+      <c r="C73">
+        <v>-141.7681921190362</v>
+      </c>
+      <c r="D73">
+        <v>112.4838078809638</v>
+      </c>
+      <c r="E73">
+        <v>-4.057999999999993</v>
+      </c>
+      <c r="F73">
+        <v>262.842</v>
+      </c>
+      <c r="G73">
+        <v>8.59</v>
+      </c>
+      <c r="H73">
+        <v>103.3</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>24.8</v>
+      </c>
+      <c r="K73">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L73">
+        <v>16.7</v>
+      </c>
+      <c r="M73">
+        <v>62.7666696</v>
+      </c>
+      <c r="N73">
+        <v>-46.0666696</v>
+      </c>
+      <c r="O73">
+        <v>-10.595334008</v>
+      </c>
+      <c r="P73">
+        <v>-35.471335592</v>
+      </c>
+      <c r="Q73">
+        <v>-27.371335592</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2715646113564832</v>
+      </c>
+      <c r="T73">
+        <v>3.263944800140974</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.06119489889264413</v>
+      </c>
+      <c r="W73">
+        <v>0.2241866581444366</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.266064777794105</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2399262645759301</v>
+      </c>
+      <c r="C74">
+        <v>-146.5887313423259</v>
+      </c>
+      <c r="D74">
+        <v>111.3652686576741</v>
+      </c>
+      <c r="E74">
+        <v>-0.3559999999999945</v>
+      </c>
+      <c r="F74">
+        <v>266.544</v>
+      </c>
+      <c r="G74">
+        <v>8.59</v>
+      </c>
+      <c r="H74">
+        <v>103.3</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>24.8</v>
+      </c>
+      <c r="K74">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L74">
+        <v>16.7</v>
+      </c>
+      <c r="M74">
+        <v>63.6507072</v>
+      </c>
+      <c r="N74">
+        <v>-46.9507072</v>
+      </c>
+      <c r="O74">
+        <v>-10.798662656</v>
+      </c>
+      <c r="P74">
+        <v>-36.152044544</v>
+      </c>
+      <c r="Q74">
+        <v>-28.052044544</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2798776331906433</v>
+      </c>
+      <c r="T74">
+        <v>3.380514257288866</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.0603449697413574</v>
+      </c>
+      <c r="W74">
+        <v>0.2243896212257639</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.2623694336580757</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2419262645759301</v>
+      </c>
+      <c r="C75">
+        <v>-151.3872440841928</v>
+      </c>
+      <c r="D75">
+        <v>110.2687559158071</v>
+      </c>
+      <c r="E75">
+        <v>3.346000000000004</v>
+      </c>
+      <c r="F75">
+        <v>270.246</v>
+      </c>
+      <c r="G75">
+        <v>8.59</v>
+      </c>
+      <c r="H75">
+        <v>103.3</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>24.8</v>
+      </c>
+      <c r="K75">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L75">
+        <v>16.7</v>
+      </c>
+      <c r="M75">
+        <v>64.5347448</v>
+      </c>
+      <c r="N75">
+        <v>-47.8347448</v>
+      </c>
+      <c r="O75">
+        <v>-11.001991304</v>
+      </c>
+      <c r="P75">
+        <v>-36.832753496</v>
+      </c>
+      <c r="Q75">
+        <v>-28.73275349599999</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2888064344199264</v>
+      </c>
+      <c r="T75">
+        <v>3.505718489040306</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.05951832632024291</v>
+      </c>
+      <c r="W75">
+        <v>0.224587023674726</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.2587753318271432</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2439262645759301</v>
+      </c>
+      <c r="C76">
+        <v>-156.1643746253137</v>
+      </c>
+      <c r="D76">
+        <v>109.1936253746863</v>
+      </c>
+      <c r="E76">
+        <v>7.048000000000002</v>
+      </c>
+      <c r="F76">
+        <v>273.948</v>
+      </c>
+      <c r="G76">
+        <v>8.59</v>
+      </c>
+      <c r="H76">
+        <v>103.3</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>24.8</v>
+      </c>
+      <c r="K76">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L76">
+        <v>16.7</v>
+      </c>
+      <c r="M76">
+        <v>65.4187824</v>
+      </c>
+      <c r="N76">
+        <v>-48.71878239999999</v>
+      </c>
+      <c r="O76">
+        <v>-11.205319952</v>
+      </c>
+      <c r="P76">
+        <v>-37.513462448</v>
+      </c>
+      <c r="Q76">
+        <v>-29.413462448</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2984220665130005</v>
+      </c>
+      <c r="T76">
+        <v>3.640553815541856</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.0587140246132126</v>
+      </c>
+      <c r="W76">
+        <v>0.2247790909223648</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.2552783678835332</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2459262645759301</v>
+      </c>
+      <c r="C77">
+        <v>-160.9207423618076</v>
+      </c>
+      <c r="D77">
+        <v>108.1392576381923</v>
+      </c>
+      <c r="E77">
+        <v>10.75</v>
+      </c>
+      <c r="F77">
+        <v>277.65</v>
+      </c>
+      <c r="G77">
+        <v>8.59</v>
+      </c>
+      <c r="H77">
+        <v>103.3</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>24.8</v>
+      </c>
+      <c r="K77">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L77">
+        <v>16.7</v>
+      </c>
+      <c r="M77">
+        <v>66.30282</v>
+      </c>
+      <c r="N77">
+        <v>-49.60281999999999</v>
+      </c>
+      <c r="O77">
+        <v>-11.4086486</v>
+      </c>
+      <c r="P77">
+        <v>-38.19417139999999</v>
+      </c>
+      <c r="Q77">
+        <v>-30.09417139999999</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3088069491735206</v>
+      </c>
+      <c r="T77">
+        <v>3.786175968163531</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.05793117095170311</v>
+      </c>
+      <c r="W77">
+        <v>0.2249660363767333</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.2518746563117527</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2479262645759301</v>
+      </c>
+      <c r="C78">
+        <v>-165.6569429951664</v>
+      </c>
+      <c r="D78">
+        <v>107.1050570048335</v>
+      </c>
+      <c r="E78">
+        <v>14.452</v>
+      </c>
+      <c r="F78">
+        <v>281.352</v>
+      </c>
+      <c r="G78">
+        <v>8.59</v>
+      </c>
+      <c r="H78">
+        <v>103.3</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>24.8</v>
+      </c>
+      <c r="K78">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L78">
+        <v>16.7</v>
+      </c>
+      <c r="M78">
+        <v>67.1868576</v>
+      </c>
+      <c r="N78">
+        <v>-50.48685759999999</v>
+      </c>
+      <c r="O78">
+        <v>-11.611977248</v>
+      </c>
+      <c r="P78">
+        <v>-38.874880352</v>
+      </c>
+      <c r="Q78">
+        <v>-30.774880352</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3200572387224173</v>
+      </c>
+      <c r="T78">
+        <v>3.943933300170344</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.0571689187023386</v>
+      </c>
+      <c r="W78">
+        <v>0.2251480622138815</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.2485605160971244</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2499262645759301</v>
+      </c>
+      <c r="C79">
+        <v>-170.3735496545507</v>
+      </c>
+      <c r="D79">
+        <v>106.0904503454492</v>
+      </c>
+      <c r="E79">
+        <v>18.154</v>
+      </c>
+      <c r="F79">
+        <v>285.054</v>
+      </c>
+      <c r="G79">
+        <v>8.59</v>
+      </c>
+      <c r="H79">
+        <v>103.3</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>24.8</v>
+      </c>
+      <c r="K79">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L79">
+        <v>16.7</v>
+      </c>
+      <c r="M79">
+        <v>68.0708952</v>
+      </c>
+      <c r="N79">
+        <v>-51.37089519999999</v>
+      </c>
+      <c r="O79">
+        <v>-11.815305896</v>
+      </c>
+      <c r="P79">
+        <v>-39.55558930399999</v>
+      </c>
+      <c r="Q79">
+        <v>-31.45558930399999</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3322858143190441</v>
+      </c>
+      <c r="T79">
+        <v>4.115408661047317</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.05642646521269783</v>
+      </c>
+      <c r="W79">
+        <v>0.2253253601072078</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.2453324574465123</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2519262645759301</v>
+      </c>
+      <c r="C80">
+        <v>-175.0711139558962</v>
+      </c>
+      <c r="D80">
+        <v>105.0948860441038</v>
+      </c>
+      <c r="E80">
+        <v>21.85600000000005</v>
+      </c>
+      <c r="F80">
+        <v>288.756</v>
+      </c>
+      <c r="G80">
+        <v>8.59</v>
+      </c>
+      <c r="H80">
+        <v>103.3</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>24.8</v>
+      </c>
+      <c r="K80">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L80">
+        <v>16.7</v>
+      </c>
+      <c r="M80">
+        <v>68.95493280000001</v>
+      </c>
+      <c r="N80">
+        <v>-52.25493280000001</v>
+      </c>
+      <c r="O80">
+        <v>-12.018634544</v>
+      </c>
+      <c r="P80">
+        <v>-40.236298256</v>
+      </c>
+      <c r="Q80">
+        <v>-32.136298256</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3456260786062734</v>
+      </c>
+      <c r="T80">
+        <v>4.302472691094922</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.05570304899202221</v>
+      </c>
+      <c r="W80">
+        <v>0.2254981119007051</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.2421871695305314</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2539262645759301</v>
+      </c>
+      <c r="C81">
+        <v>-179.7501670019413</v>
+      </c>
+      <c r="D81">
+        <v>104.1178329980587</v>
+      </c>
+      <c r="E81">
+        <v>25.55800000000005</v>
+      </c>
+      <c r="F81">
+        <v>292.458</v>
+      </c>
+      <c r="G81">
+        <v>8.59</v>
+      </c>
+      <c r="H81">
+        <v>103.3</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>24.8</v>
+      </c>
+      <c r="K81">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L81">
+        <v>16.7</v>
+      </c>
+      <c r="M81">
+        <v>69.83897040000001</v>
+      </c>
+      <c r="N81">
+        <v>-53.13897040000001</v>
+      </c>
+      <c r="O81">
+        <v>-12.221963192</v>
+      </c>
+      <c r="P81">
+        <v>-40.917007208</v>
+      </c>
+      <c r="Q81">
+        <v>-32.817007208</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3602368442541912</v>
+      </c>
+      <c r="T81">
+        <v>4.507352343051823</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.05499794710604725</v>
+      </c>
+      <c r="W81">
+        <v>0.2256664902310759</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.2391215091567273</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2559262645759302</v>
+      </c>
+      <c r="C82">
+        <v>-184.4112203269862</v>
+      </c>
+      <c r="D82">
+        <v>103.1587796730139</v>
+      </c>
+      <c r="E82">
+        <v>29.26000000000005</v>
+      </c>
+      <c r="F82">
+        <v>296.16</v>
+      </c>
+      <c r="G82">
+        <v>8.59</v>
+      </c>
+      <c r="H82">
+        <v>103.3</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>24.8</v>
+      </c>
+      <c r="K82">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L82">
+        <v>16.7</v>
+      </c>
+      <c r="M82">
+        <v>70.72300800000001</v>
+      </c>
+      <c r="N82">
+        <v>-54.023008</v>
+      </c>
+      <c r="O82">
+        <v>-12.42529184</v>
+      </c>
+      <c r="P82">
+        <v>-41.59771616</v>
+      </c>
+      <c r="Q82">
+        <v>-33.49771616</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3763086864669007</v>
+      </c>
+      <c r="T82">
+        <v>4.732719960204414</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.05431047276722165</v>
+      </c>
+      <c r="W82">
+        <v>0.2258306591031875</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.2361324902922681</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2579262645759302</v>
+      </c>
+      <c r="C83">
+        <v>-189.0547667899139</v>
+      </c>
+      <c r="D83">
+        <v>102.2172332100861</v>
+      </c>
+      <c r="E83">
+        <v>32.96200000000005</v>
+      </c>
+      <c r="F83">
+        <v>299.862</v>
+      </c>
+      <c r="G83">
+        <v>8.59</v>
+      </c>
+      <c r="H83">
+        <v>103.3</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>24.8</v>
+      </c>
+      <c r="K83">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L83">
+        <v>16.7</v>
+      </c>
+      <c r="M83">
+        <v>71.60704560000001</v>
+      </c>
+      <c r="N83">
+        <v>-54.9070456</v>
+      </c>
+      <c r="O83">
+        <v>-12.628620488</v>
+      </c>
+      <c r="P83">
+        <v>-42.27842511200001</v>
+      </c>
+      <c r="Q83">
+        <v>-34.17842511200001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3940723015441061</v>
+      </c>
+      <c r="T83">
+        <v>4.9818104844257</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.05363997310342879</v>
+      </c>
+      <c r="W83">
+        <v>0.2259907744229012</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.233217274362734</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2599262645759302</v>
+      </c>
+      <c r="C84">
+        <v>-193.6812814187492</v>
+      </c>
+      <c r="D84">
+        <v>101.2927185812508</v>
+      </c>
+      <c r="E84">
+        <v>36.66400000000004</v>
+      </c>
+      <c r="F84">
+        <v>303.564</v>
+      </c>
+      <c r="G84">
+        <v>8.59</v>
+      </c>
+      <c r="H84">
+        <v>103.3</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>24.8</v>
+      </c>
+      <c r="K84">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L84">
+        <v>16.7</v>
+      </c>
+      <c r="M84">
+        <v>72.49108320000001</v>
+      </c>
+      <c r="N84">
+        <v>-55.7910832</v>
+      </c>
+      <c r="O84">
+        <v>-12.831949136</v>
+      </c>
+      <c r="P84">
+        <v>-42.959134064</v>
+      </c>
+      <c r="Q84">
+        <v>-34.859134064</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4138096516298898</v>
+      </c>
+      <c r="T84">
+        <v>5.258577733560461</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.05298582708997235</v>
+      </c>
+      <c r="W84">
+        <v>0.2261469844909146</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.2303731612607494</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2619262645759302</v>
+      </c>
+      <c r="C85">
+        <v>-198.2912222097966</v>
+      </c>
+      <c r="D85">
+        <v>100.3847777902035</v>
+      </c>
+      <c r="E85">
+        <v>40.36600000000004</v>
+      </c>
+      <c r="F85">
+        <v>307.266</v>
+      </c>
+      <c r="G85">
+        <v>8.59</v>
+      </c>
+      <c r="H85">
+        <v>103.3</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>24.8</v>
+      </c>
+      <c r="K85">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L85">
+        <v>16.7</v>
+      </c>
+      <c r="M85">
+        <v>73.3751208</v>
+      </c>
+      <c r="N85">
+        <v>-56.6751208</v>
+      </c>
+      <c r="O85">
+        <v>-13.035277784</v>
+      </c>
+      <c r="P85">
+        <v>-43.639843016</v>
+      </c>
+      <c r="Q85">
+        <v>-35.539843016</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4358690429022363</v>
+      </c>
+      <c r="T85">
+        <v>5.567905835534606</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.05234744363105701</v>
+      </c>
+      <c r="W85">
+        <v>0.2262994304609036</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.2275975810045958</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2639262645759302</v>
+      </c>
+      <c r="C86">
+        <v>-202.8850308841802</v>
+      </c>
+      <c r="D86">
+        <v>99.49296911581979</v>
+      </c>
+      <c r="E86">
+        <v>44.06799999999998</v>
+      </c>
+      <c r="F86">
+        <v>310.968</v>
+      </c>
+      <c r="G86">
+        <v>8.59</v>
+      </c>
+      <c r="H86">
+        <v>103.3</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>24.8</v>
+      </c>
+      <c r="K86">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L86">
+        <v>16.7</v>
+      </c>
+      <c r="M86">
+        <v>74.25915839999999</v>
+      </c>
+      <c r="N86">
+        <v>-57.55915839999999</v>
+      </c>
+      <c r="O86">
+        <v>-13.238606432</v>
+      </c>
+      <c r="P86">
+        <v>-44.32055196799999</v>
+      </c>
+      <c r="Q86">
+        <v>-36.22055196799999</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4606858580836258</v>
+      </c>
+      <c r="T86">
+        <v>5.915899950255517</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.05172425977830635</v>
+      </c>
+      <c r="W86">
+        <v>0.2264482467649405</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.2248880859926363</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2659262645759301</v>
+      </c>
+      <c r="C87">
+        <v>-207.4631336044145</v>
+      </c>
+      <c r="D87">
+        <v>98.61686639558545</v>
+      </c>
+      <c r="E87">
+        <v>47.76999999999998</v>
+      </c>
+      <c r="F87">
+        <v>314.67</v>
+      </c>
+      <c r="G87">
+        <v>8.59</v>
+      </c>
+      <c r="H87">
+        <v>103.3</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>24.8</v>
+      </c>
+      <c r="K87">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L87">
+        <v>16.7</v>
+      </c>
+      <c r="M87">
+        <v>75.14319599999999</v>
+      </c>
+      <c r="N87">
+        <v>-58.44319599999999</v>
+      </c>
+      <c r="O87">
+        <v>-13.44193508</v>
+      </c>
+      <c r="P87">
+        <v>-45.00126091999999</v>
+      </c>
+      <c r="Q87">
+        <v>-36.90126091999999</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4888115819558675</v>
+      </c>
+      <c r="T87">
+        <v>6.31029328027255</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.05111573907503215</v>
+      </c>
+      <c r="W87">
+        <v>0.2265935615088823</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.2222423438044877</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2679262645759301</v>
+      </c>
+      <c r="C88">
+        <v>-212.0259416534446</v>
+      </c>
+      <c r="D88">
+        <v>97.75605834655531</v>
+      </c>
+      <c r="E88">
+        <v>51.47199999999998</v>
+      </c>
+      <c r="F88">
+        <v>318.372</v>
+      </c>
+      <c r="G88">
+        <v>8.59</v>
+      </c>
+      <c r="H88">
+        <v>103.3</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>24.8</v>
+      </c>
+      <c r="K88">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L88">
+        <v>16.7</v>
+      </c>
+      <c r="M88">
+        <v>76.02723359999999</v>
+      </c>
+      <c r="N88">
+        <v>-59.32723359999999</v>
+      </c>
+      <c r="O88">
+        <v>-13.645263728</v>
+      </c>
+      <c r="P88">
+        <v>-45.68196987199999</v>
+      </c>
+      <c r="Q88">
+        <v>-37.58196987199999</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5209552663812866</v>
+      </c>
+      <c r="T88">
+        <v>6.761028514577733</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.05052137001602015</v>
+      </c>
+      <c r="W88">
+        <v>0.2267354968401744</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.2196581305044355</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2699262645759301</v>
+      </c>
+      <c r="C89">
+        <v>-216.5738520784319</v>
+      </c>
+      <c r="D89">
+        <v>96.91014792156817</v>
+      </c>
+      <c r="E89">
+        <v>55.17400000000004</v>
+      </c>
+      <c r="F89">
+        <v>322.074</v>
+      </c>
+      <c r="G89">
+        <v>8.59</v>
+      </c>
+      <c r="H89">
+        <v>103.3</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>24.8</v>
+      </c>
+      <c r="K89">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L89">
+        <v>16.7</v>
+      </c>
+      <c r="M89">
+        <v>76.9112712</v>
+      </c>
+      <c r="N89">
+        <v>-60.2112712</v>
+      </c>
+      <c r="O89">
+        <v>-13.848592376</v>
+      </c>
+      <c r="P89">
+        <v>-46.362678824</v>
+      </c>
+      <c r="Q89">
+        <v>-38.262678824</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.5580441330260011</v>
+      </c>
+      <c r="T89">
+        <v>7.281107631083712</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.04994066461353716</v>
+      </c>
+      <c r="W89">
+        <v>0.2268741692902873</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.2171333244066833</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2719262645759301</v>
+      </c>
+      <c r="C90">
+        <v>-221.1072483014001</v>
+      </c>
+      <c r="D90">
+        <v>96.0787516985999</v>
+      </c>
+      <c r="E90">
+        <v>58.87600000000003</v>
+      </c>
+      <c r="F90">
+        <v>325.776</v>
+      </c>
+      <c r="G90">
+        <v>8.59</v>
+      </c>
+      <c r="H90">
+        <v>103.3</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>24.8</v>
+      </c>
+      <c r="K90">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L90">
+        <v>16.7</v>
+      </c>
+      <c r="M90">
+        <v>77.7953088</v>
+      </c>
+      <c r="N90">
+        <v>-61.0953088</v>
+      </c>
+      <c r="O90">
+        <v>-14.051921024</v>
+      </c>
+      <c r="P90">
+        <v>-47.043387776</v>
+      </c>
+      <c r="Q90">
+        <v>-38.943387776</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6013144774448345</v>
+      </c>
+      <c r="T90">
+        <v>7.88786660034069</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.0493731570611106</v>
+      </c>
+      <c r="W90">
+        <v>0.2270096900938068</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.2146659002656983</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2739262645759302</v>
+      </c>
+      <c r="C91">
+        <v>-225.6265006987185</v>
+      </c>
+      <c r="D91">
+        <v>95.26149930128148</v>
+      </c>
+      <c r="E91">
+        <v>62.57800000000003</v>
+      </c>
+      <c r="F91">
+        <v>329.478</v>
+      </c>
+      <c r="G91">
+        <v>8.59</v>
+      </c>
+      <c r="H91">
+        <v>103.3</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>24.8</v>
+      </c>
+      <c r="K91">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L91">
+        <v>16.7</v>
+      </c>
+      <c r="M91">
+        <v>78.6793464</v>
+      </c>
+      <c r="N91">
+        <v>-61.9793464</v>
+      </c>
+      <c r="O91">
+        <v>-14.255249672</v>
+      </c>
+      <c r="P91">
+        <v>-47.724096728</v>
+      </c>
+      <c r="Q91">
+        <v>-39.624096728</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.6524521572125468</v>
+      </c>
+      <c r="T91">
+        <v>8.604945382189843</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.04881840248739025</v>
+      </c>
+      <c r="W91">
+        <v>0.2271421654860112</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.2122539238582186</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2759262645759301</v>
+      </c>
+      <c r="C92">
+        <v>-230.1319671512572</v>
+      </c>
+      <c r="D92">
+        <v>94.45803284874285</v>
+      </c>
+      <c r="E92">
+        <v>66.28000000000003</v>
+      </c>
+      <c r="F92">
+        <v>333.18</v>
+      </c>
+      <c r="G92">
+        <v>8.59</v>
+      </c>
+      <c r="H92">
+        <v>103.3</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>24.8</v>
+      </c>
+      <c r="K92">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L92">
+        <v>16.7</v>
+      </c>
+      <c r="M92">
+        <v>79.563384</v>
+      </c>
+      <c r="N92">
+        <v>-62.863384</v>
+      </c>
+      <c r="O92">
+        <v>-14.45857832</v>
+      </c>
+      <c r="P92">
+        <v>-48.40480568</v>
+      </c>
+      <c r="Q92">
+        <v>-40.30480567999999</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.7138173729338015</v>
+      </c>
+      <c r="T92">
+        <v>9.465439920408828</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.04827597579308592</v>
+      </c>
+      <c r="W92">
+        <v>0.2272716969806111</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2098955469264606</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2779262645759301</v>
+      </c>
+      <c r="C93">
+        <v>-234.6239935669356</v>
+      </c>
+      <c r="D93">
+        <v>93.66800643306443</v>
+      </c>
+      <c r="E93">
+        <v>69.98200000000003</v>
+      </c>
+      <c r="F93">
+        <v>336.882</v>
+      </c>
+      <c r="G93">
+        <v>8.59</v>
+      </c>
+      <c r="H93">
+        <v>103.3</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>24.8</v>
+      </c>
+      <c r="K93">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L93">
+        <v>16.7</v>
+      </c>
+      <c r="M93">
+        <v>80.4474216</v>
+      </c>
+      <c r="N93">
+        <v>-63.7474216</v>
+      </c>
+      <c r="O93">
+        <v>-14.661906968</v>
+      </c>
+      <c r="P93">
+        <v>-49.085514632</v>
+      </c>
+      <c r="Q93">
+        <v>-40.985514632</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.7888193032597797</v>
+      </c>
+      <c r="T93">
+        <v>10.51715546712092</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.04774547056459047</v>
+      </c>
+      <c r="W93">
+        <v>0.2273983816291758</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2075890024547412</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2799262645759302</v>
+      </c>
+      <c r="C94">
+        <v>-239.1029143772654</v>
+      </c>
+      <c r="D94">
+        <v>92.89108562273464</v>
+      </c>
+      <c r="E94">
+        <v>73.68400000000003</v>
+      </c>
+      <c r="F94">
+        <v>340.584</v>
+      </c>
+      <c r="G94">
+        <v>8.59</v>
+      </c>
+      <c r="H94">
+        <v>103.3</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>24.8</v>
+      </c>
+      <c r="K94">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L94">
+        <v>16.7</v>
+      </c>
+      <c r="M94">
+        <v>81.33145920000001</v>
+      </c>
+      <c r="N94">
+        <v>-64.63145920000001</v>
+      </c>
+      <c r="O94">
+        <v>-14.865235616</v>
+      </c>
+      <c r="P94">
+        <v>-49.76622358400001</v>
+      </c>
+      <c r="Q94">
+        <v>-41.66622358400001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.8825717161672522</v>
+      </c>
+      <c r="T94">
+        <v>11.83179990051104</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.04722649805845361</v>
+      </c>
+      <c r="W94">
+        <v>0.2275223122636413</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2053326002541462</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2819262645759301</v>
+      </c>
+      <c r="C95">
+        <v>-243.5690530093852</v>
+      </c>
+      <c r="D95">
+        <v>92.12694699061475</v>
+      </c>
+      <c r="E95">
+        <v>77.38600000000002</v>
+      </c>
+      <c r="F95">
+        <v>344.286</v>
+      </c>
+      <c r="G95">
+        <v>8.59</v>
+      </c>
+      <c r="H95">
+        <v>103.3</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>24.8</v>
+      </c>
+      <c r="K95">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L95">
+        <v>16.7</v>
+      </c>
+      <c r="M95">
+        <v>82.21549680000001</v>
+      </c>
+      <c r="N95">
+        <v>-65.51549680000001</v>
+      </c>
+      <c r="O95">
+        <v>-15.068564264</v>
+      </c>
+      <c r="P95">
+        <v>-50.44693253600001</v>
+      </c>
+      <c r="Q95">
+        <v>-42.346932536</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.003110532762574</v>
+      </c>
+      <c r="T95">
+        <v>13.52205702915548</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.04671868625137347</v>
+      </c>
+      <c r="W95">
+        <v>0.227643577723172</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2031247228320586</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2839262645759301</v>
+      </c>
+      <c r="C96">
+        <v>-248.0227223349877</v>
+      </c>
+      <c r="D96">
+        <v>91.37527766501232</v>
+      </c>
+      <c r="E96">
+        <v>81.08800000000002</v>
+      </c>
+      <c r="F96">
+        <v>347.988</v>
+      </c>
+      <c r="G96">
+        <v>8.59</v>
+      </c>
+      <c r="H96">
+        <v>103.3</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>24.8</v>
+      </c>
+      <c r="K96">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L96">
+        <v>16.7</v>
+      </c>
+      <c r="M96">
+        <v>83.09953440000001</v>
+      </c>
+      <c r="N96">
+        <v>-66.39953440000001</v>
+      </c>
+      <c r="O96">
+        <v>-15.271892912</v>
+      </c>
+      <c r="P96">
+        <v>-51.12764148800001</v>
+      </c>
+      <c r="Q96">
+        <v>-43.02764148800001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.16382895488967</v>
+      </c>
+      <c r="T96">
+        <v>15.77573320068139</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.04622167895082694</v>
+      </c>
+      <c r="W96">
+        <v>0.2277622630665425</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2009638215253345</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2859262645759301</v>
+      </c>
+      <c r="C97">
+        <v>-252.4642250974464</v>
+      </c>
+      <c r="D97">
+        <v>90.63577490255354</v>
+      </c>
+      <c r="E97">
+        <v>84.79000000000002</v>
+      </c>
+      <c r="F97">
+        <v>351.69</v>
+      </c>
+      <c r="G97">
+        <v>8.59</v>
+      </c>
+      <c r="H97">
+        <v>103.3</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>24.8</v>
+      </c>
+      <c r="K97">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L97">
+        <v>16.7</v>
+      </c>
+      <c r="M97">
+        <v>83.98357200000001</v>
+      </c>
+      <c r="N97">
+        <v>-67.28357200000001</v>
+      </c>
+      <c r="O97">
+        <v>-15.47522156</v>
+      </c>
+      <c r="P97">
+        <v>-51.80835044000001</v>
+      </c>
+      <c r="Q97">
+        <v>-43.70835044</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.388834745867605</v>
+      </c>
+      <c r="T97">
+        <v>18.93087984081768</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.04573513496187087</v>
+      </c>
+      <c r="W97">
+        <v>0.2278784497711052</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1988484128776995</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2879262645759301</v>
+      </c>
+      <c r="C98">
+        <v>-256.8938543183705</v>
+      </c>
+      <c r="D98">
+        <v>89.90814568162948</v>
+      </c>
+      <c r="E98">
+        <v>88.49200000000002</v>
+      </c>
+      <c r="F98">
+        <v>355.392</v>
+      </c>
+      <c r="G98">
+        <v>8.59</v>
+      </c>
+      <c r="H98">
+        <v>103.3</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>24.8</v>
+      </c>
+      <c r="K98">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L98">
+        <v>16.7</v>
+      </c>
+      <c r="M98">
+        <v>84.86760960000001</v>
+      </c>
+      <c r="N98">
+        <v>-68.16760960000001</v>
+      </c>
+      <c r="O98">
+        <v>-15.678550208</v>
+      </c>
+      <c r="P98">
+        <v>-52.489059392</v>
+      </c>
+      <c r="Q98">
+        <v>-44.389059392</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.726343432334502</v>
+      </c>
+      <c r="T98">
+        <v>23.66359980102204</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.04525872730601804</v>
+      </c>
+      <c r="W98">
+        <v>0.2279922159193229</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1967770752435568</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2899262645759302</v>
+      </c>
+      <c r="C99">
+        <v>-261.3118936847304</v>
+      </c>
+      <c r="D99">
+        <v>89.19210631526964</v>
+      </c>
+      <c r="E99">
+        <v>92.19400000000002</v>
+      </c>
+      <c r="F99">
+        <v>359.094</v>
+      </c>
+      <c r="G99">
+        <v>8.59</v>
+      </c>
+      <c r="H99">
+        <v>103.3</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>24.8</v>
+      </c>
+      <c r="K99">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L99">
+        <v>16.7</v>
+      </c>
+      <c r="M99">
+        <v>85.75164720000001</v>
+      </c>
+      <c r="N99">
+        <v>-69.05164720000001</v>
+      </c>
+      <c r="O99">
+        <v>-15.881878856</v>
+      </c>
+      <c r="P99">
+        <v>-53.169768344</v>
+      </c>
+      <c r="Q99">
+        <v>-45.069768344</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.288857909779336</v>
+      </c>
+      <c r="T99">
+        <v>31.55146640136273</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.04479214248843023</v>
+      </c>
+      <c r="W99">
+        <v>0.2281036363737629</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1947484456018707</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2919262645759301</v>
+      </c>
+      <c r="C100">
+        <v>-265.718617917632</v>
+      </c>
+      <c r="D100">
+        <v>88.48738208236797</v>
+      </c>
+      <c r="E100">
+        <v>95.89600000000002</v>
+      </c>
+      <c r="F100">
+        <v>362.796</v>
+      </c>
+      <c r="G100">
+        <v>8.59</v>
+      </c>
+      <c r="H100">
+        <v>103.3</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>24.8</v>
+      </c>
+      <c r="K100">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L100">
+        <v>16.7</v>
+      </c>
+      <c r="M100">
+        <v>86.63568480000001</v>
+      </c>
+      <c r="N100">
+        <v>-69.9356848</v>
+      </c>
+      <c r="O100">
+        <v>-16.085207504</v>
+      </c>
+      <c r="P100">
+        <v>-53.85047729600001</v>
+      </c>
+      <c r="Q100">
+        <v>-45.75047729600001</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.413886864669005</v>
+      </c>
+      <c r="T100">
+        <v>47.3271996020441</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.04433507980997686</v>
+      </c>
+      <c r="W100">
+        <v>0.2282127829413775</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1927612165651168</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2939262645759301</v>
+      </c>
+      <c r="C101">
+        <v>-270.1142931237458</v>
+      </c>
+      <c r="D101">
+        <v>87.79370687625423</v>
+      </c>
+      <c r="E101">
+        <v>99.59800000000001</v>
+      </c>
+      <c r="F101">
+        <v>366.498</v>
+      </c>
+      <c r="G101">
+        <v>8.59</v>
+      </c>
+      <c r="H101">
+        <v>103.3</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>24.8</v>
+      </c>
+      <c r="K101">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="L101">
+        <v>16.7</v>
+      </c>
+      <c r="M101">
+        <v>87.51972240000001</v>
+      </c>
+      <c r="N101">
+        <v>-70.8197224</v>
+      </c>
+      <c r="O101">
+        <v>-16.288536152</v>
+      </c>
+      <c r="P101">
+        <v>-54.531186248</v>
+      </c>
+      <c r="Q101">
+        <v>-46.431186248</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.788973729338009</v>
+      </c>
+      <c r="T101">
+        <v>94.65439920408819</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.0438872507209872</v>
+      </c>
+      <c r="W101">
+        <v>0.2283197245278283</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.1908141335695096</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/israel/israel_recreation.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_recreation.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1037808793450012</v>
+        <v>0.1035768333225077</v>
       </c>
       <c r="C2">
-        <v>415.4720722072117</v>
+        <v>412.6510024600183</v>
       </c>
       <c r="D2">
-        <v>411.9720722072117</v>
+        <v>413.4270024600183</v>
       </c>
       <c r="E2">
-        <v>-290.6</v>
+        <v>-286.324</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.276000000000001</v>
       </c>
       <c r="G2">
         <v>3.5</v>
@@ -1451,28 +1451,28 @@
         <v>35</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2150828</v>
       </c>
       <c r="N2">
-        <v>35</v>
+        <v>34.7849172</v>
       </c>
       <c r="O2">
-        <v>8.050000000000001</v>
+        <v>8.000530956</v>
       </c>
       <c r="P2">
-        <v>26.95</v>
+        <v>26.784386244</v>
       </c>
       <c r="Q2">
-        <v>35.55</v>
+        <v>35.38438624400001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1037808793450012</v>
+        <v>0.1042318417399068</v>
       </c>
       <c r="T2">
-        <v>0.8969457633378592</v>
+        <v>0.9039220081638205</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>162.7280284615971</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1035768333225077</v>
+        <v>0.1033727873000142</v>
       </c>
       <c r="C3">
-        <v>412.6510024600183</v>
+        <v>409.8402456660452</v>
       </c>
       <c r="D3">
-        <v>413.4270024600183</v>
+        <v>414.8922456660453</v>
       </c>
       <c r="E3">
-        <v>-286.324</v>
+        <v>-282.048</v>
       </c>
       <c r="F3">
-        <v>4.276000000000001</v>
+        <v>8.552000000000001</v>
       </c>
       <c r="G3">
         <v>3.5</v>
@@ -1533,28 +1533,28 @@
         <v>35</v>
       </c>
       <c r="M3">
-        <v>0.2150828</v>
+        <v>0.4301656</v>
       </c>
       <c r="N3">
-        <v>34.7849172</v>
+        <v>34.5698344</v>
       </c>
       <c r="O3">
-        <v>8.000530956</v>
+        <v>7.951061912</v>
       </c>
       <c r="P3">
-        <v>26.784386244</v>
+        <v>26.618772488</v>
       </c>
       <c r="Q3">
-        <v>35.38438624400001</v>
+        <v>35.218772488</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1042318417399068</v>
+        <v>0.1046920074489941</v>
       </c>
       <c r="T3">
-        <v>0.9039220081638205</v>
+        <v>0.9110406253331685</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>162.7280284615971</v>
+        <v>81.36401423079855</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1033727873000142</v>
+        <v>0.1031687412775208</v>
       </c>
       <c r="C4">
-        <v>409.8402456660452</v>
+        <v>407.0399118669476</v>
       </c>
       <c r="D4">
-        <v>414.8922456660453</v>
+        <v>416.3679118669476</v>
       </c>
       <c r="E4">
-        <v>-282.048</v>
+        <v>-277.772</v>
       </c>
       <c r="F4">
-        <v>8.552000000000001</v>
+        <v>12.828</v>
       </c>
       <c r="G4">
         <v>3.5</v>
@@ -1615,28 +1615,28 @@
         <v>35</v>
       </c>
       <c r="M4">
-        <v>0.4301656</v>
+        <v>0.6452483999999999</v>
       </c>
       <c r="N4">
-        <v>34.5698344</v>
+        <v>34.3547516</v>
       </c>
       <c r="O4">
-        <v>7.951061912</v>
+        <v>7.901592868000001</v>
       </c>
       <c r="P4">
-        <v>26.618772488</v>
+        <v>26.453158732</v>
       </c>
       <c r="Q4">
-        <v>35.218772488</v>
+        <v>35.053158732</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1046920074489941</v>
+        <v>0.1051616611108461</v>
       </c>
       <c r="T4">
-        <v>0.9110406253331685</v>
+        <v>0.9183060181142557</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>81.36401423079855</v>
+        <v>54.24267615386571</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1031687412775208</v>
+        <v>0.1029646952550272</v>
       </c>
       <c r="C5">
-        <v>407.0399118669476</v>
+        <v>404.25011267553</v>
       </c>
       <c r="D5">
-        <v>416.3679118669476</v>
+        <v>417.85411267553</v>
       </c>
       <c r="E5">
-        <v>-277.772</v>
+        <v>-273.496</v>
       </c>
       <c r="F5">
-        <v>12.828</v>
+        <v>17.104</v>
       </c>
       <c r="G5">
         <v>3.5</v>
@@ -1697,28 +1697,28 @@
         <v>35</v>
       </c>
       <c r="M5">
-        <v>0.6452483999999999</v>
+        <v>0.8603312000000001</v>
       </c>
       <c r="N5">
-        <v>34.3547516</v>
+        <v>34.1396688</v>
       </c>
       <c r="O5">
-        <v>7.901592868000001</v>
+        <v>7.852123824000001</v>
       </c>
       <c r="P5">
-        <v>26.453158732</v>
+        <v>26.287544976</v>
       </c>
       <c r="Q5">
-        <v>35.053158732</v>
+        <v>34.887544976</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1051616611108461</v>
+        <v>0.1056410992239867</v>
       </c>
       <c r="T5">
-        <v>0.9183060181142557</v>
+        <v>0.9257227732449488</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>54.24267615386571</v>
+        <v>40.68200711539928</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1029646952550272</v>
+        <v>0.1027606492325337</v>
       </c>
       <c r="C6">
-        <v>404.25011267553</v>
+        <v>401.4709613038861</v>
       </c>
       <c r="D6">
-        <v>417.85411267553</v>
+        <v>419.3509613038861</v>
       </c>
       <c r="E6">
-        <v>-273.496</v>
+        <v>-269.22</v>
       </c>
       <c r="F6">
-        <v>17.104</v>
+        <v>21.38</v>
       </c>
       <c r="G6">
         <v>3.5</v>
@@ -1779,28 +1779,28 @@
         <v>35</v>
       </c>
       <c r="M6">
-        <v>0.8603312000000001</v>
+        <v>1.075414</v>
       </c>
       <c r="N6">
-        <v>34.1396688</v>
+        <v>33.924586</v>
       </c>
       <c r="O6">
-        <v>7.852123824000001</v>
+        <v>7.80265478</v>
       </c>
       <c r="P6">
-        <v>26.287544976</v>
+        <v>26.12193122</v>
       </c>
       <c r="Q6">
-        <v>34.887544976</v>
+        <v>34.72193122</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1056410992239867</v>
+        <v>0.1061306307710881</v>
       </c>
       <c r="T6">
-        <v>0.9257227732449488</v>
+        <v>0.9332956705889199</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>40.68200711539928</v>
+        <v>32.54560569231942</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1027606492325337</v>
+        <v>0.1025566032100402</v>
       </c>
       <c r="C7">
-        <v>401.4709613038861</v>
+        <v>398.7025725921484</v>
       </c>
       <c r="D7">
-        <v>419.3509613038861</v>
+        <v>420.8585725921484</v>
       </c>
       <c r="E7">
-        <v>-269.22</v>
+        <v>-264.944</v>
       </c>
       <c r="F7">
-        <v>21.38</v>
+        <v>25.656</v>
       </c>
       <c r="G7">
         <v>3.5</v>
@@ -1861,28 +1861,28 @@
         <v>35</v>
       </c>
       <c r="M7">
-        <v>1.075414</v>
+        <v>1.2904968</v>
       </c>
       <c r="N7">
-        <v>33.924586</v>
+        <v>33.7095032</v>
       </c>
       <c r="O7">
-        <v>7.80265478</v>
+        <v>7.753185736000001</v>
       </c>
       <c r="P7">
-        <v>26.12193122</v>
+        <v>25.956317464</v>
       </c>
       <c r="Q7">
-        <v>34.72193122</v>
+        <v>34.556317464</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1061306307710881</v>
+        <v>0.1066305778830215</v>
       </c>
       <c r="T7">
-        <v>0.9332956705889199</v>
+        <v>0.9410296934082946</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>32.54560569231942</v>
+        <v>27.12133807693285</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1025566032100402</v>
+        <v>0.1023525571875467</v>
       </c>
       <c r="C8">
-        <v>398.7025725921484</v>
+        <v>395.9450630378576</v>
       </c>
       <c r="D8">
-        <v>420.8585725921484</v>
+        <v>422.3770630378576</v>
       </c>
       <c r="E8">
-        <v>-264.944</v>
+        <v>-260.668</v>
       </c>
       <c r="F8">
-        <v>25.656</v>
+        <v>29.932</v>
       </c>
       <c r="G8">
         <v>3.5</v>
@@ -1943,28 +1943,28 @@
         <v>35</v>
       </c>
       <c r="M8">
-        <v>1.2904968</v>
+        <v>1.5055796</v>
       </c>
       <c r="N8">
-        <v>33.7095032</v>
+        <v>33.4944204</v>
       </c>
       <c r="O8">
-        <v>7.753185736000001</v>
+        <v>7.703716692000001</v>
       </c>
       <c r="P8">
-        <v>25.956317464</v>
+        <v>25.790703708</v>
       </c>
       <c r="Q8">
-        <v>34.556317464</v>
+        <v>34.390703708</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1066305778830215</v>
+        <v>0.1071412765457492</v>
       </c>
       <c r="T8">
-        <v>0.9410296934082943</v>
+        <v>0.9489300392990534</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>27.12133807693285</v>
+        <v>23.24686120879959</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1023525571875467</v>
+        <v>0.1021485111650532</v>
       </c>
       <c r="C9">
-        <v>395.9450630378577</v>
+        <v>393.1985508259719</v>
       </c>
       <c r="D9">
-        <v>422.3770630378577</v>
+        <v>423.9065508259719</v>
       </c>
       <c r="E9">
-        <v>-260.668</v>
+        <v>-256.392</v>
       </c>
       <c r="F9">
-        <v>29.93200000000001</v>
+        <v>34.20800000000001</v>
       </c>
       <c r="G9">
         <v>3.5</v>
@@ -2025,28 +2025,28 @@
         <v>35</v>
       </c>
       <c r="M9">
-        <v>1.5055796</v>
+        <v>1.7206624</v>
       </c>
       <c r="N9">
-        <v>33.4944204</v>
+        <v>33.2793376</v>
       </c>
       <c r="O9">
-        <v>7.703716692000001</v>
+        <v>7.654247648</v>
       </c>
       <c r="P9">
-        <v>25.790703708</v>
+        <v>25.625089952</v>
       </c>
       <c r="Q9">
-        <v>34.390703708</v>
+        <v>34.225089952</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1071412765457492</v>
+        <v>0.1076630773533187</v>
       </c>
       <c r="T9">
-        <v>0.9489300392990534</v>
+        <v>0.9570021318396115</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>23.24686120879959</v>
+        <v>20.34100355769964</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1021485111650532</v>
+        <v>0.1019444651425597</v>
       </c>
       <c r="C10">
-        <v>393.1985508259719</v>
+        <v>390.4631558595285</v>
       </c>
       <c r="D10">
-        <v>423.9065508259719</v>
+        <v>425.4471558595285</v>
       </c>
       <c r="E10">
-        <v>-256.392</v>
+        <v>-252.116</v>
       </c>
       <c r="F10">
-        <v>34.20800000000001</v>
+        <v>38.484</v>
       </c>
       <c r="G10">
         <v>3.5</v>
@@ -2107,28 +2107,28 @@
         <v>35</v>
       </c>
       <c r="M10">
-        <v>1.7206624</v>
+        <v>1.9357452</v>
       </c>
       <c r="N10">
-        <v>33.2793376</v>
+        <v>33.0642548</v>
       </c>
       <c r="O10">
-        <v>7.654247648</v>
+        <v>7.604778604000001</v>
       </c>
       <c r="P10">
-        <v>25.625089952</v>
+        <v>25.459476196</v>
       </c>
       <c r="Q10">
-        <v>34.225089952</v>
+        <v>34.05947619600001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1076630773533187</v>
+        <v>0.1081963463105052</v>
       </c>
       <c r="T10">
-        <v>0.9570021318396115</v>
+        <v>0.9652516330074348</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>20.34100355769964</v>
+        <v>18.08089205128857</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1019444651425597</v>
+        <v>0.1017404191200662</v>
       </c>
       <c r="C11">
-        <v>390.4631558595285</v>
+        <v>387.7389997909797</v>
       </c>
       <c r="D11">
-        <v>425.4471558595285</v>
+        <v>426.9989997909797</v>
       </c>
       <c r="E11">
-        <v>-252.116</v>
+        <v>-247.84</v>
       </c>
       <c r="F11">
-        <v>38.484</v>
+        <v>42.76</v>
       </c>
       <c r="G11">
         <v>3.5</v>
@@ -2189,28 +2189,28 @@
         <v>35</v>
       </c>
       <c r="M11">
-        <v>1.9357452</v>
+        <v>2.150828</v>
       </c>
       <c r="N11">
-        <v>33.0642548</v>
+        <v>32.849172</v>
       </c>
       <c r="O11">
-        <v>7.604778604000001</v>
+        <v>7.555309560000001</v>
       </c>
       <c r="P11">
-        <v>25.459476196</v>
+        <v>25.29386244</v>
       </c>
       <c r="Q11">
-        <v>34.05947619600001</v>
+        <v>33.89386244000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1081963463105052</v>
+        <v>0.1087414656889625</v>
       </c>
       <c r="T11">
-        <v>0.9652516330074348</v>
+        <v>0.9736844564234317</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.08089205128857</v>
+        <v>16.27280284615971</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1017404191200662</v>
+        <v>0.1015363730975727</v>
       </c>
       <c r="C12">
-        <v>387.7389997909797</v>
+        <v>385.0262060542134</v>
       </c>
       <c r="D12">
-        <v>426.9989997909797</v>
+        <v>428.5622060542134</v>
       </c>
       <c r="E12">
-        <v>-247.84</v>
+        <v>-243.564</v>
       </c>
       <c r="F12">
-        <v>42.76000000000001</v>
+        <v>47.036</v>
       </c>
       <c r="G12">
         <v>3.5</v>
@@ -2271,28 +2271,28 @@
         <v>35</v>
       </c>
       <c r="M12">
-        <v>2.150828</v>
+        <v>2.3659108</v>
       </c>
       <c r="N12">
-        <v>32.849172</v>
+        <v>32.6340892</v>
       </c>
       <c r="O12">
-        <v>7.555309560000001</v>
+        <v>7.505840516</v>
       </c>
       <c r="P12">
-        <v>25.29386244</v>
+        <v>25.128248684</v>
       </c>
       <c r="Q12">
-        <v>33.89386244000001</v>
+        <v>33.728248684</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1087414656889625</v>
+        <v>0.1092988349410929</v>
       </c>
       <c r="T12">
-        <v>0.9736844564234317</v>
+        <v>0.9823067814892263</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.27280284615971</v>
+        <v>14.79345713287247</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1015363730975727</v>
+        <v>0.1013323270750792</v>
       </c>
       <c r="C13">
-        <v>385.0262060542134</v>
+        <v>382.3248998972821</v>
       </c>
       <c r="D13">
-        <v>428.5622060542134</v>
+        <v>430.1368998972821</v>
       </c>
       <c r="E13">
-        <v>-243.564</v>
+        <v>-239.288</v>
       </c>
       <c r="F13">
-        <v>47.036</v>
+        <v>51.312</v>
       </c>
       <c r="G13">
         <v>3.5</v>
@@ -2353,28 +2353,28 @@
         <v>35</v>
       </c>
       <c r="M13">
-        <v>2.3659108</v>
+        <v>2.5809936</v>
       </c>
       <c r="N13">
-        <v>32.6340892</v>
+        <v>32.4190064</v>
       </c>
       <c r="O13">
-        <v>7.505840516</v>
+        <v>7.456371472000001</v>
       </c>
       <c r="P13">
-        <v>25.128248684</v>
+        <v>24.962634928</v>
       </c>
       <c r="Q13">
-        <v>33.728248684</v>
+        <v>33.562634928</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1092988349410929</v>
+        <v>0.1098688716762264</v>
       </c>
       <c r="T13">
-        <v>0.9823067814892263</v>
+        <v>0.9911250684883345</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.79345713287247</v>
+        <v>13.56066903846643</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1013323270750792</v>
+        <v>0.1012784310525857</v>
       </c>
       <c r="C14">
-        <v>382.3248998972821</v>
+        <v>378.4667680235487</v>
       </c>
       <c r="D14">
-        <v>430.1368998972821</v>
+        <v>430.5547680235487</v>
       </c>
       <c r="E14">
-        <v>-239.288</v>
+        <v>-235.012</v>
       </c>
       <c r="F14">
-        <v>51.312</v>
+        <v>55.58800000000001</v>
       </c>
       <c r="G14">
         <v>3.5</v>
@@ -2435,45 +2435,45 @@
         <v>35</v>
       </c>
       <c r="M14">
-        <v>2.5809936</v>
+        <v>2.8794584</v>
       </c>
       <c r="N14">
-        <v>32.4190064</v>
+        <v>32.1205416</v>
       </c>
       <c r="O14">
-        <v>7.456371472000001</v>
+        <v>7.387724568000001</v>
       </c>
       <c r="P14">
-        <v>24.962634928</v>
+        <v>24.732817032</v>
       </c>
       <c r="Q14">
-        <v>33.562634928</v>
+        <v>33.332817032</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1098688716762264</v>
+        <v>0.1104520127041215</v>
       </c>
       <c r="T14">
-        <v>0.9911250684883345</v>
+        <v>1.000146074728801</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.23</v>
       </c>
       <c r="W14">
-        <v>0.038731</v>
+        <v>0.039886</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>13.56066903846643</v>
+        <v>12.15506360501683</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1012784310525857</v>
+        <v>0.1010859350300922</v>
       </c>
       <c r="C15">
-        <v>378.4667680235487</v>
+        <v>375.6898849375527</v>
       </c>
       <c r="D15">
-        <v>430.5547680235487</v>
+        <v>432.0538849375528</v>
       </c>
       <c r="E15">
-        <v>-235.012</v>
+        <v>-230.736</v>
       </c>
       <c r="F15">
-        <v>55.58800000000001</v>
+        <v>59.86400000000001</v>
       </c>
       <c r="G15">
         <v>3.5</v>
@@ -2517,28 +2517,28 @@
         <v>35</v>
       </c>
       <c r="M15">
-        <v>2.8794584</v>
+        <v>3.1009552</v>
       </c>
       <c r="N15">
-        <v>32.1205416</v>
+        <v>31.8990448</v>
       </c>
       <c r="O15">
-        <v>7.387724568000001</v>
+        <v>7.336780304</v>
       </c>
       <c r="P15">
-        <v>24.732817032</v>
+        <v>24.562264496</v>
       </c>
       <c r="Q15">
-        <v>33.332817032</v>
+        <v>33.162264496</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1104520127041215</v>
+        <v>0.11104871515127</v>
       </c>
       <c r="T15">
-        <v>1.000146074728801</v>
+        <v>1.00937687181207</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>12.15506360501683</v>
+        <v>11.28684477608706</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1010859350300922</v>
+        <v>0.1008934390075987</v>
       </c>
       <c r="C16">
-        <v>375.6898849375527</v>
+        <v>372.9234776558775</v>
       </c>
       <c r="D16">
-        <v>432.0538849375528</v>
+        <v>433.5634776558775</v>
       </c>
       <c r="E16">
-        <v>-230.736</v>
+        <v>-226.46</v>
       </c>
       <c r="F16">
-        <v>59.86400000000001</v>
+        <v>64.14000000000001</v>
       </c>
       <c r="G16">
         <v>3.5</v>
@@ -2599,28 +2599,28 @@
         <v>35</v>
       </c>
       <c r="M16">
-        <v>3.1009552</v>
+        <v>3.322452000000001</v>
       </c>
       <c r="N16">
-        <v>31.8990448</v>
+        <v>31.677548</v>
       </c>
       <c r="O16">
-        <v>7.336780304</v>
+        <v>7.28583604</v>
       </c>
       <c r="P16">
-        <v>24.562264496</v>
+        <v>24.39171196</v>
       </c>
       <c r="Q16">
-        <v>33.162264496</v>
+        <v>32.99171196</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.11104871515127</v>
+        <v>0.1116594576559985</v>
       </c>
       <c r="T16">
-        <v>1.00937687181207</v>
+        <v>1.018824864120827</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.28684477608706</v>
+        <v>10.53438845768125</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1008934390075987</v>
+        <v>0.1007009429851052</v>
       </c>
       <c r="C17">
-        <v>372.9234776558775</v>
+        <v>370.1676563706559</v>
       </c>
       <c r="D17">
-        <v>433.5634776558775</v>
+        <v>435.0836563706559</v>
       </c>
       <c r="E17">
-        <v>-226.46</v>
+        <v>-222.184</v>
       </c>
       <c r="F17">
-        <v>64.14</v>
+        <v>68.41600000000001</v>
       </c>
       <c r="G17">
         <v>3.5</v>
@@ -2681,28 +2681,28 @@
         <v>35</v>
       </c>
       <c r="M17">
-        <v>3.322452</v>
+        <v>3.5439488</v>
       </c>
       <c r="N17">
-        <v>31.677548</v>
+        <v>31.4560512</v>
       </c>
       <c r="O17">
-        <v>7.28583604</v>
+        <v>7.234891776</v>
       </c>
       <c r="P17">
-        <v>24.39171196</v>
+        <v>24.221159424</v>
       </c>
       <c r="Q17">
-        <v>32.99171196</v>
+        <v>32.821159424</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1116594576559985</v>
+        <v>0.1122847416489348</v>
       </c>
       <c r="T17">
-        <v>1.018824864120827</v>
+        <v>1.028497808627412</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.53438845768126</v>
+        <v>9.875989179076175</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1007009429851052</v>
+        <v>0.1007309769626117</v>
       </c>
       <c r="C18">
-        <v>370.1676563706559</v>
+        <v>365.6537706917285</v>
       </c>
       <c r="D18">
-        <v>435.0836563706559</v>
+        <v>434.8457706917285</v>
       </c>
       <c r="E18">
-        <v>-222.184</v>
+        <v>-217.908</v>
       </c>
       <c r="F18">
-        <v>68.41600000000001</v>
+        <v>72.69200000000001</v>
       </c>
       <c r="G18">
         <v>3.5</v>
@@ -2763,45 +2763,45 @@
         <v>35</v>
       </c>
       <c r="M18">
-        <v>3.5439488</v>
+        <v>3.889022</v>
       </c>
       <c r="N18">
-        <v>31.4560512</v>
+        <v>31.110978</v>
       </c>
       <c r="O18">
-        <v>7.234891776</v>
+        <v>7.15552494</v>
       </c>
       <c r="P18">
-        <v>24.221159424</v>
+        <v>23.95545306</v>
       </c>
       <c r="Q18">
-        <v>32.821159424</v>
+        <v>32.55545306</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1122847416489348</v>
+        <v>0.1129250927260382</v>
       </c>
       <c r="T18">
-        <v>1.028497808627412</v>
+        <v>1.038403836134155</v>
       </c>
       <c r="U18">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V18">
         <v>0.23</v>
       </c>
       <c r="W18">
-        <v>0.039886</v>
+        <v>0.041195</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>9.875989179076175</v>
+        <v>8.999691953401136</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1007309769626117</v>
+        <v>0.1005515709401182</v>
       </c>
       <c r="C19">
-        <v>365.6537706917285</v>
+        <v>362.8026421388556</v>
       </c>
       <c r="D19">
-        <v>434.8457706917285</v>
+        <v>436.2706421388556</v>
       </c>
       <c r="E19">
-        <v>-217.908</v>
+        <v>-213.632</v>
       </c>
       <c r="F19">
-        <v>72.69200000000001</v>
+        <v>76.96800000000002</v>
       </c>
       <c r="G19">
         <v>3.5</v>
@@ -2845,28 +2845,28 @@
         <v>35</v>
       </c>
       <c r="M19">
-        <v>3.889022</v>
+        <v>4.117788000000001</v>
       </c>
       <c r="N19">
-        <v>31.110978</v>
+        <v>30.882212</v>
       </c>
       <c r="O19">
-        <v>7.15552494</v>
+        <v>7.10290876</v>
       </c>
       <c r="P19">
-        <v>23.95545306</v>
+        <v>23.77930324</v>
       </c>
       <c r="Q19">
-        <v>32.55545306</v>
+        <v>32.37930324</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1129250927260382</v>
+        <v>0.1135810621220954</v>
       </c>
       <c r="T19">
-        <v>1.038403836134155</v>
+        <v>1.048551474067893</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.999691953401136</v>
+        <v>8.499709067101072</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1005515709401182</v>
+        <v>0.1003721649176247</v>
       </c>
       <c r="C20">
-        <v>362.8026421388556</v>
+        <v>359.9608821173313</v>
       </c>
       <c r="D20">
-        <v>436.2706421388556</v>
+        <v>437.7048821173312</v>
       </c>
       <c r="E20">
-        <v>-213.632</v>
+        <v>-209.356</v>
       </c>
       <c r="F20">
-        <v>76.968</v>
+        <v>81.244</v>
       </c>
       <c r="G20">
         <v>3.5</v>
@@ -2927,28 +2927,28 @@
         <v>35</v>
       </c>
       <c r="M20">
-        <v>4.117788</v>
+        <v>4.346554</v>
       </c>
       <c r="N20">
-        <v>30.882212</v>
+        <v>30.653446</v>
       </c>
       <c r="O20">
-        <v>7.10290876</v>
+        <v>7.05029258</v>
       </c>
       <c r="P20">
-        <v>23.77930324</v>
+        <v>23.60315342</v>
       </c>
       <c r="Q20">
-        <v>32.37930324</v>
+        <v>32.20315342</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1135810621220954</v>
+        <v>0.1142532282933638</v>
       </c>
       <c r="T20">
-        <v>1.048551474067893</v>
+        <v>1.058949670962956</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.499709067101074</v>
+        <v>8.052355958306281</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1003721649176247</v>
+        <v>0.1001927588951312</v>
       </c>
       <c r="C21">
-        <v>359.9608821173313</v>
+        <v>357.128583329069</v>
       </c>
       <c r="D21">
-        <v>437.7048821173312</v>
+        <v>439.148583329069</v>
       </c>
       <c r="E21">
-        <v>-209.356</v>
+        <v>-205.08</v>
       </c>
       <c r="F21">
-        <v>81.244</v>
+        <v>85.52000000000001</v>
       </c>
       <c r="G21">
         <v>3.5</v>
@@ -3009,28 +3009,28 @@
         <v>35</v>
       </c>
       <c r="M21">
-        <v>4.346554</v>
+        <v>4.57532</v>
       </c>
       <c r="N21">
-        <v>30.653446</v>
+        <v>30.42468</v>
       </c>
       <c r="O21">
-        <v>7.05029258</v>
+        <v>6.9976764</v>
       </c>
       <c r="P21">
-        <v>23.60315342</v>
+        <v>23.4270036</v>
       </c>
       <c r="Q21">
-        <v>32.20315342</v>
+        <v>32.0270036</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1142532282933638</v>
+        <v>0.114942198618914</v>
       </c>
       <c r="T21">
-        <v>1.058949670962956</v>
+        <v>1.069607822780397</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.052355958306281</v>
+        <v>7.649738160390966</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1001927588951312</v>
+        <v>0.1001427128726377</v>
       </c>
       <c r="C22">
-        <v>357.128583329069</v>
+        <v>353.2570099525757</v>
       </c>
       <c r="D22">
-        <v>439.148583329069</v>
+        <v>439.5530099525757</v>
       </c>
       <c r="E22">
-        <v>-205.08</v>
+        <v>-200.804</v>
       </c>
       <c r="F22">
-        <v>85.52000000000001</v>
+        <v>89.79600000000001</v>
       </c>
       <c r="G22">
         <v>3.5</v>
@@ -3091,45 +3091,45 @@
         <v>35</v>
       </c>
       <c r="M22">
-        <v>4.57532</v>
+        <v>4.875922800000001</v>
       </c>
       <c r="N22">
-        <v>30.42468</v>
+        <v>30.1240772</v>
       </c>
       <c r="O22">
-        <v>6.9976764</v>
+        <v>6.928537756</v>
       </c>
       <c r="P22">
-        <v>23.4270036</v>
+        <v>23.195539444</v>
       </c>
       <c r="Q22">
-        <v>32.0270036</v>
+        <v>31.795539444</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.114942198618914</v>
+        <v>0.1156486112311869</v>
       </c>
       <c r="T22">
-        <v>1.069607822780397</v>
+        <v>1.080535801226127</v>
       </c>
       <c r="U22">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0.23</v>
       </c>
       <c r="W22">
-        <v>0.041195</v>
+        <v>0.041811</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.649738160390966</v>
+        <v>7.178128414994593</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1001427128726377</v>
+        <v>0.0999694668501442</v>
       </c>
       <c r="C23">
-        <v>353.2570099525757</v>
+        <v>350.3867983990449</v>
       </c>
       <c r="D23">
-        <v>439.5530099525757</v>
+        <v>440.9587983990449</v>
       </c>
       <c r="E23">
-        <v>-200.804</v>
+        <v>-196.528</v>
       </c>
       <c r="F23">
-        <v>89.79600000000001</v>
+        <v>94.072</v>
       </c>
       <c r="G23">
         <v>3.5</v>
@@ -3173,28 +3173,28 @@
         <v>35</v>
       </c>
       <c r="M23">
-        <v>4.875922800000001</v>
+        <v>5.108109600000001</v>
       </c>
       <c r="N23">
-        <v>30.1240772</v>
+        <v>29.8918904</v>
       </c>
       <c r="O23">
-        <v>6.928537756</v>
+        <v>6.875134792000001</v>
       </c>
       <c r="P23">
-        <v>23.195539444</v>
+        <v>23.016755608</v>
       </c>
       <c r="Q23">
-        <v>31.795539444</v>
+        <v>31.616755608</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1156486112311869</v>
+        <v>0.1163731369873643</v>
       </c>
       <c r="T23">
-        <v>1.080535801226127</v>
+        <v>1.091743984247389</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.178128414994593</v>
+        <v>6.851849850676657</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0999694668501442</v>
+        <v>0.09979622082765068</v>
       </c>
       <c r="C24">
-        <v>350.3867983990449</v>
+        <v>347.52560774561</v>
       </c>
       <c r="D24">
-        <v>440.9587983990449</v>
+        <v>442.3736077456101</v>
       </c>
       <c r="E24">
-        <v>-196.528</v>
+        <v>-192.252</v>
       </c>
       <c r="F24">
-        <v>94.072</v>
+        <v>98.34800000000001</v>
       </c>
       <c r="G24">
         <v>3.5</v>
@@ -3255,28 +3255,28 @@
         <v>35</v>
       </c>
       <c r="M24">
-        <v>5.108109600000001</v>
+        <v>5.340296400000001</v>
       </c>
       <c r="N24">
-        <v>29.8918904</v>
+        <v>29.6597036</v>
       </c>
       <c r="O24">
-        <v>6.875134792000001</v>
+        <v>6.821731828000001</v>
       </c>
       <c r="P24">
-        <v>23.016755608</v>
+        <v>22.837971772</v>
       </c>
       <c r="Q24">
-        <v>31.616755608</v>
+        <v>31.437971772</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1163731369873643</v>
+        <v>0.1171164815943515</v>
       </c>
       <c r="T24">
-        <v>1.091743984247389</v>
+        <v>1.103243288905567</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.851849850676657</v>
+        <v>6.553943335429846</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09979622082765068</v>
+        <v>0.09962297480515718</v>
       </c>
       <c r="C25">
-        <v>347.52560774561</v>
+        <v>344.6735251020078</v>
       </c>
       <c r="D25">
-        <v>442.3736077456101</v>
+        <v>443.7975251020078</v>
       </c>
       <c r="E25">
-        <v>-192.252</v>
+        <v>-187.976</v>
       </c>
       <c r="F25">
-        <v>98.34800000000001</v>
+        <v>102.624</v>
       </c>
       <c r="G25">
         <v>3.5</v>
@@ -3337,28 +3337,28 @@
         <v>35</v>
       </c>
       <c r="M25">
-        <v>5.340296400000001</v>
+        <v>5.572483200000001</v>
       </c>
       <c r="N25">
-        <v>29.6597036</v>
+        <v>29.4275168</v>
       </c>
       <c r="O25">
-        <v>6.821731828000001</v>
+        <v>6.768328864</v>
       </c>
       <c r="P25">
-        <v>22.837971772</v>
+        <v>22.659187936</v>
       </c>
       <c r="Q25">
-        <v>31.437971772</v>
+        <v>31.259187936</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1171164815943515</v>
+        <v>0.1178793879015226</v>
       </c>
       <c r="T25">
-        <v>1.103243288905567</v>
+        <v>1.115045206844223</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.553943335429846</v>
+        <v>6.280862363120269</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09962297480515718</v>
+        <v>0.09964222878266367</v>
       </c>
       <c r="C26">
-        <v>344.6735251020078</v>
+        <v>340.2388231359313</v>
       </c>
       <c r="D26">
-        <v>443.7975251020078</v>
+        <v>443.6388231359313</v>
       </c>
       <c r="E26">
-        <v>-187.976</v>
+        <v>-183.7</v>
       </c>
       <c r="F26">
-        <v>102.624</v>
+        <v>106.9</v>
       </c>
       <c r="G26">
         <v>3.5</v>
@@ -3419,45 +3419,45 @@
         <v>35</v>
       </c>
       <c r="M26">
-        <v>5.5724832</v>
+        <v>5.91157</v>
       </c>
       <c r="N26">
-        <v>29.4275168</v>
+        <v>29.08843</v>
       </c>
       <c r="O26">
-        <v>6.768328864</v>
+        <v>6.6903389</v>
       </c>
       <c r="P26">
-        <v>22.659187936</v>
+        <v>22.3980911</v>
       </c>
       <c r="Q26">
-        <v>31.259187936</v>
+        <v>30.9980911</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1178793879015226</v>
+        <v>0.1186626383768849</v>
       </c>
       <c r="T26">
-        <v>1.115045206844223</v>
+        <v>1.127161842594576</v>
       </c>
       <c r="U26">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V26">
         <v>0.23</v>
       </c>
       <c r="W26">
-        <v>0.041811</v>
+        <v>0.042581</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>6.28086236312027</v>
+        <v>5.92059300659554</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09964222878266367</v>
+        <v>0.09947668276017016</v>
       </c>
       <c r="C27">
-        <v>340.2388231359313</v>
+        <v>337.3310642197181</v>
       </c>
       <c r="D27">
-        <v>443.6388231359313</v>
+        <v>445.0070642197181</v>
       </c>
       <c r="E27">
-        <v>-183.7</v>
+        <v>-179.424</v>
       </c>
       <c r="F27">
-        <v>106.9</v>
+        <v>111.176</v>
       </c>
       <c r="G27">
         <v>3.5</v>
@@ -3501,28 +3501,28 @@
         <v>35</v>
       </c>
       <c r="M27">
-        <v>5.91157</v>
+        <v>6.148032800000001</v>
       </c>
       <c r="N27">
-        <v>29.08843</v>
+        <v>28.8519672</v>
       </c>
       <c r="O27">
-        <v>6.6903389</v>
+        <v>6.635952456</v>
       </c>
       <c r="P27">
-        <v>22.3980911</v>
+        <v>22.216014744</v>
       </c>
       <c r="Q27">
-        <v>30.9980911</v>
+        <v>30.816014744</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1186626383768849</v>
+        <v>0.1194670577840137</v>
       </c>
       <c r="T27">
-        <v>1.127161842594576</v>
+        <v>1.139605954986831</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.92059300659554</v>
+        <v>5.692877890957249</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09947668276017016</v>
+        <v>0.09931113673767666</v>
       </c>
       <c r="C28">
-        <v>337.3310642197181</v>
+        <v>334.4317710877525</v>
       </c>
       <c r="D28">
-        <v>445.0070642197181</v>
+        <v>446.3837710877525</v>
       </c>
       <c r="E28">
-        <v>-179.424</v>
+        <v>-175.148</v>
       </c>
       <c r="F28">
-        <v>111.176</v>
+        <v>115.452</v>
       </c>
       <c r="G28">
         <v>3.5</v>
@@ -3583,28 +3583,28 @@
         <v>35</v>
       </c>
       <c r="M28">
-        <v>6.148032800000001</v>
+        <v>6.384495600000001</v>
       </c>
       <c r="N28">
-        <v>28.8519672</v>
+        <v>28.6155044</v>
       </c>
       <c r="O28">
-        <v>6.635952456</v>
+        <v>6.581566012</v>
       </c>
       <c r="P28">
-        <v>22.216014744</v>
+        <v>22.033938388</v>
       </c>
       <c r="Q28">
-        <v>30.816014744</v>
+        <v>30.633938388</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1194670577840137</v>
+        <v>0.1202935160790091</v>
       </c>
       <c r="T28">
-        <v>1.139605954986831</v>
+        <v>1.152391001965176</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.692877890957249</v>
+        <v>5.482030561662537</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09931113673767666</v>
+        <v>0.09914559071518317</v>
       </c>
       <c r="C29">
-        <v>334.4317710877525</v>
+        <v>331.5410225549968</v>
       </c>
       <c r="D29">
-        <v>446.3837710877525</v>
+        <v>447.7690225549968</v>
       </c>
       <c r="E29">
-        <v>-175.148</v>
+        <v>-170.872</v>
       </c>
       <c r="F29">
-        <v>115.452</v>
+        <v>119.728</v>
       </c>
       <c r="G29">
         <v>3.5</v>
@@ -3665,28 +3665,28 @@
         <v>35</v>
       </c>
       <c r="M29">
-        <v>6.384495600000001</v>
+        <v>6.620958400000002</v>
       </c>
       <c r="N29">
-        <v>28.6155044</v>
+        <v>28.3790416</v>
       </c>
       <c r="O29">
-        <v>6.581566012</v>
+        <v>6.527179567999999</v>
       </c>
       <c r="P29">
-        <v>22.033938388</v>
+        <v>21.851862032</v>
       </c>
       <c r="Q29">
-        <v>30.633938388</v>
+        <v>30.451862032</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1202935160790091</v>
+        <v>0.1211429315488655</v>
       </c>
       <c r="T29">
-        <v>1.152391001965176</v>
+        <v>1.165531189137363</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.482030561662537</v>
+        <v>5.286243755888874</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09914559071518317</v>
+        <v>0.09898004469268967</v>
       </c>
       <c r="C30">
-        <v>331.5410225549968</v>
+        <v>328.658898417797</v>
       </c>
       <c r="D30">
-        <v>447.7690225549968</v>
+        <v>449.1628984177971</v>
       </c>
       <c r="E30">
-        <v>-170.872</v>
+        <v>-166.596</v>
       </c>
       <c r="F30">
-        <v>119.728</v>
+        <v>124.004</v>
       </c>
       <c r="G30">
         <v>3.5</v>
@@ -3747,28 +3747,28 @@
         <v>35</v>
       </c>
       <c r="M30">
-        <v>6.620958400000002</v>
+        <v>6.857421200000001</v>
       </c>
       <c r="N30">
-        <v>28.3790416</v>
+        <v>28.1425788</v>
       </c>
       <c r="O30">
-        <v>6.527179567999999</v>
+        <v>6.472793124</v>
       </c>
       <c r="P30">
-        <v>21.851862032</v>
+        <v>21.669785676</v>
       </c>
       <c r="Q30">
-        <v>30.451862032</v>
+        <v>30.269785676</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1211429315488655</v>
+        <v>0.1220162742150559</v>
       </c>
       <c r="T30">
-        <v>1.165531189137363</v>
+        <v>1.179041522427076</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.286243755888874</v>
+        <v>5.103959488444431</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09898004469268967</v>
+        <v>0.09881449867019616</v>
       </c>
       <c r="C31">
-        <v>328.658898417797</v>
+        <v>325.7854794692053</v>
       </c>
       <c r="D31">
-        <v>449.1628984177971</v>
+        <v>450.5654794692053</v>
       </c>
       <c r="E31">
-        <v>-166.596</v>
+        <v>-162.32</v>
       </c>
       <c r="F31">
-        <v>124.004</v>
+        <v>128.28</v>
       </c>
       <c r="G31">
         <v>3.5</v>
@@ -3829,28 +3829,28 @@
         <v>35</v>
       </c>
       <c r="M31">
-        <v>6.8574212</v>
+        <v>7.093884</v>
       </c>
       <c r="N31">
-        <v>28.1425788</v>
+        <v>27.906116</v>
       </c>
       <c r="O31">
-        <v>6.472793124</v>
+        <v>6.41840668</v>
       </c>
       <c r="P31">
-        <v>21.669785676</v>
+        <v>21.48770932</v>
       </c>
       <c r="Q31">
-        <v>30.269785676</v>
+        <v>30.08770932</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1220162742150559</v>
+        <v>0.1229145695288517</v>
       </c>
       <c r="T31">
-        <v>1.179041522427076</v>
+        <v>1.192937865239353</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.103959488444431</v>
+        <v>4.933827505496284</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09881449867019616</v>
+        <v>0.09864895264770265</v>
       </c>
       <c r="C32">
-        <v>325.7854794692053</v>
+        <v>322.9208475145898</v>
       </c>
       <c r="D32">
-        <v>450.5654794692053</v>
+        <v>451.9768475145898</v>
       </c>
       <c r="E32">
-        <v>-162.32</v>
+        <v>-158.044</v>
       </c>
       <c r="F32">
-        <v>128.28</v>
+        <v>132.556</v>
       </c>
       <c r="G32">
         <v>3.5</v>
@@ -3911,28 +3911,28 @@
         <v>35</v>
       </c>
       <c r="M32">
-        <v>7.093884</v>
+        <v>7.330346800000001</v>
       </c>
       <c r="N32">
-        <v>27.906116</v>
+        <v>27.6696532</v>
       </c>
       <c r="O32">
-        <v>6.41840668</v>
+        <v>6.364020236</v>
       </c>
       <c r="P32">
-        <v>21.48770932</v>
+        <v>21.305632964</v>
       </c>
       <c r="Q32">
-        <v>30.08770932</v>
+        <v>29.905632964</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1229145695288517</v>
+        <v>0.1238389023879749</v>
       </c>
       <c r="T32">
-        <v>1.192937865239353</v>
+        <v>1.207237000596913</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.933827505496284</v>
+        <v>4.774671779512532</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09864895264770265</v>
+        <v>0.09848340662520916</v>
       </c>
       <c r="C33">
-        <v>322.9208475145898</v>
+        <v>320.0650853875406</v>
       </c>
       <c r="D33">
-        <v>451.9768475145898</v>
+        <v>453.3970853875406</v>
       </c>
       <c r="E33">
-        <v>-158.044</v>
+        <v>-153.768</v>
       </c>
       <c r="F33">
-        <v>132.556</v>
+        <v>136.832</v>
       </c>
       <c r="G33">
         <v>3.5</v>
@@ -3993,28 +3993,28 @@
         <v>35</v>
       </c>
       <c r="M33">
-        <v>7.330346800000001</v>
+        <v>7.566809600000002</v>
       </c>
       <c r="N33">
-        <v>27.6696532</v>
+        <v>27.4331904</v>
       </c>
       <c r="O33">
-        <v>6.364020236</v>
+        <v>6.309633792</v>
       </c>
       <c r="P33">
-        <v>21.305632964</v>
+        <v>21.123556608</v>
       </c>
       <c r="Q33">
-        <v>29.905632964</v>
+        <v>29.723556608</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1238389023879749</v>
+        <v>0.1247904215076605</v>
       </c>
       <c r="T33">
-        <v>1.207237000596913</v>
+        <v>1.221956698759107</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.774671779512532</v>
+        <v>4.625463286402764</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09848340662520916</v>
+        <v>0.09895311060271565</v>
       </c>
       <c r="C34">
-        <v>320.0650853875406</v>
+        <v>311.7825011635592</v>
       </c>
       <c r="D34">
-        <v>453.3970853875406</v>
+        <v>449.3905011635592</v>
       </c>
       <c r="E34">
-        <v>-153.768</v>
+        <v>-149.492</v>
       </c>
       <c r="F34">
-        <v>136.832</v>
+        <v>141.108</v>
       </c>
       <c r="G34">
         <v>3.5</v>
@@ -4075,45 +4075,45 @@
         <v>35</v>
       </c>
       <c r="M34">
-        <v>7.566809600000002</v>
+        <v>8.1560424</v>
       </c>
       <c r="N34">
-        <v>27.4331904</v>
+        <v>26.8439576</v>
       </c>
       <c r="O34">
-        <v>6.309633792</v>
+        <v>6.174110248</v>
       </c>
       <c r="P34">
-        <v>21.123556608</v>
+        <v>20.669847352</v>
       </c>
       <c r="Q34">
-        <v>29.723556608</v>
+        <v>29.269847352</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1247904215076605</v>
+        <v>0.1257703441831577</v>
       </c>
       <c r="T34">
-        <v>1.221956698759107</v>
+        <v>1.237115790896292</v>
       </c>
       <c r="U34">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V34">
         <v>0.23</v>
       </c>
       <c r="W34">
-        <v>0.042581</v>
+        <v>0.044506</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.625463286402764</v>
+        <v>4.291296965302681</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09895311060271565</v>
+        <v>0.09880681458022214</v>
       </c>
       <c r="C35">
-        <v>311.7825011635592</v>
+        <v>308.7467953292668</v>
       </c>
       <c r="D35">
-        <v>449.3905011635592</v>
+        <v>450.6307953292668</v>
       </c>
       <c r="E35">
-        <v>-149.492</v>
+        <v>-145.216</v>
       </c>
       <c r="F35">
-        <v>141.108</v>
+        <v>145.384</v>
       </c>
       <c r="G35">
         <v>3.5</v>
@@ -4157,28 +4157,28 @@
         <v>35</v>
       </c>
       <c r="M35">
-        <v>8.1560424</v>
+        <v>8.403195200000001</v>
       </c>
       <c r="N35">
-        <v>26.8439576</v>
+        <v>26.5968048</v>
       </c>
       <c r="O35">
-        <v>6.174110248</v>
+        <v>6.117265104</v>
       </c>
       <c r="P35">
-        <v>20.669847352</v>
+        <v>20.479539696</v>
       </c>
       <c r="Q35">
-        <v>29.269847352</v>
+        <v>29.079539696</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1257703441831577</v>
+        <v>0.1267799614851851</v>
       </c>
       <c r="T35">
-        <v>1.237115790896292</v>
+        <v>1.252734249461877</v>
       </c>
       <c r="U35">
         <v>0.0578</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.291296965302681</v>
+        <v>4.165082348676131</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09880681458022214</v>
+        <v>0.09866051855772864</v>
       </c>
       <c r="C36">
-        <v>308.7467953292668</v>
+        <v>305.7179547361076</v>
       </c>
       <c r="D36">
-        <v>450.6307953292668</v>
+        <v>451.8779547361076</v>
       </c>
       <c r="E36">
-        <v>-145.216</v>
+        <v>-140.94</v>
       </c>
       <c r="F36">
-        <v>145.384</v>
+        <v>149.66</v>
       </c>
       <c r="G36">
         <v>3.5</v>
@@ -4239,28 +4239,28 @@
         <v>35</v>
       </c>
       <c r="M36">
-        <v>8.403195200000001</v>
+        <v>8.650348000000003</v>
       </c>
       <c r="N36">
-        <v>26.5968048</v>
+        <v>26.349652</v>
       </c>
       <c r="O36">
-        <v>6.117265104</v>
+        <v>6.06041996</v>
       </c>
       <c r="P36">
-        <v>20.479539696</v>
+        <v>20.28923204</v>
       </c>
       <c r="Q36">
-        <v>29.079539696</v>
+        <v>28.88923204</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1267799614851851</v>
+        <v>0.1278206439349671</v>
       </c>
       <c r="T36">
-        <v>1.252734249461877</v>
+        <v>1.268833275983325</v>
       </c>
       <c r="U36">
         <v>0.0578</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.165082348676131</v>
+        <v>4.046079995856813</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09866051855772864</v>
+        <v>0.09948442253523512</v>
       </c>
       <c r="C37">
-        <v>305.7179547361076</v>
+        <v>294.5069067897463</v>
       </c>
       <c r="D37">
-        <v>451.8779547361076</v>
+        <v>444.9429067897463</v>
       </c>
       <c r="E37">
-        <v>-140.94</v>
+        <v>-136.664</v>
       </c>
       <c r="F37">
-        <v>149.66</v>
+        <v>153.936</v>
       </c>
       <c r="G37">
         <v>3.5</v>
@@ -4321,45 +4321,45 @@
         <v>35</v>
       </c>
       <c r="M37">
-        <v>8.650348000000003</v>
+        <v>9.436276800000002</v>
       </c>
       <c r="N37">
-        <v>26.349652</v>
+        <v>25.5637232</v>
       </c>
       <c r="O37">
-        <v>6.06041996</v>
+        <v>5.879656336</v>
       </c>
       <c r="P37">
-        <v>20.28923204</v>
+        <v>19.684066864</v>
       </c>
       <c r="Q37">
-        <v>28.88923204</v>
+        <v>28.284066864</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1278206439349671</v>
+        <v>0.1288938477113049</v>
       </c>
       <c r="T37">
-        <v>1.268833275983325</v>
+        <v>1.285435397083569</v>
       </c>
       <c r="U37">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V37">
         <v>0.23</v>
       </c>
       <c r="W37">
-        <v>0.044506</v>
+        <v>0.047201</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.046079995856813</v>
+        <v>3.709090008889946</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09948442253523514</v>
+        <v>0.09936507651274162</v>
       </c>
       <c r="C38">
-        <v>294.5069067897462</v>
+        <v>291.2222647718341</v>
       </c>
       <c r="D38">
-        <v>444.9429067897462</v>
+        <v>445.9342647718341</v>
       </c>
       <c r="E38">
-        <v>-136.664</v>
+        <v>-132.388</v>
       </c>
       <c r="F38">
-        <v>153.936</v>
+        <v>158.212</v>
       </c>
       <c r="G38">
         <v>3.5</v>
@@ -4403,28 +4403,28 @@
         <v>35</v>
       </c>
       <c r="M38">
-        <v>9.4362768</v>
+        <v>9.698395600000001</v>
       </c>
       <c r="N38">
-        <v>25.5637232</v>
+        <v>25.3016044</v>
       </c>
       <c r="O38">
-        <v>5.879656336</v>
+        <v>5.819369012</v>
       </c>
       <c r="P38">
-        <v>19.684066864</v>
+        <v>19.482235388</v>
       </c>
       <c r="Q38">
-        <v>28.284066864</v>
+        <v>28.082235388</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1288938477113049</v>
+        <v>0.1300011214487962</v>
       </c>
       <c r="T38">
-        <v>1.285435397083569</v>
+        <v>1.302564569647313</v>
       </c>
       <c r="U38">
         <v>0.0613</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.709090008889947</v>
+        <v>3.608844332974002</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09936507651274162</v>
+        <v>0.09924573049024814</v>
       </c>
       <c r="C39">
-        <v>291.2222647718341</v>
+        <v>287.9420502219701</v>
       </c>
       <c r="D39">
-        <v>445.9342647718341</v>
+        <v>446.9300502219701</v>
       </c>
       <c r="E39">
-        <v>-132.388</v>
+        <v>-128.112</v>
       </c>
       <c r="F39">
-        <v>158.212</v>
+        <v>162.488</v>
       </c>
       <c r="G39">
         <v>3.5</v>
@@ -4485,28 +4485,28 @@
         <v>35</v>
       </c>
       <c r="M39">
-        <v>9.698395600000001</v>
+        <v>9.960514399999999</v>
       </c>
       <c r="N39">
-        <v>25.3016044</v>
+        <v>25.0394856</v>
       </c>
       <c r="O39">
-        <v>5.819369012</v>
+        <v>5.759081688</v>
       </c>
       <c r="P39">
-        <v>19.482235388</v>
+        <v>19.280403912</v>
       </c>
       <c r="Q39">
-        <v>28.082235388</v>
+        <v>27.880403912</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1300011214487962</v>
+        <v>0.1311441136939486</v>
       </c>
       <c r="T39">
-        <v>1.302564569647313</v>
+        <v>1.320246296164726</v>
       </c>
       <c r="U39">
         <v>0.0613</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.608844332974002</v>
+        <v>3.513874745264161</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09924573049024814</v>
+        <v>0.09996722446775465</v>
       </c>
       <c r="C40">
-        <v>287.9420502219701</v>
+        <v>277.7130529478751</v>
       </c>
       <c r="D40">
-        <v>446.9300502219701</v>
+        <v>440.9770529478751</v>
       </c>
       <c r="E40">
-        <v>-128.112</v>
+        <v>-123.836</v>
       </c>
       <c r="F40">
-        <v>162.488</v>
+        <v>166.764</v>
       </c>
       <c r="G40">
         <v>3.5</v>
@@ -4567,45 +4567,45 @@
         <v>35</v>
       </c>
       <c r="M40">
-        <v>9.960514399999999</v>
+        <v>10.6895724</v>
       </c>
       <c r="N40">
-        <v>25.0394856</v>
+        <v>24.3104276</v>
       </c>
       <c r="O40">
-        <v>5.759081688</v>
+        <v>5.591398347999999</v>
       </c>
       <c r="P40">
-        <v>19.280403912</v>
+        <v>18.719029252</v>
       </c>
       <c r="Q40">
-        <v>27.880403912</v>
+        <v>27.319029252</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1311441136939486</v>
+        <v>0.1323245810946797</v>
       </c>
       <c r="T40">
-        <v>1.320246296164726</v>
+        <v>1.338507751420415</v>
       </c>
       <c r="U40">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V40">
         <v>0.23</v>
       </c>
       <c r="W40">
-        <v>0.047201</v>
+        <v>0.04935700000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.513874745264161</v>
+        <v>3.27421890140339</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09996722446775465</v>
+        <v>0.09986943844526114</v>
       </c>
       <c r="C41">
-        <v>277.7130529478751</v>
+        <v>274.2345717174169</v>
       </c>
       <c r="D41">
-        <v>440.9770529478751</v>
+        <v>441.774571717417</v>
       </c>
       <c r="E41">
-        <v>-123.836</v>
+        <v>-119.56</v>
       </c>
       <c r="F41">
-        <v>166.764</v>
+        <v>171.04</v>
       </c>
       <c r="G41">
         <v>3.5</v>
@@ -4649,28 +4649,28 @@
         <v>35</v>
       </c>
       <c r="M41">
-        <v>10.6895724</v>
+        <v>10.963664</v>
       </c>
       <c r="N41">
-        <v>24.3104276</v>
+        <v>24.036336</v>
       </c>
       <c r="O41">
-        <v>5.591398347999999</v>
+        <v>5.52835728</v>
       </c>
       <c r="P41">
-        <v>18.719029252</v>
+        <v>18.50797872</v>
       </c>
       <c r="Q41">
-        <v>27.319029252</v>
+        <v>27.10797872</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1323245810946797</v>
+        <v>0.1335443974087686</v>
       </c>
       <c r="T41">
-        <v>1.338507751420415</v>
+        <v>1.357377921851294</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.27421890140339</v>
+        <v>3.192363428868305</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09986943844526114</v>
+        <v>0.09977165242276763</v>
       </c>
       <c r="C42">
-        <v>274.2345717174169</v>
+        <v>270.7589803813695</v>
       </c>
       <c r="D42">
-        <v>441.774571717417</v>
+        <v>442.5749803813695</v>
       </c>
       <c r="E42">
-        <v>-119.56</v>
+        <v>-115.284</v>
       </c>
       <c r="F42">
-        <v>171.04</v>
+        <v>175.316</v>
       </c>
       <c r="G42">
         <v>3.5</v>
@@ -4731,28 +4731,28 @@
         <v>35</v>
       </c>
       <c r="M42">
-        <v>10.963664</v>
+        <v>11.2377556</v>
       </c>
       <c r="N42">
-        <v>24.036336</v>
+        <v>23.7622444</v>
       </c>
       <c r="O42">
-        <v>5.52835728</v>
+        <v>5.465316211999999</v>
       </c>
       <c r="P42">
-        <v>18.50797872</v>
+        <v>18.296928188</v>
       </c>
       <c r="Q42">
-        <v>27.10797872</v>
+        <v>26.896928188</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1335443974087686</v>
+        <v>0.1348055634284197</v>
       </c>
       <c r="T42">
-        <v>1.357377921851294</v>
+        <v>1.376887759076439</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.192363428868305</v>
+        <v>3.11450090621298</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09977165242276763</v>
+        <v>0.09967386640027413</v>
       </c>
       <c r="C43">
-        <v>270.7589803813695</v>
+        <v>267.2862946760051</v>
       </c>
       <c r="D43">
-        <v>442.5749803813695</v>
+        <v>443.3782946760052</v>
       </c>
       <c r="E43">
-        <v>-115.284</v>
+        <v>-111.008</v>
       </c>
       <c r="F43">
-        <v>175.316</v>
+        <v>179.592</v>
       </c>
       <c r="G43">
         <v>3.5</v>
@@ -4813,28 +4813,28 @@
         <v>35</v>
       </c>
       <c r="M43">
-        <v>11.2377556</v>
+        <v>11.5118472</v>
       </c>
       <c r="N43">
-        <v>23.7622444</v>
+        <v>23.4881528</v>
       </c>
       <c r="O43">
-        <v>5.465316211999999</v>
+        <v>5.402275144</v>
       </c>
       <c r="P43">
-        <v>18.296928188</v>
+        <v>18.085877656</v>
       </c>
       <c r="Q43">
-        <v>26.896928188</v>
+        <v>26.685877656</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1348055634284197</v>
+        <v>0.1361102179315071</v>
       </c>
       <c r="T43">
-        <v>1.376887759076439</v>
+        <v>1.397070349309348</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.11450090621298</v>
+        <v>3.040346122731719</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09967386640027413</v>
+        <v>0.1021586603777806</v>
       </c>
       <c r="C44">
-        <v>267.2862946760051</v>
+        <v>243.4622126424162</v>
       </c>
       <c r="D44">
-        <v>443.3782946760052</v>
+        <v>423.8302126424162</v>
       </c>
       <c r="E44">
-        <v>-111.008</v>
+        <v>-106.732</v>
       </c>
       <c r="F44">
-        <v>179.592</v>
+        <v>183.868</v>
       </c>
       <c r="G44">
         <v>3.5</v>
@@ -4895,45 +4895,45 @@
         <v>35</v>
       </c>
       <c r="M44">
-        <v>11.5118472</v>
+        <v>13.2201092</v>
       </c>
       <c r="N44">
-        <v>23.4881528</v>
+        <v>21.7798908</v>
       </c>
       <c r="O44">
-        <v>5.402275144</v>
+        <v>5.009374884</v>
       </c>
       <c r="P44">
-        <v>18.085877656</v>
+        <v>16.770515916</v>
       </c>
       <c r="Q44">
-        <v>26.685877656</v>
+        <v>25.370515916</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1361102179315071</v>
+        <v>0.13746064978558</v>
       </c>
       <c r="T44">
-        <v>1.397070349309348</v>
+        <v>1.417961100603061</v>
       </c>
       <c r="U44">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V44">
         <v>0.23</v>
       </c>
       <c r="W44">
-        <v>0.04935700000000001</v>
+        <v>0.055363</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>3.040346122731719</v>
+        <v>2.647481913386918</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1021586603777806</v>
+        <v>0.1021209343552871</v>
       </c>
       <c r="C45">
-        <v>243.4622126424162</v>
+        <v>239.4701111309374</v>
       </c>
       <c r="D45">
-        <v>423.8302126424162</v>
+        <v>424.1141111309374</v>
       </c>
       <c r="E45">
-        <v>-106.732</v>
+        <v>-102.456</v>
       </c>
       <c r="F45">
-        <v>183.868</v>
+        <v>188.144</v>
       </c>
       <c r="G45">
         <v>3.5</v>
@@ -4977,28 +4977,28 @@
         <v>35</v>
       </c>
       <c r="M45">
-        <v>13.2201092</v>
+        <v>13.5275536</v>
       </c>
       <c r="N45">
-        <v>21.7798908</v>
+        <v>21.4724464</v>
       </c>
       <c r="O45">
-        <v>5.009374884</v>
+        <v>4.938662672</v>
       </c>
       <c r="P45">
-        <v>16.770515916</v>
+        <v>16.533783728</v>
       </c>
       <c r="Q45">
-        <v>25.370515916</v>
+        <v>25.133783728</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.13746064978558</v>
+        <v>0.138859311348727</v>
       </c>
       <c r="T45">
-        <v>1.417961100603061</v>
+        <v>1.439597950157264</v>
       </c>
       <c r="U45">
         <v>0.07190000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.647481913386918</v>
+        <v>2.587311869900851</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1021209343552871</v>
+        <v>0.1020832083327936</v>
       </c>
       <c r="C46">
-        <v>239.4701111309374</v>
+        <v>235.478390207598</v>
       </c>
       <c r="D46">
-        <v>424.1141111309374</v>
+        <v>424.398390207598</v>
       </c>
       <c r="E46">
-        <v>-102.456</v>
+        <v>-98.18000000000001</v>
       </c>
       <c r="F46">
-        <v>188.144</v>
+        <v>192.42</v>
       </c>
       <c r="G46">
         <v>3.5</v>
@@ -5059,28 +5059,28 @@
         <v>35</v>
       </c>
       <c r="M46">
-        <v>13.5275536</v>
+        <v>13.834998</v>
       </c>
       <c r="N46">
-        <v>21.4724464</v>
+        <v>21.165002</v>
       </c>
       <c r="O46">
-        <v>4.938662672</v>
+        <v>4.867950459999999</v>
       </c>
       <c r="P46">
-        <v>16.533783728</v>
+        <v>16.29705154</v>
       </c>
       <c r="Q46">
-        <v>25.133783728</v>
+        <v>24.89705154</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.138859311348727</v>
+        <v>0.140308833332352</v>
       </c>
       <c r="T46">
-        <v>1.439597950157264</v>
+        <v>1.46202159424071</v>
       </c>
       <c r="U46">
         <v>0.07190000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.587311869900851</v>
+        <v>2.529816050569721</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1020832083327936</v>
+        <v>0.1034268623103001</v>
       </c>
       <c r="C47">
-        <v>235.478390207598</v>
+        <v>221.3069254505679</v>
       </c>
       <c r="D47">
-        <v>424.398390207598</v>
+        <v>414.5029254505679</v>
       </c>
       <c r="E47">
-        <v>-98.18000000000001</v>
+        <v>-93.904</v>
       </c>
       <c r="F47">
-        <v>192.42</v>
+        <v>196.696</v>
       </c>
       <c r="G47">
         <v>3.5</v>
@@ -5141,45 +5141,45 @@
         <v>35</v>
       </c>
       <c r="M47">
-        <v>13.834998</v>
+        <v>14.9095568</v>
       </c>
       <c r="N47">
-        <v>21.165002</v>
+        <v>20.0904432</v>
       </c>
       <c r="O47">
-        <v>4.867950459999999</v>
+        <v>4.620801935999999</v>
       </c>
       <c r="P47">
-        <v>16.29705154</v>
+        <v>15.469641264</v>
       </c>
       <c r="Q47">
-        <v>24.89705154</v>
+        <v>24.069641264</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.140308833332352</v>
+        <v>0.1418120413153706</v>
       </c>
       <c r="T47">
-        <v>1.46202159424071</v>
+        <v>1.485275743660581</v>
       </c>
       <c r="U47">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V47">
         <v>0.23</v>
       </c>
       <c r="W47">
-        <v>0.055363</v>
+        <v>0.05836600000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.529816050569721</v>
+        <v>2.347487619484436</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1034268623103001</v>
+        <v>0.1034191662878066</v>
       </c>
       <c r="C48">
-        <v>221.3069254505679</v>
+        <v>217.0862893866228</v>
       </c>
       <c r="D48">
-        <v>414.5029254505679</v>
+        <v>414.5582893866228</v>
       </c>
       <c r="E48">
-        <v>-93.904</v>
+        <v>-89.62799999999999</v>
       </c>
       <c r="F48">
-        <v>196.696</v>
+        <v>200.972</v>
       </c>
       <c r="G48">
         <v>3.5</v>
@@ -5223,28 +5223,28 @@
         <v>35</v>
       </c>
       <c r="M48">
-        <v>14.9095568</v>
+        <v>15.2336776</v>
       </c>
       <c r="N48">
-        <v>20.0904432</v>
+        <v>19.7663224</v>
       </c>
       <c r="O48">
-        <v>4.620801935999999</v>
+        <v>4.546254151999999</v>
       </c>
       <c r="P48">
-        <v>15.469641264</v>
+        <v>15.220068248</v>
       </c>
       <c r="Q48">
-        <v>24.069641264</v>
+        <v>23.820068248</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1418120413153706</v>
+        <v>0.143371974127937</v>
       </c>
       <c r="T48">
-        <v>1.485275743660581</v>
+        <v>1.509407408152899</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.347487619484436</v>
+        <v>2.297541074389023</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1034191662878066</v>
+        <v>0.1034114702653131</v>
       </c>
       <c r="C49">
-        <v>217.0862893866228</v>
+        <v>212.8656681142494</v>
       </c>
       <c r="D49">
-        <v>414.5582893866228</v>
+        <v>414.6136681142494</v>
       </c>
       <c r="E49">
-        <v>-89.62799999999999</v>
+        <v>-85.352</v>
       </c>
       <c r="F49">
-        <v>200.972</v>
+        <v>205.248</v>
       </c>
       <c r="G49">
         <v>3.5</v>
@@ -5305,28 +5305,28 @@
         <v>35</v>
       </c>
       <c r="M49">
-        <v>15.2336776</v>
+        <v>15.5577984</v>
       </c>
       <c r="N49">
-        <v>19.7663224</v>
+        <v>19.4422016</v>
       </c>
       <c r="O49">
-        <v>4.546254151999999</v>
+        <v>4.471706368</v>
       </c>
       <c r="P49">
-        <v>15.220068248</v>
+        <v>14.970495232</v>
       </c>
       <c r="Q49">
-        <v>23.820068248</v>
+        <v>23.570495232</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.143371974127937</v>
+        <v>0.1449919043563714</v>
       </c>
       <c r="T49">
-        <v>1.509407408152899</v>
+        <v>1.53446721358723</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.297541074389023</v>
+        <v>2.249675635339252</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1034114702653131</v>
+        <v>0.1034037742428196</v>
       </c>
       <c r="C50">
-        <v>212.8656681142494</v>
+        <v>208.6450616393763</v>
       </c>
       <c r="D50">
-        <v>414.6136681142494</v>
+        <v>414.6690616393763</v>
       </c>
       <c r="E50">
-        <v>-85.35200000000003</v>
+        <v>-81.07600000000002</v>
       </c>
       <c r="F50">
-        <v>205.248</v>
+        <v>209.524</v>
       </c>
       <c r="G50">
         <v>3.5</v>
@@ -5387,28 +5387,28 @@
         <v>35</v>
       </c>
       <c r="M50">
-        <v>15.5577984</v>
+        <v>15.8819192</v>
       </c>
       <c r="N50">
-        <v>19.4422016</v>
+        <v>19.1180808</v>
       </c>
       <c r="O50">
-        <v>4.471706368</v>
+        <v>4.397158584</v>
       </c>
       <c r="P50">
-        <v>14.970495232</v>
+        <v>14.720922216</v>
       </c>
       <c r="Q50">
-        <v>23.570495232</v>
+        <v>23.320922216</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1449919043563714</v>
+        <v>0.1466753612604306</v>
       </c>
       <c r="T50">
-        <v>1.53446721358723</v>
+        <v>1.560509756489574</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.249675635339252</v>
+        <v>2.203763887679267</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1034037742428196</v>
+        <v>0.1033960782203261</v>
       </c>
       <c r="C51">
-        <v>208.6450616393763</v>
+        <v>204.4244699679352</v>
       </c>
       <c r="D51">
-        <v>414.6690616393763</v>
+        <v>414.7244699679352</v>
       </c>
       <c r="E51">
-        <v>-81.07600000000002</v>
+        <v>-76.80000000000001</v>
       </c>
       <c r="F51">
-        <v>209.524</v>
+        <v>213.8</v>
       </c>
       <c r="G51">
         <v>3.5</v>
@@ -5469,28 +5469,28 @@
         <v>35</v>
       </c>
       <c r="M51">
-        <v>15.8819192</v>
+        <v>16.20604</v>
       </c>
       <c r="N51">
-        <v>19.1180808</v>
+        <v>18.79396</v>
       </c>
       <c r="O51">
-        <v>4.397158584</v>
+        <v>4.3226108</v>
       </c>
       <c r="P51">
-        <v>14.720922216</v>
+        <v>14.4713492</v>
       </c>
       <c r="Q51">
-        <v>23.320922216</v>
+        <v>23.0713492</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1466753612604306</v>
+        <v>0.1484261564406522</v>
       </c>
       <c r="T51">
-        <v>1.560509756489574</v>
+        <v>1.587594001108011</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.203763887679267</v>
+        <v>2.159688609925682</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1033960782203261</v>
+        <v>0.1033883821978326</v>
       </c>
       <c r="C52">
-        <v>204.4244699679352</v>
+        <v>200.203893105861</v>
       </c>
       <c r="D52">
-        <v>414.7244699679352</v>
+        <v>414.779893105861</v>
       </c>
       <c r="E52">
-        <v>-76.80000000000001</v>
+        <v>-72.524</v>
       </c>
       <c r="F52">
-        <v>213.8</v>
+        <v>218.076</v>
       </c>
       <c r="G52">
         <v>3.5</v>
@@ -5551,28 +5551,28 @@
         <v>35</v>
       </c>
       <c r="M52">
-        <v>16.20604</v>
+        <v>16.5301608</v>
       </c>
       <c r="N52">
-        <v>18.79396</v>
+        <v>18.4698392</v>
       </c>
       <c r="O52">
-        <v>4.3226108</v>
+        <v>4.248063015999999</v>
       </c>
       <c r="P52">
-        <v>14.4713492</v>
+        <v>14.221776184</v>
       </c>
       <c r="Q52">
-        <v>23.0713492</v>
+        <v>22.821776184</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1484261564406522</v>
+        <v>0.150248412648638</v>
       </c>
       <c r="T52">
-        <v>1.587594001108011</v>
+        <v>1.61578372509863</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.159688609925682</v>
+        <v>2.117341774436943</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1033883821978326</v>
+        <v>0.1033806861753391</v>
       </c>
       <c r="C53">
-        <v>200.203893105861</v>
+        <v>195.983331059092</v>
       </c>
       <c r="D53">
-        <v>414.779893105861</v>
+        <v>414.835331059092</v>
       </c>
       <c r="E53">
-        <v>-72.524</v>
+        <v>-68.24799999999999</v>
       </c>
       <c r="F53">
-        <v>218.076</v>
+        <v>222.352</v>
       </c>
       <c r="G53">
         <v>3.5</v>
@@ -5633,28 +5633,28 @@
         <v>35</v>
       </c>
       <c r="M53">
-        <v>16.5301608</v>
+        <v>16.8542816</v>
       </c>
       <c r="N53">
-        <v>18.4698392</v>
+        <v>18.1457184</v>
       </c>
       <c r="O53">
-        <v>4.248063015999999</v>
+        <v>4.173515232</v>
       </c>
       <c r="P53">
-        <v>14.221776184</v>
+        <v>13.972203168</v>
       </c>
       <c r="Q53">
-        <v>22.821776184</v>
+        <v>22.572203168</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.150248412648638</v>
+        <v>0.1521465961986231</v>
       </c>
       <c r="T53">
-        <v>1.61578372509863</v>
+        <v>1.64514802092219</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.117341774436943</v>
+        <v>2.076623663390079</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1033806861753391</v>
+        <v>0.1033729901528456</v>
       </c>
       <c r="C54">
-        <v>195.983331059092</v>
+        <v>191.7627838335693</v>
       </c>
       <c r="D54">
-        <v>414.835331059092</v>
+        <v>414.8907838335693</v>
       </c>
       <c r="E54">
-        <v>-68.24799999999999</v>
+        <v>-63.97200000000001</v>
       </c>
       <c r="F54">
-        <v>222.352</v>
+        <v>226.628</v>
       </c>
       <c r="G54">
         <v>3.5</v>
@@ -5715,28 +5715,28 @@
         <v>35</v>
       </c>
       <c r="M54">
-        <v>16.8542816</v>
+        <v>17.1784024</v>
       </c>
       <c r="N54">
-        <v>18.1457184</v>
+        <v>17.8215976</v>
       </c>
       <c r="O54">
-        <v>4.173515232</v>
+        <v>4.098967448</v>
       </c>
       <c r="P54">
-        <v>13.972203168</v>
+        <v>13.722630152</v>
       </c>
       <c r="Q54">
-        <v>22.572203168</v>
+        <v>22.322630152</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1521465961986231</v>
+        <v>0.1541255535166928</v>
       </c>
       <c r="T54">
-        <v>1.64514802092219</v>
+        <v>1.675761861248882</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.076623663390079</v>
+        <v>2.037442084835549</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1033729901528456</v>
+        <v>0.1092696541303521</v>
       </c>
       <c r="C55">
-        <v>191.7627838335693</v>
+        <v>148.9412525375212</v>
       </c>
       <c r="D55">
-        <v>414.8907838335693</v>
+        <v>376.3452525375212</v>
       </c>
       <c r="E55">
-        <v>-63.97200000000001</v>
+        <v>-59.696</v>
       </c>
       <c r="F55">
-        <v>226.628</v>
+        <v>230.904</v>
       </c>
       <c r="G55">
         <v>3.5</v>
@@ -5797,45 +5797,45 @@
         <v>35</v>
       </c>
       <c r="M55">
-        <v>17.1784024</v>
+        <v>20.78136</v>
       </c>
       <c r="N55">
-        <v>17.8215976</v>
+        <v>14.21864</v>
       </c>
       <c r="O55">
-        <v>4.098967448</v>
+        <v>3.270287199999999</v>
       </c>
       <c r="P55">
-        <v>13.722630152</v>
+        <v>10.9483528</v>
       </c>
       <c r="Q55">
-        <v>22.322630152</v>
+        <v>19.5483528</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1541255535166928</v>
+        <v>0.1561905524572872</v>
       </c>
       <c r="T55">
-        <v>1.675761861248882</v>
+        <v>1.707706738111516</v>
       </c>
       <c r="U55">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V55">
         <v>0.23</v>
       </c>
       <c r="W55">
-        <v>0.05836600000000001</v>
+        <v>0.0693</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.037442084835549</v>
+        <v>1.684201611444102</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1092696541303521</v>
+        <v>0.1093712981078586</v>
       </c>
       <c r="C56">
-        <v>148.9412525375212</v>
+        <v>144.0635151257933</v>
       </c>
       <c r="D56">
-        <v>376.3452525375212</v>
+        <v>375.7435151257933</v>
       </c>
       <c r="E56">
-        <v>-59.696</v>
+        <v>-55.41999999999999</v>
       </c>
       <c r="F56">
-        <v>230.904</v>
+        <v>235.18</v>
       </c>
       <c r="G56">
         <v>3.5</v>
@@ -5879,28 +5879,28 @@
         <v>35</v>
       </c>
       <c r="M56">
-        <v>20.78136</v>
+        <v>21.1662</v>
       </c>
       <c r="N56">
-        <v>14.21864</v>
+        <v>13.8338</v>
       </c>
       <c r="O56">
-        <v>3.270287199999999</v>
+        <v>3.181773999999999</v>
       </c>
       <c r="P56">
-        <v>10.9483528</v>
+        <v>10.652026</v>
       </c>
       <c r="Q56">
-        <v>19.5483528</v>
+        <v>19.252026</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1561905524572872</v>
+        <v>0.1583473291285747</v>
       </c>
       <c r="T56">
-        <v>1.707706738111516</v>
+        <v>1.741071387279156</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.684201611444102</v>
+        <v>1.6535797639633</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1093712981078586</v>
+        <v>0.1094729420853651</v>
       </c>
       <c r="C57">
-        <v>144.0635151257933</v>
+        <v>139.1876988749836</v>
       </c>
       <c r="D57">
-        <v>375.7435151257933</v>
+        <v>375.1436988749837</v>
       </c>
       <c r="E57">
-        <v>-55.41999999999999</v>
+        <v>-51.14399999999998</v>
       </c>
       <c r="F57">
-        <v>235.18</v>
+        <v>239.456</v>
       </c>
       <c r="G57">
         <v>3.5</v>
@@ -5961,28 +5961,28 @@
         <v>35</v>
       </c>
       <c r="M57">
-        <v>21.1662</v>
+        <v>21.55104</v>
       </c>
       <c r="N57">
-        <v>13.8338</v>
+        <v>13.44896</v>
       </c>
       <c r="O57">
-        <v>3.181773999999999</v>
+        <v>3.093260799999999</v>
       </c>
       <c r="P57">
-        <v>10.652026</v>
+        <v>10.3556992</v>
       </c>
       <c r="Q57">
-        <v>19.252026</v>
+        <v>18.9556992</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1583473291285747</v>
+        <v>0.1606021411031025</v>
       </c>
       <c r="T57">
-        <v>1.741071387279156</v>
+        <v>1.775952611408961</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.6535797639633</v>
+        <v>1.624051553892526</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1094729420853651</v>
+        <v>0.1095745860628716</v>
       </c>
       <c r="C58">
-        <v>139.1876988749836</v>
+        <v>134.3137945992498</v>
       </c>
       <c r="D58">
-        <v>375.1436988749837</v>
+        <v>374.5457945992499</v>
       </c>
       <c r="E58">
-        <v>-51.14399999999998</v>
+        <v>-46.86799999999999</v>
       </c>
       <c r="F58">
-        <v>239.456</v>
+        <v>243.732</v>
       </c>
       <c r="G58">
         <v>3.5</v>
@@ -6043,28 +6043,28 @@
         <v>35</v>
       </c>
       <c r="M58">
-        <v>21.55104</v>
+        <v>21.93588</v>
       </c>
       <c r="N58">
-        <v>13.44896</v>
+        <v>13.06412</v>
       </c>
       <c r="O58">
-        <v>3.093260799999999</v>
+        <v>3.0047476</v>
       </c>
       <c r="P58">
-        <v>10.3556992</v>
+        <v>10.0593724</v>
       </c>
       <c r="Q58">
-        <v>18.9556992</v>
+        <v>18.6593724</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1606021411031025</v>
+        <v>0.1629618280531897</v>
       </c>
       <c r="T58">
-        <v>1.775952611408961</v>
+        <v>1.812456218056432</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.624051553892526</v>
+        <v>1.595559421368096</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1095745860628716</v>
+        <v>0.1096762300403781</v>
       </c>
       <c r="C59">
-        <v>134.3137945992498</v>
+        <v>129.4417931712173</v>
       </c>
       <c r="D59">
-        <v>374.5457945992499</v>
+        <v>373.9497931712173</v>
       </c>
       <c r="E59">
-        <v>-46.86799999999999</v>
+        <v>-42.59199999999998</v>
       </c>
       <c r="F59">
-        <v>243.732</v>
+        <v>248.008</v>
       </c>
       <c r="G59">
         <v>3.5</v>
@@ -6125,28 +6125,28 @@
         <v>35</v>
       </c>
       <c r="M59">
-        <v>21.93588</v>
+        <v>22.32072</v>
       </c>
       <c r="N59">
-        <v>13.06412</v>
+        <v>12.67928</v>
       </c>
       <c r="O59">
-        <v>3.0047476</v>
+        <v>2.9162344</v>
       </c>
       <c r="P59">
-        <v>10.0593724</v>
+        <v>9.763045599999998</v>
       </c>
       <c r="Q59">
-        <v>18.6593724</v>
+        <v>18.3630456</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1629618280531897</v>
+        <v>0.1654338810485192</v>
       </c>
       <c r="T59">
-        <v>1.812456218056432</v>
+        <v>1.850698091687116</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.595559421368096</v>
+        <v>1.568049776172095</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1096762300403781</v>
+        <v>0.1097778740178846</v>
       </c>
       <c r="C60">
-        <v>129.4417931712171</v>
+        <v>124.5716855215159</v>
       </c>
       <c r="D60">
-        <v>373.9497931712172</v>
+        <v>373.3556855215159</v>
       </c>
       <c r="E60">
-        <v>-42.59200000000001</v>
+        <v>-38.31600000000003</v>
       </c>
       <c r="F60">
-        <v>248.008</v>
+        <v>252.284</v>
       </c>
       <c r="G60">
         <v>3.5</v>
@@ -6207,28 +6207,28 @@
         <v>35</v>
       </c>
       <c r="M60">
-        <v>22.32072</v>
+        <v>22.70556</v>
       </c>
       <c r="N60">
-        <v>12.67928</v>
+        <v>12.29444</v>
       </c>
       <c r="O60">
-        <v>2.9162344</v>
+        <v>2.8277212</v>
       </c>
       <c r="P60">
-        <v>9.763045599999998</v>
+        <v>9.466718800000001</v>
       </c>
       <c r="Q60">
-        <v>18.3630456</v>
+        <v>18.0667188</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1654338810485192</v>
+        <v>0.1680265219948404</v>
       </c>
       <c r="T60">
-        <v>1.850698091687116</v>
+        <v>1.890805422568077</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.568049776172095</v>
+        <v>1.54147266132172</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1097778740178846</v>
+        <v>0.1098795179953911</v>
       </c>
       <c r="C61">
-        <v>124.5716855215159</v>
+        <v>119.7034626383195</v>
       </c>
       <c r="D61">
-        <v>373.3556855215159</v>
+        <v>372.7634626383195</v>
       </c>
       <c r="E61">
-        <v>-38.31600000000003</v>
+        <v>-34.04000000000002</v>
       </c>
       <c r="F61">
-        <v>252.284</v>
+        <v>256.56</v>
       </c>
       <c r="G61">
         <v>3.5</v>
@@ -6289,28 +6289,28 @@
         <v>35</v>
       </c>
       <c r="M61">
-        <v>22.70556</v>
+        <v>23.0904</v>
       </c>
       <c r="N61">
-        <v>12.29444</v>
+        <v>11.9096</v>
       </c>
       <c r="O61">
-        <v>2.8277212</v>
+        <v>2.739208000000001</v>
       </c>
       <c r="P61">
-        <v>9.466718800000001</v>
+        <v>9.170392</v>
       </c>
       <c r="Q61">
-        <v>18.0667188</v>
+        <v>17.770392</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1680265219948404</v>
+        <v>0.1707487949884777</v>
       </c>
       <c r="T61">
-        <v>1.890805422568077</v>
+        <v>1.932918119993086</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.54147266132172</v>
+        <v>1.515781450299692</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1098795179953911</v>
+        <v>0.1391292582010832</v>
       </c>
       <c r="C62">
-        <v>119.7034626383195</v>
+        <v>-1.398007214375866</v>
       </c>
       <c r="D62">
-        <v>372.7634626383195</v>
+        <v>255.9379927856241</v>
       </c>
       <c r="E62">
-        <v>-34.04000000000002</v>
+        <v>-29.76400000000001</v>
       </c>
       <c r="F62">
-        <v>256.56</v>
+        <v>260.836</v>
       </c>
       <c r="G62">
         <v>3.5</v>
@@ -6371,45 +6371,45 @@
         <v>35</v>
       </c>
       <c r="M62">
-        <v>23.0904</v>
+        <v>38.29072480000001</v>
       </c>
       <c r="N62">
-        <v>11.9096</v>
+        <v>-3.290724800000007</v>
       </c>
       <c r="O62">
-        <v>2.739208000000001</v>
+        <v>-0.7568667040000016</v>
       </c>
       <c r="P62">
-        <v>9.170392</v>
+        <v>-2.533858096000005</v>
       </c>
       <c r="Q62">
-        <v>17.770392</v>
+        <v>6.066141903999997</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1707487949884777</v>
+        <v>0.1754032405482188</v>
       </c>
       <c r="T62">
-        <v>1.932918119993086</v>
+        <v>2.00492091251121</v>
       </c>
       <c r="U62">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.23</v>
+        <v>0.2102336804029366</v>
       </c>
       <c r="W62">
-        <v>0.0693</v>
+        <v>0.1159376957168489</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y62">
-        <v>1.515781450299692</v>
+        <v>0.9140594800127678</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1391292582010832</v>
+        <v>0.1401392582010832</v>
       </c>
       <c r="C63">
-        <v>-1.398007214375866</v>
+        <v>-8.414089950266202</v>
       </c>
       <c r="D63">
-        <v>255.9379927856241</v>
+        <v>253.1979100497338</v>
       </c>
       <c r="E63">
-        <v>-29.76400000000001</v>
+        <v>-25.488</v>
       </c>
       <c r="F63">
-        <v>260.836</v>
+        <v>265.112</v>
       </c>
       <c r="G63">
         <v>3.5</v>
@@ -6453,37 +6453,37 @@
         <v>35</v>
       </c>
       <c r="M63">
-        <v>38.29072480000001</v>
+        <v>38.91844160000001</v>
       </c>
       <c r="N63">
-        <v>-3.290724800000007</v>
+        <v>-3.918441600000008</v>
       </c>
       <c r="O63">
-        <v>-0.7568667040000016</v>
+        <v>-0.901241568000002</v>
       </c>
       <c r="P63">
-        <v>-2.533858096000005</v>
+        <v>-3.017200032000007</v>
       </c>
       <c r="Q63">
-        <v>6.066141903999997</v>
+        <v>5.582799967999994</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1754032405482188</v>
+        <v>0.178813852141593</v>
       </c>
       <c r="T63">
-        <v>2.00492091251121</v>
+        <v>2.057681989156243</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.2102336804029366</v>
+        <v>0.206842814589986</v>
       </c>
       <c r="W63">
-        <v>0.1159376957168489</v>
+        <v>0.1164354748181901</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.9140594800127678</v>
+        <v>0.8993165851738522</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1401392582010832</v>
+        <v>0.1411492582010832</v>
       </c>
       <c r="C64">
-        <v>-8.414089950266202</v>
+        <v>-15.3721232872316</v>
       </c>
       <c r="D64">
-        <v>253.1979100497338</v>
+        <v>250.5158767127684</v>
       </c>
       <c r="E64">
-        <v>-25.488</v>
+        <v>-21.21199999999999</v>
       </c>
       <c r="F64">
-        <v>265.112</v>
+        <v>269.388</v>
       </c>
       <c r="G64">
         <v>3.5</v>
@@ -6535,37 +6535,37 @@
         <v>35</v>
       </c>
       <c r="M64">
-        <v>38.91844160000001</v>
+        <v>39.54615840000001</v>
       </c>
       <c r="N64">
-        <v>-3.918441600000008</v>
+        <v>-4.54615840000001</v>
       </c>
       <c r="O64">
-        <v>-0.901241568000002</v>
+        <v>-1.045616432000002</v>
       </c>
       <c r="P64">
-        <v>-3.017200032000007</v>
+        <v>-3.500541968000008</v>
       </c>
       <c r="Q64">
-        <v>5.582799967999994</v>
+        <v>5.099458031999994</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.178813852141593</v>
+        <v>0.1824088211183928</v>
       </c>
       <c r="T64">
-        <v>2.057681989156243</v>
+        <v>2.113295015890195</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.206842814589986</v>
+        <v>0.2035595953107799</v>
       </c>
       <c r="W64">
-        <v>0.1164354748181901</v>
+        <v>0.1169174514083775</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8993165851738522</v>
+        <v>0.8850417187425211</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1411492582010832</v>
+        <v>0.1421592582010832</v>
       </c>
       <c r="C65">
-        <v>-15.3721232872316</v>
+        <v>-22.27393257845603</v>
       </c>
       <c r="D65">
-        <v>250.5158767127684</v>
+        <v>247.890067421544</v>
       </c>
       <c r="E65">
-        <v>-21.21199999999999</v>
+        <v>-16.93599999999998</v>
       </c>
       <c r="F65">
-        <v>269.388</v>
+        <v>273.664</v>
       </c>
       <c r="G65">
         <v>3.5</v>
@@ -6617,37 +6617,37 @@
         <v>35</v>
       </c>
       <c r="M65">
-        <v>39.54615840000001</v>
+        <v>40.17387520000001</v>
       </c>
       <c r="N65">
-        <v>-4.54615840000001</v>
+        <v>-5.173875200000012</v>
       </c>
       <c r="O65">
-        <v>-1.045616432000002</v>
+        <v>-1.189991296000003</v>
       </c>
       <c r="P65">
-        <v>-3.500541968000008</v>
+        <v>-3.983883904000009</v>
       </c>
       <c r="Q65">
-        <v>5.099458031999994</v>
+        <v>4.616116095999992</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1824088211183928</v>
+        <v>0.1862035105939037</v>
       </c>
       <c r="T65">
-        <v>2.113295015890195</v>
+        <v>2.171997655220478</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.2035595953107799</v>
+        <v>0.2003789766340489</v>
       </c>
       <c r="W65">
-        <v>0.1169174514083775</v>
+        <v>0.1173843662301216</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8850417187425211</v>
+        <v>0.8712129418871692</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1421592582010832</v>
+        <v>0.1431692582010832</v>
       </c>
       <c r="C66">
-        <v>-22.27393257845603</v>
+        <v>-29.12126744041728</v>
       </c>
       <c r="D66">
-        <v>247.890067421544</v>
+        <v>245.3187325595827</v>
       </c>
       <c r="E66">
-        <v>-16.93599999999998</v>
+        <v>-12.66000000000003</v>
       </c>
       <c r="F66">
-        <v>273.664</v>
+        <v>277.94</v>
       </c>
       <c r="G66">
         <v>3.5</v>
@@ -6699,37 +6699,37 @@
         <v>35</v>
       </c>
       <c r="M66">
-        <v>40.17387520000001</v>
+        <v>40.80159200000001</v>
       </c>
       <c r="N66">
-        <v>-5.173875200000012</v>
+        <v>-5.801592000000007</v>
       </c>
       <c r="O66">
-        <v>-1.189991296000003</v>
+        <v>-1.334366160000002</v>
       </c>
       <c r="P66">
-        <v>-3.983883904000009</v>
+        <v>-4.467225840000005</v>
       </c>
       <c r="Q66">
-        <v>4.616116095999992</v>
+        <v>4.132774159999997</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1862035105939037</v>
+        <v>0.1902150394680152</v>
       </c>
       <c r="T66">
-        <v>2.171997655220478</v>
+        <v>2.23405473108392</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.2003789766340489</v>
+        <v>0.1972962231473713</v>
       </c>
       <c r="W66">
-        <v>0.1173843662301216</v>
+        <v>0.1178369144419659</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8712129418871692</v>
+        <v>0.857809665858136</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1431692582010832</v>
+        <v>0.1441792582010832</v>
       </c>
       <c r="C67">
-        <v>-29.12126744041728</v>
+        <v>-35.91580564060118</v>
       </c>
       <c r="D67">
-        <v>245.3187325595827</v>
+        <v>242.8001943593988</v>
       </c>
       <c r="E67">
-        <v>-12.66000000000003</v>
+        <v>-8.384000000000015</v>
       </c>
       <c r="F67">
-        <v>277.94</v>
+        <v>282.216</v>
       </c>
       <c r="G67">
         <v>3.5</v>
@@ -6781,37 +6781,37 @@
         <v>35</v>
       </c>
       <c r="M67">
-        <v>40.80159200000001</v>
+        <v>41.42930880000001</v>
       </c>
       <c r="N67">
-        <v>-5.801592000000007</v>
+        <v>-6.429308800000008</v>
       </c>
       <c r="O67">
-        <v>-1.334366160000002</v>
+        <v>-1.478741024000002</v>
       </c>
       <c r="P67">
-        <v>-4.467225840000005</v>
+        <v>-4.950567776000006</v>
       </c>
       <c r="Q67">
-        <v>4.132774159999997</v>
+        <v>3.649432223999995</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1902150394680152</v>
+        <v>0.1944625406288392</v>
       </c>
       <c r="T67">
-        <v>2.23405473108392</v>
+        <v>2.299762223174624</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.1972962231473713</v>
+        <v>0.1943068864330172</v>
       </c>
       <c r="W67">
-        <v>0.1178369144419659</v>
+        <v>0.1182757490716331</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.857809665858136</v>
+        <v>0.8448125497087703</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1441792582010832</v>
+        <v>0.1451892582010832</v>
       </c>
       <c r="C68">
-        <v>-35.91580564060118</v>
+        <v>-42.65915674817109</v>
       </c>
       <c r="D68">
-        <v>242.8001943593988</v>
+        <v>240.3328432518289</v>
       </c>
       <c r="E68">
-        <v>-8.384000000000015</v>
+        <v>-4.108000000000004</v>
       </c>
       <c r="F68">
-        <v>282.216</v>
+        <v>286.492</v>
       </c>
       <c r="G68">
         <v>3.5</v>
@@ -6863,37 +6863,37 @@
         <v>35</v>
       </c>
       <c r="M68">
-        <v>41.42930880000001</v>
+        <v>42.05702560000001</v>
       </c>
       <c r="N68">
-        <v>-6.429308800000008</v>
+        <v>-7.05702560000001</v>
       </c>
       <c r="O68">
-        <v>-1.478741024000002</v>
+        <v>-1.623115888000002</v>
       </c>
       <c r="P68">
-        <v>-4.950567776000006</v>
+        <v>-5.433909712000007</v>
       </c>
       <c r="Q68">
-        <v>3.649432223999995</v>
+        <v>3.166090287999994</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1944625406288392</v>
+        <v>0.1989674661024405</v>
       </c>
       <c r="T68">
-        <v>2.299762223174624</v>
+        <v>2.36945198751325</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.1943068864330172</v>
+        <v>0.1914067836504348</v>
       </c>
       <c r="W68">
-        <v>0.1182757490716331</v>
+        <v>0.1187014841601162</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8448125497087703</v>
+        <v>0.8322034071758035</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1451892582010832</v>
+        <v>0.1461992582010832</v>
       </c>
       <c r="C69">
-        <v>-42.65915674817109</v>
+        <v>-49.35286556428792</v>
       </c>
       <c r="D69">
-        <v>240.3328432518289</v>
+        <v>237.9151344357121</v>
       </c>
       <c r="E69">
-        <v>-4.108000000000004</v>
+        <v>0.1680000000000064</v>
       </c>
       <c r="F69">
-        <v>286.492</v>
+        <v>290.768</v>
       </c>
       <c r="G69">
         <v>3.5</v>
@@ -6945,37 +6945,37 @@
         <v>35</v>
       </c>
       <c r="M69">
-        <v>42.05702560000001</v>
+        <v>42.68474240000001</v>
       </c>
       <c r="N69">
-        <v>-7.05702560000001</v>
+        <v>-7.684742400000012</v>
       </c>
       <c r="O69">
-        <v>-1.623115888000002</v>
+        <v>-1.767490752000003</v>
       </c>
       <c r="P69">
-        <v>-5.433909712000007</v>
+        <v>-5.917251648000009</v>
       </c>
       <c r="Q69">
-        <v>3.166090287999994</v>
+        <v>2.682748351999992</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1989674661024405</v>
+        <v>0.2037539494181417</v>
       </c>
       <c r="T69">
-        <v>2.36945198751325</v>
+        <v>2.443497362123038</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.1914067836504348</v>
+        <v>0.1885919780085167</v>
       </c>
       <c r="W69">
-        <v>0.1187014841601162</v>
+        <v>0.1191146976283498</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8322034071758035</v>
+        <v>0.8199651217761593</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1461992582010832</v>
+        <v>0.1472092582010832</v>
       </c>
       <c r="C70">
-        <v>-49.35286556428792</v>
+        <v>-55.99841534744078</v>
       </c>
       <c r="D70">
-        <v>237.9151344357121</v>
+        <v>235.5455846525593</v>
       </c>
       <c r="E70">
-        <v>0.1680000000000064</v>
+        <v>4.444000000000017</v>
       </c>
       <c r="F70">
-        <v>290.768</v>
+        <v>295.044</v>
       </c>
       <c r="G70">
         <v>3.5</v>
@@ -7027,37 +7027,37 @@
         <v>35</v>
       </c>
       <c r="M70">
-        <v>42.68474240000001</v>
+        <v>43.31245920000001</v>
       </c>
       <c r="N70">
-        <v>-7.684742400000012</v>
+        <v>-8.312459200000006</v>
       </c>
       <c r="O70">
-        <v>-1.767490752000003</v>
+        <v>-1.911865616000002</v>
       </c>
       <c r="P70">
-        <v>-5.917251648000009</v>
+        <v>-6.400593584000005</v>
       </c>
       <c r="Q70">
-        <v>2.682748351999992</v>
+        <v>2.199406415999997</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2037539494181417</v>
+        <v>0.2088492381090495</v>
       </c>
       <c r="T70">
-        <v>2.443497362123038</v>
+        <v>2.522319857675395</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.1885919780085167</v>
+        <v>0.1858587609359295</v>
       </c>
       <c r="W70">
-        <v>0.1191146976283498</v>
+        <v>0.1195159338946056</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8199651217761593</v>
+        <v>0.8080815692866499</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1472092582010832</v>
+        <v>0.1880188759236159</v>
       </c>
       <c r="C71">
-        <v>-55.99841534744078</v>
+        <v>-127.8640739175464</v>
       </c>
       <c r="D71">
-        <v>235.5455846525593</v>
+        <v>167.9559260824536</v>
       </c>
       <c r="E71">
-        <v>4.444000000000017</v>
+        <v>8.720000000000027</v>
       </c>
       <c r="F71">
-        <v>295.044</v>
+        <v>299.3200000000001</v>
       </c>
       <c r="G71">
         <v>3.5</v>
@@ -7109,45 +7109,45 @@
         <v>35</v>
       </c>
       <c r="M71">
-        <v>43.31245920000001</v>
+        <v>60.10345600000001</v>
       </c>
       <c r="N71">
-        <v>-8.312459200000006</v>
+        <v>-25.10345600000001</v>
       </c>
       <c r="O71">
-        <v>-1.911865616000002</v>
+        <v>-5.773794880000002</v>
       </c>
       <c r="P71">
-        <v>-6.400593584000005</v>
+        <v>-19.32966112</v>
       </c>
       <c r="Q71">
-        <v>2.199406415999997</v>
+        <v>-10.72966112</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2088492381090495</v>
+        <v>0.220949605121127</v>
       </c>
       <c r="T71">
-        <v>2.522319857675395</v>
+        <v>2.709508686974373</v>
       </c>
       <c r="U71">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1858587609359295</v>
+        <v>0.1339357257592642</v>
       </c>
       <c r="W71">
-        <v>0.1195159338946056</v>
+        <v>0.1739057062675398</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.8080815692866499</v>
+        <v>0.5823292424315832</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1880188759236159</v>
+        <v>0.1895688759236159</v>
       </c>
       <c r="C72">
-        <v>-127.8640739175464</v>
+        <v>-133.950839173624</v>
       </c>
       <c r="D72">
-        <v>167.9559260824536</v>
+        <v>166.1451608263761</v>
       </c>
       <c r="E72">
-        <v>8.720000000000027</v>
+        <v>12.99600000000004</v>
       </c>
       <c r="F72">
-        <v>299.3200000000001</v>
+        <v>303.5960000000001</v>
       </c>
       <c r="G72">
         <v>3.5</v>
@@ -7191,37 +7191,37 @@
         <v>35</v>
       </c>
       <c r="M72">
-        <v>60.10345600000001</v>
+        <v>60.96207680000001</v>
       </c>
       <c r="N72">
-        <v>-25.10345600000001</v>
+        <v>-25.96207680000001</v>
       </c>
       <c r="O72">
-        <v>-5.773794880000002</v>
+        <v>-5.971277664000003</v>
       </c>
       <c r="P72">
-        <v>-19.32966112</v>
+        <v>-19.99079913600001</v>
       </c>
       <c r="Q72">
-        <v>-10.72966112</v>
+        <v>-11.39079913600001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.220949605121127</v>
+        <v>0.226989246677028</v>
       </c>
       <c r="T72">
-        <v>2.709508686974373</v>
+        <v>2.802940021007973</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1339357257592642</v>
+        <v>0.1320493070865985</v>
       </c>
       <c r="W72">
-        <v>0.1739057062675398</v>
+        <v>0.174284499137011</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5823292424315832</v>
+        <v>0.5741274221156454</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1895688759236159</v>
+        <v>0.191118875923616</v>
       </c>
       <c r="C73">
-        <v>-133.9508391736239</v>
+        <v>-139.9989764657968</v>
       </c>
       <c r="D73">
-        <v>166.1451608263761</v>
+        <v>164.3730235342032</v>
       </c>
       <c r="E73">
-        <v>12.99599999999998</v>
+        <v>17.27199999999999</v>
       </c>
       <c r="F73">
-        <v>303.596</v>
+        <v>307.872</v>
       </c>
       <c r="G73">
         <v>3.5</v>
@@ -7273,37 +7273,37 @@
         <v>35</v>
       </c>
       <c r="M73">
-        <v>60.96207680000001</v>
+        <v>61.8206976</v>
       </c>
       <c r="N73">
-        <v>-25.96207680000001</v>
+        <v>-26.8206976</v>
       </c>
       <c r="O73">
-        <v>-5.971277664000001</v>
+        <v>-6.168760448</v>
       </c>
       <c r="P73">
-        <v>-19.990799136</v>
+        <v>-20.651937152</v>
       </c>
       <c r="Q73">
-        <v>-11.390799136</v>
+        <v>-12.051937152</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2269892466770279</v>
+        <v>0.2334602912012075</v>
       </c>
       <c r="T73">
-        <v>2.802940021007972</v>
+        <v>2.903045021758257</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1320493070865985</v>
+        <v>0.1302152889326179</v>
       </c>
       <c r="W73">
-        <v>0.174284499137011</v>
+        <v>0.1746527699823303</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5741274221156454</v>
+        <v>0.5661534301418171</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.191118875923616</v>
+        <v>0.1926688759236159</v>
       </c>
       <c r="C74">
-        <v>-139.9989764657968</v>
+        <v>-146.0097087899587</v>
       </c>
       <c r="D74">
-        <v>164.3730235342032</v>
+        <v>162.6382912100414</v>
       </c>
       <c r="E74">
-        <v>17.27199999999999</v>
+        <v>21.548</v>
       </c>
       <c r="F74">
-        <v>307.872</v>
+        <v>312.148</v>
       </c>
       <c r="G74">
         <v>3.5</v>
@@ -7355,37 +7355,37 @@
         <v>35</v>
       </c>
       <c r="M74">
-        <v>61.8206976</v>
+        <v>62.67931840000001</v>
       </c>
       <c r="N74">
-        <v>-26.8206976</v>
+        <v>-27.67931840000001</v>
       </c>
       <c r="O74">
-        <v>-6.168760448</v>
+        <v>-6.366243232000002</v>
       </c>
       <c r="P74">
-        <v>-20.651937152</v>
+        <v>-21.313075168</v>
       </c>
       <c r="Q74">
-        <v>-12.051937152</v>
+        <v>-12.713075168</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2334602912012075</v>
+        <v>0.2404106723568077</v>
       </c>
       <c r="T74">
-        <v>2.903045021758257</v>
+        <v>3.010565207749303</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1302152889326179</v>
+        <v>0.1284315178513492</v>
       </c>
       <c r="W74">
-        <v>0.1746527699823303</v>
+        <v>0.1750109512154491</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5661534301418171</v>
+        <v>0.5583979037015181</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1926688759236159</v>
+        <v>0.1942188759236159</v>
       </c>
       <c r="C75">
-        <v>-146.0097087899587</v>
+        <v>-151.9842080529857</v>
       </c>
       <c r="D75">
-        <v>162.6382912100414</v>
+        <v>160.9397919470143</v>
       </c>
       <c r="E75">
-        <v>21.548</v>
+        <v>25.82400000000001</v>
       </c>
       <c r="F75">
-        <v>312.148</v>
+        <v>316.424</v>
       </c>
       <c r="G75">
         <v>3.5</v>
@@ -7437,37 +7437,37 @@
         <v>35</v>
       </c>
       <c r="M75">
-        <v>62.67931840000001</v>
+        <v>63.53793920000001</v>
       </c>
       <c r="N75">
-        <v>-27.67931840000001</v>
+        <v>-28.53793920000001</v>
       </c>
       <c r="O75">
-        <v>-6.366243232000002</v>
+        <v>-6.563726016000003</v>
       </c>
       <c r="P75">
-        <v>-21.313075168</v>
+        <v>-21.97421318400001</v>
       </c>
       <c r="Q75">
-        <v>-12.713075168</v>
+        <v>-13.37421318400001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2404106723568077</v>
+        <v>0.247895698216685</v>
       </c>
       <c r="T75">
-        <v>3.010565207749303</v>
+        <v>3.126356177278122</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1284315178513492</v>
+        <v>0.1266959567993039</v>
       </c>
       <c r="W75">
-        <v>0.1750109512154491</v>
+        <v>0.1753594518746998</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5583979037015181</v>
+        <v>0.55085198608393</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1942188759236159</v>
+        <v>0.1957688759236159</v>
       </c>
       <c r="C76">
-        <v>-151.9842080529857</v>
+        <v>-157.9235977128838</v>
       </c>
       <c r="D76">
-        <v>160.9397919470143</v>
+        <v>159.2764022871163</v>
       </c>
       <c r="E76">
-        <v>25.82400000000001</v>
+        <v>30.10000000000002</v>
       </c>
       <c r="F76">
-        <v>316.424</v>
+        <v>320.7</v>
       </c>
       <c r="G76">
         <v>3.5</v>
@@ -7519,37 +7519,37 @@
         <v>35</v>
       </c>
       <c r="M76">
-        <v>63.53793920000001</v>
+        <v>64.39656000000001</v>
       </c>
       <c r="N76">
-        <v>-28.53793920000001</v>
+        <v>-29.39656000000001</v>
       </c>
       <c r="O76">
-        <v>-6.563726016000003</v>
+        <v>-6.761208800000002</v>
       </c>
       <c r="P76">
-        <v>-21.97421318400001</v>
+        <v>-22.63535120000001</v>
       </c>
       <c r="Q76">
-        <v>-13.37421318400001</v>
+        <v>-14.0353512</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.247895698216685</v>
+        <v>0.2559795261453524</v>
       </c>
       <c r="T76">
-        <v>3.126356177278122</v>
+        <v>3.251410424369247</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1266959567993039</v>
+        <v>0.1250066773753132</v>
       </c>
       <c r="W76">
-        <v>0.1753594518746998</v>
+        <v>0.1756986591830371</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.55085198608393</v>
+        <v>0.5435072929361444</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1957688759236159</v>
+        <v>0.1973188759236159</v>
       </c>
       <c r="C77">
-        <v>-157.9235977128838</v>
+        <v>-163.8289552568869</v>
       </c>
       <c r="D77">
-        <v>159.2764022871163</v>
+        <v>157.6470447431131</v>
       </c>
       <c r="E77">
-        <v>30.10000000000002</v>
+        <v>34.37599999999998</v>
       </c>
       <c r="F77">
-        <v>320.7</v>
+        <v>324.976</v>
       </c>
       <c r="G77">
         <v>3.5</v>
@@ -7601,37 +7601,37 @@
         <v>35</v>
       </c>
       <c r="M77">
-        <v>64.39656000000001</v>
+        <v>65.25518080000001</v>
       </c>
       <c r="N77">
-        <v>-29.39656000000001</v>
+        <v>-30.25518080000001</v>
       </c>
       <c r="O77">
-        <v>-6.761208800000002</v>
+        <v>-6.958691584000001</v>
       </c>
       <c r="P77">
-        <v>-22.63535120000001</v>
+        <v>-23.296489216</v>
       </c>
       <c r="Q77">
-        <v>-14.0353512</v>
+        <v>-14.696489216</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2559795261453524</v>
+        <v>0.2647370064014087</v>
       </c>
       <c r="T77">
-        <v>3.251410424369247</v>
+        <v>3.386885858717966</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1250066773753132</v>
+        <v>0.1233618526730065</v>
       </c>
       <c r="W77">
-        <v>0.1756986591830371</v>
+        <v>0.1760289399832603</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5435072929361444</v>
+        <v>0.5363558811869846</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1973188759236159</v>
+        <v>0.1988688759236159</v>
       </c>
       <c r="C78">
-        <v>-163.8289552568869</v>
+        <v>-169.701314528995</v>
       </c>
       <c r="D78">
-        <v>157.6470447431131</v>
+        <v>156.050685471005</v>
       </c>
       <c r="E78">
-        <v>34.37599999999998</v>
+        <v>38.65199999999999</v>
       </c>
       <c r="F78">
-        <v>324.976</v>
+        <v>329.252</v>
       </c>
       <c r="G78">
         <v>3.5</v>
@@ -7683,37 +7683,37 @@
         <v>35</v>
       </c>
       <c r="M78">
-        <v>65.25518080000001</v>
+        <v>66.1138016</v>
       </c>
       <c r="N78">
-        <v>-30.25518080000001</v>
+        <v>-31.1138016</v>
       </c>
       <c r="O78">
-        <v>-6.958691584000001</v>
+        <v>-7.156174368000001</v>
       </c>
       <c r="P78">
-        <v>-23.296489216</v>
+        <v>-23.957627232</v>
       </c>
       <c r="Q78">
-        <v>-14.696489216</v>
+        <v>-15.357627232</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2647370064014087</v>
+        <v>0.2742560066797309</v>
       </c>
       <c r="T78">
-        <v>3.386885858717966</v>
+        <v>3.534141765618747</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1233618526730065</v>
+        <v>0.1217597506902401</v>
       </c>
       <c r="W78">
-        <v>0.1760289399832603</v>
+        <v>0.1763506420613998</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5363558811869846</v>
+        <v>0.5293902203923484</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1988688759236159</v>
+        <v>0.2004188759236159</v>
       </c>
       <c r="C79">
-        <v>-169.701314528995</v>
+        <v>-175.5416679175137</v>
       </c>
       <c r="D79">
-        <v>156.050685471005</v>
+        <v>154.4863320824863</v>
       </c>
       <c r="E79">
-        <v>38.65199999999999</v>
+        <v>42.928</v>
       </c>
       <c r="F79">
-        <v>329.252</v>
+        <v>333.528</v>
       </c>
       <c r="G79">
         <v>3.5</v>
@@ -7765,37 +7765,37 @@
         <v>35</v>
       </c>
       <c r="M79">
-        <v>66.1138016</v>
+        <v>66.9724224</v>
       </c>
       <c r="N79">
-        <v>-31.1138016</v>
+        <v>-31.9724224</v>
       </c>
       <c r="O79">
-        <v>-7.156174368000001</v>
+        <v>-7.353657152</v>
       </c>
       <c r="P79">
-        <v>-23.957627232</v>
+        <v>-24.618765248</v>
       </c>
       <c r="Q79">
-        <v>-15.357627232</v>
+        <v>-16.018765248</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2742560066797309</v>
+        <v>0.2846403706197186</v>
       </c>
       <c r="T79">
-        <v>3.534141765618747</v>
+        <v>3.694784573146872</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1217597506902401</v>
+        <v>0.1201987282454935</v>
       </c>
       <c r="W79">
-        <v>0.1763506420613998</v>
+        <v>0.1766640953683049</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5293902203923484</v>
+        <v>0.5226031662847542</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2004188759236159</v>
+        <v>0.201968875923616</v>
       </c>
       <c r="C80">
-        <v>-175.5416679175137</v>
+        <v>-181.3509684123254</v>
       </c>
       <c r="D80">
-        <v>154.4863320824863</v>
+        <v>152.9530315876746</v>
       </c>
       <c r="E80">
-        <v>42.928</v>
+        <v>47.20400000000001</v>
       </c>
       <c r="F80">
-        <v>333.528</v>
+        <v>337.804</v>
       </c>
       <c r="G80">
         <v>3.5</v>
@@ -7847,37 +7847,37 @@
         <v>35</v>
       </c>
       <c r="M80">
-        <v>66.9724224</v>
+        <v>67.83104320000001</v>
       </c>
       <c r="N80">
-        <v>-31.9724224</v>
+        <v>-32.83104320000001</v>
       </c>
       <c r="O80">
-        <v>-7.353657152</v>
+        <v>-7.551139936000003</v>
       </c>
       <c r="P80">
-        <v>-24.618765248</v>
+        <v>-25.27990326400001</v>
       </c>
       <c r="Q80">
-        <v>-16.018765248</v>
+        <v>-16.67990326400001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2846403706197186</v>
+        <v>0.29601372160161</v>
       </c>
       <c r="T80">
-        <v>3.694784573146872</v>
+        <v>3.870726695677677</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1201987282454935</v>
+        <v>0.11867722535631</v>
       </c>
       <c r="W80">
-        <v>0.1766640953683049</v>
+        <v>0.176969613148453</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5226031662847542</v>
+        <v>0.5159879363317825</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.201968875923616</v>
+        <v>0.2035188759236159</v>
       </c>
       <c r="C81">
-        <v>-181.3509684123254</v>
+        <v>-187.130131540851</v>
       </c>
       <c r="D81">
-        <v>152.9530315876746</v>
+        <v>151.449868459149</v>
       </c>
       <c r="E81">
-        <v>47.20400000000001</v>
+        <v>51.48000000000002</v>
       </c>
       <c r="F81">
-        <v>337.804</v>
+        <v>342.08</v>
       </c>
       <c r="G81">
         <v>3.5</v>
@@ -7929,37 +7929,37 @@
         <v>35</v>
       </c>
       <c r="M81">
-        <v>67.83104320000001</v>
+        <v>68.68966400000001</v>
       </c>
       <c r="N81">
-        <v>-32.83104320000001</v>
+        <v>-33.68966400000001</v>
       </c>
       <c r="O81">
-        <v>-7.551139936000003</v>
+        <v>-7.748622720000002</v>
       </c>
       <c r="P81">
-        <v>-25.27990326400001</v>
+        <v>-25.94104128000001</v>
       </c>
       <c r="Q81">
-        <v>-16.67990326400001</v>
+        <v>-17.34104128000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.29601372160161</v>
+        <v>0.3085244076816906</v>
       </c>
       <c r="T81">
-        <v>3.870726695677677</v>
+        <v>4.064263030461561</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.11867722535631</v>
+        <v>0.1171937600393561</v>
       </c>
       <c r="W81">
-        <v>0.176969613148453</v>
+        <v>0.1772674929840973</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5159879363317825</v>
+        <v>0.5095380871276354</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2035188759236159</v>
+        <v>0.205068875923616</v>
       </c>
       <c r="C82">
-        <v>-187.130131540851</v>
+        <v>-192.8800371909686</v>
       </c>
       <c r="D82">
-        <v>151.449868459149</v>
+        <v>149.9759628090315</v>
       </c>
       <c r="E82">
-        <v>51.48000000000002</v>
+        <v>55.75600000000003</v>
       </c>
       <c r="F82">
-        <v>342.08</v>
+        <v>346.3560000000001</v>
       </c>
       <c r="G82">
         <v>3.5</v>
@@ -8011,37 +8011,37 @@
         <v>35</v>
       </c>
       <c r="M82">
-        <v>68.68966400000001</v>
+        <v>69.54828480000002</v>
       </c>
       <c r="N82">
-        <v>-33.68966400000001</v>
+        <v>-34.54828480000002</v>
       </c>
       <c r="O82">
-        <v>-7.748622720000002</v>
+        <v>-7.946105504000005</v>
       </c>
       <c r="P82">
-        <v>-25.94104128000001</v>
+        <v>-26.60217929600001</v>
       </c>
       <c r="Q82">
-        <v>-17.34104128000001</v>
+        <v>-18.00217929600001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3085244076816906</v>
+        <v>0.3223520080859901</v>
       </c>
       <c r="T82">
-        <v>4.064263030461561</v>
+        <v>4.27817161101217</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1171937600393561</v>
+        <v>0.1157469234956603</v>
       </c>
       <c r="W82">
-        <v>0.1772674929840973</v>
+        <v>0.1775580177620714</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5095380871276354</v>
+        <v>0.5032474934593929</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.205068875923616</v>
+        <v>0.2361257458273615</v>
       </c>
       <c r="C83">
-        <v>-192.8800371909686</v>
+        <v>-221.6287323873084</v>
       </c>
       <c r="D83">
-        <v>149.9759628090315</v>
+        <v>125.5032676126916</v>
       </c>
       <c r="E83">
-        <v>55.75600000000003</v>
+        <v>60.03200000000004</v>
       </c>
       <c r="F83">
-        <v>346.3560000000001</v>
+        <v>350.6320000000001</v>
       </c>
       <c r="G83">
         <v>3.5</v>
@@ -8093,45 +8093,45 @@
         <v>35</v>
       </c>
       <c r="M83">
-        <v>69.54828480000002</v>
+        <v>82.67902560000002</v>
       </c>
       <c r="N83">
-        <v>-34.54828480000002</v>
+        <v>-47.67902560000002</v>
       </c>
       <c r="O83">
-        <v>-7.946105504000005</v>
+        <v>-10.966175888</v>
       </c>
       <c r="P83">
-        <v>-26.60217929600001</v>
+        <v>-36.71284971200001</v>
       </c>
       <c r="Q83">
-        <v>-18.00217929600001</v>
+        <v>-28.11284971200001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3223520080859901</v>
+        <v>0.3421986191115762</v>
       </c>
       <c r="T83">
-        <v>4.27817161101217</v>
+        <v>4.585192371599316</v>
       </c>
       <c r="U83">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1157469234956603</v>
+        <v>0.0973644759548303</v>
       </c>
       <c r="W83">
-        <v>0.1775580177620714</v>
+        <v>0.212841456569851</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.5032474934593929</v>
+        <v>0.4233238084992621</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2361257458273615</v>
+        <v>0.2380257458273616</v>
       </c>
       <c r="C84">
-        <v>-221.6287323873084</v>
+        <v>-227.1452332756664</v>
       </c>
       <c r="D84">
-        <v>125.5032676126916</v>
+        <v>124.2627667243337</v>
       </c>
       <c r="E84">
-        <v>60.03200000000004</v>
+        <v>64.30800000000005</v>
       </c>
       <c r="F84">
-        <v>350.6320000000001</v>
+        <v>354.9080000000001</v>
       </c>
       <c r="G84">
         <v>3.5</v>
@@ -8175,37 +8175,37 @@
         <v>35</v>
       </c>
       <c r="M84">
-        <v>82.67902560000002</v>
+        <v>83.68730640000003</v>
       </c>
       <c r="N84">
-        <v>-47.67902560000002</v>
+        <v>-48.68730640000003</v>
       </c>
       <c r="O84">
-        <v>-10.966175888</v>
+        <v>-11.19808047200001</v>
       </c>
       <c r="P84">
-        <v>-36.71284971200001</v>
+        <v>-37.48922592800002</v>
       </c>
       <c r="Q84">
-        <v>-28.11284971200001</v>
+        <v>-28.88922592800002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3421986191115762</v>
+        <v>0.3596338320004924</v>
       </c>
       <c r="T84">
-        <v>4.585192371599316</v>
+        <v>4.854909569928687</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0973644759548303</v>
+        <v>0.09619140997947088</v>
       </c>
       <c r="W84">
-        <v>0.212841456569851</v>
+        <v>0.2131180655268408</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4233238084992621</v>
+        <v>0.4182235216498734</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2380257458273616</v>
+        <v>0.2399257458273615</v>
       </c>
       <c r="C85">
-        <v>-227.1452332756664</v>
+        <v>-232.6374514324594</v>
       </c>
       <c r="D85">
-        <v>124.2627667243337</v>
+        <v>123.0465485675406</v>
       </c>
       <c r="E85">
-        <v>64.30800000000005</v>
+        <v>68.584</v>
       </c>
       <c r="F85">
-        <v>354.9080000000001</v>
+        <v>359.184</v>
       </c>
       <c r="G85">
         <v>3.5</v>
@@ -8257,37 +8257,37 @@
         <v>35</v>
       </c>
       <c r="M85">
-        <v>83.68730640000003</v>
+        <v>84.69558720000001</v>
       </c>
       <c r="N85">
-        <v>-48.68730640000003</v>
+        <v>-49.69558720000001</v>
       </c>
       <c r="O85">
-        <v>-11.19808047200001</v>
+        <v>-11.429985056</v>
       </c>
       <c r="P85">
-        <v>-37.48922592800002</v>
+        <v>-38.26560214400001</v>
       </c>
       <c r="Q85">
-        <v>-28.88922592800002</v>
+        <v>-29.665602144</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3596338320004924</v>
+        <v>0.3792484465005233</v>
       </c>
       <c r="T85">
-        <v>4.854909569928687</v>
+        <v>5.158341418049232</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.09619140997947088</v>
+        <v>0.09504627414638198</v>
       </c>
       <c r="W85">
-        <v>0.2131180655268408</v>
+        <v>0.2133880885562831</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4182235216498734</v>
+        <v>0.4132446702016608</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2399257458273615</v>
+        <v>0.2418257458273615</v>
       </c>
       <c r="C86">
-        <v>-232.6374514324594</v>
+        <v>-238.1060929464177</v>
       </c>
       <c r="D86">
-        <v>123.0465485675406</v>
+        <v>121.8539070535824</v>
       </c>
       <c r="E86">
-        <v>68.584</v>
+        <v>72.86000000000001</v>
       </c>
       <c r="F86">
-        <v>359.184</v>
+        <v>363.46</v>
       </c>
       <c r="G86">
         <v>3.5</v>
@@ -8339,37 +8339,37 @@
         <v>35</v>
       </c>
       <c r="M86">
-        <v>84.69558720000001</v>
+        <v>85.70386800000001</v>
       </c>
       <c r="N86">
-        <v>-49.69558720000001</v>
+        <v>-50.70386800000001</v>
       </c>
       <c r="O86">
-        <v>-11.429985056</v>
+        <v>-11.66188964</v>
       </c>
       <c r="P86">
-        <v>-38.26560214400001</v>
+        <v>-39.04197836000001</v>
       </c>
       <c r="Q86">
-        <v>-29.665602144</v>
+        <v>-30.44197836000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.379248446500523</v>
+        <v>0.4014783429338912</v>
       </c>
       <c r="T86">
-        <v>5.158341418049228</v>
+        <v>5.502230845919176</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.09504627414638198</v>
+        <v>0.09392808268583629</v>
       </c>
       <c r="W86">
-        <v>0.2133880885562831</v>
+        <v>0.2136517581026798</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4132446702016608</v>
+        <v>0.4083829681992882</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2418257458273615</v>
+        <v>0.2437257458273615</v>
       </c>
       <c r="C87">
-        <v>-238.1060929464177</v>
+        <v>-243.5518367937075</v>
       </c>
       <c r="D87">
-        <v>121.8539070535824</v>
+        <v>120.6841632062925</v>
       </c>
       <c r="E87">
-        <v>72.86000000000001</v>
+        <v>77.13599999999997</v>
       </c>
       <c r="F87">
-        <v>363.46</v>
+        <v>367.736</v>
       </c>
       <c r="G87">
         <v>3.5</v>
@@ -8421,37 +8421,37 @@
         <v>35</v>
       </c>
       <c r="M87">
-        <v>85.70386800000001</v>
+        <v>86.71214879999999</v>
       </c>
       <c r="N87">
-        <v>-50.70386800000001</v>
+        <v>-51.71214879999999</v>
       </c>
       <c r="O87">
-        <v>-11.66188964</v>
+        <v>-11.893794224</v>
       </c>
       <c r="P87">
-        <v>-39.04197836000001</v>
+        <v>-39.818354576</v>
       </c>
       <c r="Q87">
-        <v>-30.44197836000001</v>
+        <v>-31.218354576</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4014783429338912</v>
+        <v>0.4268839388577406</v>
       </c>
       <c r="T87">
-        <v>5.502230845919176</v>
+        <v>5.895247334913404</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.09392808268583629</v>
+        <v>0.09283589567786146</v>
       </c>
       <c r="W87">
-        <v>0.2136517581026798</v>
+        <v>0.2139092957991603</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4083829681992882</v>
+        <v>0.4036343290341803</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2437257458273615</v>
+        <v>0.2456257458273615</v>
       </c>
       <c r="C88">
-        <v>-243.5518367937075</v>
+        <v>-248.9753361269018</v>
       </c>
       <c r="D88">
-        <v>120.6841632062925</v>
+        <v>119.5366638730982</v>
       </c>
       <c r="E88">
-        <v>77.13599999999997</v>
+        <v>81.41199999999998</v>
       </c>
       <c r="F88">
-        <v>367.736</v>
+        <v>372.012</v>
       </c>
       <c r="G88">
         <v>3.5</v>
@@ -8503,37 +8503,37 @@
         <v>35</v>
       </c>
       <c r="M88">
-        <v>86.71214879999999</v>
+        <v>87.7204296</v>
       </c>
       <c r="N88">
-        <v>-51.71214879999999</v>
+        <v>-52.7204296</v>
       </c>
       <c r="O88">
-        <v>-11.893794224</v>
+        <v>-12.125698808</v>
       </c>
       <c r="P88">
-        <v>-39.818354576</v>
+        <v>-40.594730792</v>
       </c>
       <c r="Q88">
-        <v>-31.218354576</v>
+        <v>-31.994730792</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4268839388577406</v>
+        <v>0.4561980880006437</v>
       </c>
       <c r="T88">
-        <v>5.895247334913404</v>
+        <v>6.348727899137511</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.09283589567786146</v>
+        <v>0.09176881641719639</v>
       </c>
       <c r="W88">
-        <v>0.2139092957991603</v>
+        <v>0.2141609130888251</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4036343290341803</v>
+        <v>0.3989948539878103</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2456257458273615</v>
+        <v>0.2475257458273615</v>
       </c>
       <c r="C89">
-        <v>-248.9753361269018</v>
+        <v>-254.3772194911068</v>
       </c>
       <c r="D89">
-        <v>119.5366638730982</v>
+        <v>118.4107805088932</v>
       </c>
       <c r="E89">
-        <v>81.41199999999998</v>
+        <v>85.68799999999999</v>
       </c>
       <c r="F89">
-        <v>372.012</v>
+        <v>376.288</v>
       </c>
       <c r="G89">
         <v>3.5</v>
@@ -8585,37 +8585,37 @@
         <v>35</v>
       </c>
       <c r="M89">
-        <v>87.7204296</v>
+        <v>88.72871040000001</v>
       </c>
       <c r="N89">
-        <v>-52.7204296</v>
+        <v>-53.72871040000001</v>
       </c>
       <c r="O89">
-        <v>-12.125698808</v>
+        <v>-12.357603392</v>
       </c>
       <c r="P89">
-        <v>-40.594730792</v>
+        <v>-41.37110700800001</v>
       </c>
       <c r="Q89">
-        <v>-31.994730792</v>
+        <v>-32.77110700800001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4561980880006437</v>
+        <v>0.4903979286673641</v>
       </c>
       <c r="T89">
-        <v>6.348727899137511</v>
+        <v>6.877788557398972</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.09176881641719639</v>
+        <v>0.09072598895791005</v>
       </c>
       <c r="W89">
-        <v>0.2141609130888251</v>
+        <v>0.2144068118037248</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3989948539878103</v>
+        <v>0.3944608215561307</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2475257458273615</v>
+        <v>0.2494257458273615</v>
       </c>
       <c r="C90">
-        <v>-254.3772194911068</v>
+        <v>-259.7580919720044</v>
       </c>
       <c r="D90">
-        <v>118.4107805088932</v>
+        <v>117.3059080279956</v>
       </c>
       <c r="E90">
-        <v>85.68799999999999</v>
+        <v>89.964</v>
       </c>
       <c r="F90">
-        <v>376.288</v>
+        <v>380.564</v>
       </c>
       <c r="G90">
         <v>3.5</v>
@@ -8667,37 +8667,37 @@
         <v>35</v>
       </c>
       <c r="M90">
-        <v>88.72871040000001</v>
+        <v>89.73699120000001</v>
       </c>
       <c r="N90">
-        <v>-53.72871040000001</v>
+        <v>-54.73699120000001</v>
       </c>
       <c r="O90">
-        <v>-12.357603392</v>
+        <v>-12.589507976</v>
       </c>
       <c r="P90">
-        <v>-41.37110700800001</v>
+        <v>-42.14748322400001</v>
       </c>
       <c r="Q90">
-        <v>-32.77110700800001</v>
+        <v>-33.547483224</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4903979286673641</v>
+        <v>0.5308159221825791</v>
       </c>
       <c r="T90">
-        <v>6.877788557398972</v>
+        <v>7.503042062617062</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.09072598895791005</v>
+        <v>0.08970659582355152</v>
       </c>
       <c r="W90">
-        <v>0.2144068118037248</v>
+        <v>0.2146471847048065</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3944608215561307</v>
+        <v>0.3900286774937023</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2494257458273615</v>
+        <v>0.2513257458273615</v>
       </c>
       <c r="C91">
-        <v>-259.7580919720044</v>
+        <v>-265.1185362802149</v>
       </c>
       <c r="D91">
-        <v>117.3059080279956</v>
+        <v>116.2214637197851</v>
       </c>
       <c r="E91">
-        <v>89.964</v>
+        <v>94.24000000000001</v>
       </c>
       <c r="F91">
-        <v>380.564</v>
+        <v>384.84</v>
       </c>
       <c r="G91">
         <v>3.5</v>
@@ -8749,37 +8749,37 @@
         <v>35</v>
       </c>
       <c r="M91">
-        <v>89.73699120000001</v>
+        <v>90.74527200000001</v>
       </c>
       <c r="N91">
-        <v>-54.73699120000001</v>
+        <v>-55.74527200000001</v>
       </c>
       <c r="O91">
-        <v>-12.589507976</v>
+        <v>-12.82141256</v>
       </c>
       <c r="P91">
-        <v>-42.14748322400001</v>
+        <v>-42.92385944000001</v>
       </c>
       <c r="Q91">
-        <v>-33.547483224</v>
+        <v>-34.32385944000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5308159221825791</v>
+        <v>0.5793175144008369</v>
       </c>
       <c r="T91">
-        <v>7.503042062617062</v>
+        <v>8.253346268878767</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.08970659582355152</v>
+        <v>0.0887098558699565</v>
       </c>
       <c r="W91">
-        <v>0.2146471847048065</v>
+        <v>0.2148822159858643</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3900286774937023</v>
+        <v>0.38569502552155</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2513257458273615</v>
+        <v>0.2532257458273615</v>
       </c>
       <c r="C92">
-        <v>-265.1185362802149</v>
+        <v>-270.4591137760643</v>
       </c>
       <c r="D92">
-        <v>116.2214637197851</v>
+        <v>115.1568862239357</v>
       </c>
       <c r="E92">
-        <v>94.24000000000001</v>
+        <v>98.51600000000002</v>
       </c>
       <c r="F92">
-        <v>384.84</v>
+        <v>389.116</v>
       </c>
       <c r="G92">
         <v>3.5</v>
@@ -8831,37 +8831,37 @@
         <v>35</v>
       </c>
       <c r="M92">
-        <v>90.74527200000001</v>
+        <v>91.75355280000001</v>
       </c>
       <c r="N92">
-        <v>-55.74527200000001</v>
+        <v>-56.75355280000001</v>
       </c>
       <c r="O92">
-        <v>-12.82141256</v>
+        <v>-13.053317144</v>
       </c>
       <c r="P92">
-        <v>-42.92385944000001</v>
+        <v>-43.700235656</v>
       </c>
       <c r="Q92">
-        <v>-34.32385944000001</v>
+        <v>-35.100235656</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5793175144008369</v>
+        <v>0.6385972382231522</v>
       </c>
       <c r="T92">
-        <v>8.253346268878767</v>
+        <v>9.17038474319863</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0887098558699565</v>
+        <v>0.08773502228896797</v>
       </c>
       <c r="W92">
-        <v>0.2148822159858643</v>
+        <v>0.2151120817442614</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.38569502552155</v>
+        <v>0.3814566186476868</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2532257458273615</v>
+        <v>0.2551257458273615</v>
       </c>
       <c r="C93">
-        <v>-270.4591137760643</v>
+        <v>-275.7803654385422</v>
       </c>
       <c r="D93">
-        <v>115.1568862239357</v>
+        <v>114.1116345614578</v>
       </c>
       <c r="E93">
-        <v>98.51600000000002</v>
+        <v>102.792</v>
       </c>
       <c r="F93">
-        <v>389.116</v>
+        <v>393.3920000000001</v>
       </c>
       <c r="G93">
         <v>3.5</v>
@@ -8913,37 +8913,37 @@
         <v>35</v>
       </c>
       <c r="M93">
-        <v>91.75355280000001</v>
+        <v>92.76183360000002</v>
       </c>
       <c r="N93">
-        <v>-56.75355280000001</v>
+        <v>-57.76183360000002</v>
       </c>
       <c r="O93">
-        <v>-13.053317144</v>
+        <v>-13.28522172800001</v>
       </c>
       <c r="P93">
-        <v>-43.700235656</v>
+        <v>-44.47661187200001</v>
       </c>
       <c r="Q93">
-        <v>-35.100235656</v>
+        <v>-35.87661187200001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6385972382231522</v>
+        <v>0.7126968930010464</v>
       </c>
       <c r="T93">
-        <v>9.17038474319863</v>
+        <v>10.31668283609846</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.08773502228896797</v>
+        <v>0.08678138074234876</v>
       </c>
       <c r="W93">
-        <v>0.2151120817442614</v>
+        <v>0.2153369504209542</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3814566186476868</v>
+        <v>0.3773103510536902</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2551257458273615</v>
+        <v>0.2570257458273615</v>
       </c>
       <c r="C94">
-        <v>-275.7803654385422</v>
+        <v>-281.082812781964</v>
       </c>
       <c r="D94">
-        <v>114.1116345614578</v>
+        <v>113.085187218036</v>
       </c>
       <c r="E94">
-        <v>102.792</v>
+        <v>107.068</v>
       </c>
       <c r="F94">
-        <v>393.3920000000001</v>
+        <v>397.6680000000001</v>
       </c>
       <c r="G94">
         <v>3.5</v>
@@ -8995,37 +8995,37 @@
         <v>35</v>
       </c>
       <c r="M94">
-        <v>92.76183360000002</v>
+        <v>93.77011440000003</v>
       </c>
       <c r="N94">
-        <v>-57.76183360000002</v>
+        <v>-58.77011440000003</v>
       </c>
       <c r="O94">
-        <v>-13.28522172800001</v>
+        <v>-13.51712631200001</v>
       </c>
       <c r="P94">
-        <v>-44.47661187200001</v>
+        <v>-45.25298808800002</v>
       </c>
       <c r="Q94">
-        <v>-35.87661187200001</v>
+        <v>-36.65298808800002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7126968930010464</v>
+        <v>0.8079678777154817</v>
       </c>
       <c r="T94">
-        <v>10.31668283609846</v>
+        <v>11.79049466982682</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.08678138074234876</v>
+        <v>0.08584824761608692</v>
       </c>
       <c r="W94">
-        <v>0.2153369504209542</v>
+        <v>0.2155569832121267</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3773103510536902</v>
+        <v>0.3732532505047257</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2570257458273615</v>
+        <v>0.2589257458273615</v>
       </c>
       <c r="C95">
-        <v>-281.082812781964</v>
+        <v>-286.3669587236013</v>
       </c>
       <c r="D95">
-        <v>113.085187218036</v>
+        <v>112.0770412763988</v>
       </c>
       <c r="E95">
-        <v>107.068</v>
+        <v>111.3440000000001</v>
       </c>
       <c r="F95">
-        <v>397.6680000000001</v>
+        <v>401.9440000000001</v>
       </c>
       <c r="G95">
         <v>3.5</v>
@@ -9077,37 +9077,37 @@
         <v>35</v>
       </c>
       <c r="M95">
-        <v>93.77011440000003</v>
+        <v>94.77839520000002</v>
       </c>
       <c r="N95">
-        <v>-58.77011440000003</v>
+        <v>-59.77839520000002</v>
       </c>
       <c r="O95">
-        <v>-13.51712631200001</v>
+        <v>-13.749030896</v>
       </c>
       <c r="P95">
-        <v>-45.25298808800002</v>
+        <v>-46.02936430400001</v>
       </c>
       <c r="Q95">
-        <v>-36.65298808800002</v>
+        <v>-37.42936430400001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8079678777154817</v>
+        <v>0.9349958573347289</v>
       </c>
       <c r="T95">
-        <v>11.79049466982682</v>
+        <v>13.75557711479795</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.08584824761608692</v>
+        <v>0.08493496838612856</v>
       </c>
       <c r="W95">
-        <v>0.2155569832121267</v>
+        <v>0.2157723344545509</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3732532505047257</v>
+        <v>0.3692824712440372</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2589257458273615</v>
+        <v>0.2608257458273616</v>
       </c>
       <c r="C96">
-        <v>-286.3669587236013</v>
+        <v>-291.6332884053136</v>
       </c>
       <c r="D96">
-        <v>112.0770412763988</v>
+        <v>111.0867115946865</v>
       </c>
       <c r="E96">
-        <v>111.3440000000001</v>
+        <v>115.62</v>
       </c>
       <c r="F96">
-        <v>401.9440000000001</v>
+        <v>406.22</v>
       </c>
       <c r="G96">
         <v>3.5</v>
@@ -9159,37 +9159,37 @@
         <v>35</v>
       </c>
       <c r="M96">
-        <v>94.77839520000002</v>
+        <v>95.78667600000001</v>
       </c>
       <c r="N96">
-        <v>-59.77839520000002</v>
+        <v>-60.78667600000001</v>
       </c>
       <c r="O96">
-        <v>-13.749030896</v>
+        <v>-13.98093548</v>
       </c>
       <c r="P96">
-        <v>-46.02936430400001</v>
+        <v>-46.80574052000001</v>
       </c>
       <c r="Q96">
-        <v>-37.42936430400001</v>
+        <v>-38.20574052000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9349958573347289</v>
+        <v>1.112835028801675</v>
       </c>
       <c r="T96">
-        <v>13.75557711479795</v>
+        <v>16.50669253775756</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.08493496838612856</v>
+        <v>0.08404091608732721</v>
       </c>
       <c r="W96">
-        <v>0.2157723344545509</v>
+        <v>0.2159831519866083</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3692824712440372</v>
+        <v>0.3653952873362053</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2608257458273616</v>
+        <v>0.2627257458273615</v>
       </c>
       <c r="C97">
-        <v>-291.6332884053136</v>
+        <v>-296.8822699720008</v>
       </c>
       <c r="D97">
-        <v>111.0867115946865</v>
+        <v>110.1137300279993</v>
       </c>
       <c r="E97">
-        <v>115.62</v>
+        <v>119.896</v>
       </c>
       <c r="F97">
-        <v>406.22</v>
+        <v>410.496</v>
       </c>
       <c r="G97">
         <v>3.5</v>
@@ -9241,37 +9241,37 @@
         <v>35</v>
       </c>
       <c r="M97">
-        <v>95.78667600000001</v>
+        <v>96.79495680000001</v>
       </c>
       <c r="N97">
-        <v>-60.78667600000001</v>
+        <v>-61.79495680000001</v>
       </c>
       <c r="O97">
-        <v>-13.98093548</v>
+        <v>-14.212840064</v>
       </c>
       <c r="P97">
-        <v>-46.80574052000001</v>
+        <v>-47.582116736</v>
       </c>
       <c r="Q97">
-        <v>-38.20574052000001</v>
+        <v>-38.982116736</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.112835028801675</v>
+        <v>1.379593786002095</v>
       </c>
       <c r="T97">
-        <v>16.50669253775756</v>
+        <v>20.63336567219695</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.08404091608732721</v>
+        <v>0.08316548987808423</v>
       </c>
       <c r="W97">
-        <v>0.2159831519866083</v>
+        <v>0.2161895774867477</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3653952873362053</v>
+        <v>0.3615890864264532</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2627257458273615</v>
+        <v>0.2646257458273615</v>
       </c>
       <c r="C98">
-        <v>-296.8822699720007</v>
+        <v>-302.1143553095014</v>
       </c>
       <c r="D98">
-        <v>110.1137300279993</v>
+        <v>109.1576446904986</v>
       </c>
       <c r="E98">
-        <v>119.896</v>
+        <v>124.172</v>
       </c>
       <c r="F98">
-        <v>410.496</v>
+        <v>414.772</v>
       </c>
       <c r="G98">
         <v>3.5</v>
@@ -9323,37 +9323,37 @@
         <v>35</v>
       </c>
       <c r="M98">
-        <v>96.79495679999999</v>
+        <v>97.8032376</v>
       </c>
       <c r="N98">
-        <v>-61.79495679999999</v>
+        <v>-62.8032376</v>
       </c>
       <c r="O98">
-        <v>-14.212840064</v>
+        <v>-14.444744648</v>
       </c>
       <c r="P98">
-        <v>-47.582116736</v>
+        <v>-48.358492952</v>
       </c>
       <c r="Q98">
-        <v>-38.98211673599999</v>
+        <v>-39.758492952</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.379593786002091</v>
+        <v>1.824191714669455</v>
       </c>
       <c r="T98">
-        <v>20.63336567219689</v>
+        <v>27.51115422959587</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.08316548987808423</v>
+        <v>0.08230811369377408</v>
       </c>
       <c r="W98">
-        <v>0.2161895774867477</v>
+        <v>0.2163917467910081</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3615890864264532</v>
+        <v>0.3578613638859742</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2646257458273615</v>
+        <v>0.2665257458273615</v>
       </c>
       <c r="C99">
-        <v>-302.1143553095014</v>
+        <v>-307.3299807443801</v>
       </c>
       <c r="D99">
-        <v>109.1576446904986</v>
+        <v>108.2180192556199</v>
       </c>
       <c r="E99">
-        <v>124.172</v>
+        <v>128.448</v>
       </c>
       <c r="F99">
-        <v>414.772</v>
+        <v>419.048</v>
       </c>
       <c r="G99">
         <v>3.5</v>
@@ -9405,37 +9405,37 @@
         <v>35</v>
       </c>
       <c r="M99">
-        <v>97.8032376</v>
+        <v>98.81151840000001</v>
       </c>
       <c r="N99">
-        <v>-62.8032376</v>
+        <v>-63.81151840000001</v>
       </c>
       <c r="O99">
-        <v>-14.444744648</v>
+        <v>-14.676649232</v>
       </c>
       <c r="P99">
-        <v>-48.358492952</v>
+        <v>-49.13486916800001</v>
       </c>
       <c r="Q99">
-        <v>-39.758492952</v>
+        <v>-40.53486916800001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.824191714669455</v>
+        <v>2.713387572004182</v>
       </c>
       <c r="T99">
-        <v>27.51115422959587</v>
+        <v>41.26673134439379</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.08230811369377408</v>
+        <v>0.08146823498261312</v>
       </c>
       <c r="W99">
-        <v>0.2163917467910081</v>
+        <v>0.2165897901910998</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3578613638859742</v>
+        <v>0.3542097173157092</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2665257458273615</v>
+        <v>0.2684257458273615</v>
       </c>
       <c r="C100">
-        <v>-307.3299807443801</v>
+        <v>-312.5295677078803</v>
       </c>
       <c r="D100">
-        <v>108.2180192556199</v>
+        <v>107.2944322921197</v>
       </c>
       <c r="E100">
-        <v>128.448</v>
+        <v>132.724</v>
       </c>
       <c r="F100">
-        <v>419.048</v>
+        <v>423.324</v>
       </c>
       <c r="G100">
         <v>3.5</v>
@@ -9487,37 +9487,37 @@
         <v>35</v>
       </c>
       <c r="M100">
-        <v>98.81151840000001</v>
+        <v>99.81979920000001</v>
       </c>
       <c r="N100">
-        <v>-63.81151840000001</v>
+        <v>-64.81979920000001</v>
       </c>
       <c r="O100">
-        <v>-14.676649232</v>
+        <v>-14.908553816</v>
       </c>
       <c r="P100">
-        <v>-49.13486916800001</v>
+        <v>-49.911245384</v>
       </c>
       <c r="Q100">
-        <v>-40.53486916800001</v>
+        <v>-41.311245384</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.713387572004182</v>
+        <v>5.380975144008364</v>
       </c>
       <c r="T100">
-        <v>41.26673134439379</v>
+        <v>82.53346268878758</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.08146823498261312</v>
+        <v>0.08064532351814228</v>
       </c>
       <c r="W100">
-        <v>0.2165897901910998</v>
+        <v>0.2167838327144221</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3542097173157092</v>
+        <v>0.3506318413832273</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2684257458273615</v>
-      </c>
-      <c r="C101">
-        <v>-312.5295677078803</v>
-      </c>
-      <c r="D101">
-        <v>107.2944322921197</v>
-      </c>
-      <c r="E101">
-        <v>132.724</v>
-      </c>
-      <c r="F101">
-        <v>423.324</v>
-      </c>
-      <c r="G101">
-        <v>3.5</v>
-      </c>
-      <c r="H101">
-        <v>137</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>43.6</v>
-      </c>
-      <c r="K101">
-        <v>8.600000000000001</v>
-      </c>
-      <c r="L101">
-        <v>35</v>
-      </c>
-      <c r="M101">
-        <v>99.81979920000001</v>
-      </c>
-      <c r="N101">
-        <v>-64.81979920000001</v>
-      </c>
-      <c r="O101">
-        <v>-14.908553816</v>
-      </c>
-      <c r="P101">
-        <v>-49.911245384</v>
-      </c>
-      <c r="Q101">
-        <v>-41.311245384</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.380975144008364</v>
-      </c>
-      <c r="T101">
-        <v>82.53346268878758</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.08064532351814228</v>
-      </c>
-      <c r="W101">
-        <v>0.2167838327144221</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3506318413832273</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
